--- a/docs/test-cases/members/Group01_23130226_VoMinhNhut.xlsx
+++ b/docs/test-cases/members/Group01_23130226_VoMinhNhut.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="Rde46881891a9440f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test case List" sheetId="2" r:id="Re227121ff27a4cfb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TestDesign" sheetId="3" r:id="R7b5cfd126cef4463"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_EMP" sheetId="4" r:id="Rfa51bb0840524cff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_PERSONAL" sheetId="5" r:id="R34ed9c7be1b84e20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_JOB" sheetId="6" r:id="R4456e1d9b5aa4ced"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="7" r:id="Rd858ca0f510241c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Automation Plan" sheetId="8" r:id="R8c412de4fab34473"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Report" sheetId="9" r:id="R417b1d9d9ad4456f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R739b45e188bb48db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test case List" sheetId="2" r:id="R9ac2463c9267459f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TestDesign" sheetId="3" r:id="Ra7589f21bff5486b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_EMP" sheetId="4" r:id="R588a0c4c3ae041d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_PERSONAL" sheetId="5" r:id="Ra576c08c4f93428c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_JOB" sheetId="6" r:id="Re87b1e7ac9514a89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="7" r:id="R3b7c9d1b71d4489e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Automation Plan" sheetId="8" r:id="R58677b5b5fa74174"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Report" sheetId="9" r:id="Rfd03dbf4708d45ac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -189,7 +189,7 @@
         <x:color rgb="FF20603A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7F2E8"/>
         </x:patternFill>
       </x:fill>
@@ -200,7 +200,7 @@
         <x:color rgb="FFA52323"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -211,7 +211,7 @@
         <x:color rgb="FF805A00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0CE"/>
         </x:patternFill>
       </x:fill>
@@ -222,7 +222,7 @@
         <x:color rgb="FF525E6D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFECEFF3"/>
         </x:patternFill>
       </x:fill>
@@ -233,7 +233,7 @@
         <x:color rgb="FF20603A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7F2E8"/>
         </x:patternFill>
       </x:fill>
@@ -244,7 +244,7 @@
         <x:color rgb="FFA52323"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -255,7 +255,7 @@
         <x:color rgb="FF805A00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0CE"/>
         </x:patternFill>
       </x:fill>
@@ -266,7 +266,7 @@
         <x:color rgb="FF525E6D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFECEFF3"/>
         </x:patternFill>
       </x:fill>
@@ -277,7 +277,7 @@
         <x:color rgb="FF20603A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7F2E8"/>
         </x:patternFill>
       </x:fill>
@@ -288,7 +288,7 @@
         <x:color rgb="FFA52323"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -299,7 +299,7 @@
         <x:color rgb="FF805A00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0CE"/>
         </x:patternFill>
       </x:fill>
@@ -310,7 +310,7 @@
         <x:color rgb="FF525E6D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFECEFF3"/>
         </x:patternFill>
       </x:fill>
@@ -4773,13 +4773,25 @@
         <x:v>Kiểm thử chức năng, không scan bảo mật hay load test.</x:v>
       </x:c>
     </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="3"/>
-      <x:c r="B25" s="3"/>
-      <x:c r="C25" s="3"/>
-      <x:c r="D25" s="3"/>
-      <x:c r="E25" s="3"/>
-      <x:c r="F25" s="3"/>
+    <x:row r="25" ht="110" customHeight="1">
+      <x:c r="A25" s="3" t="str">
+        <x:v>ADD_DEFAULT</x:v>
+      </x:c>
+      <x:c r="B25" s="3" t="str">
+        <x:v>First=G01N01; Middle=Minh; Last=NhutBaseline</x:v>
+      </x:c>
+      <x:c r="C25" s="3" t="str">
+        <x:v>Áp dụng cho các ô tên còn lại khi TC chỉ thay một trường hoặc ghi tên hợp lệ. Employee Id dùng ID riêng được chỉ rõ trong TC; nếu chưa chỉ rõ, giữ ID tự sinh và kiểm tra chưa tồn tại.</x:v>
+      </x:c>
+      <x:c r="D25" s="3" t="str">
+        <x:v>Add Employee: chuỗi biên, ID, ảnh và validation</x:v>
+      </x:c>
+      <x:c r="E25" s="3" t="str">
+        <x:v>Sau case, xóa riêng nhân viên đã tạo sau khi giữ bằng chứng.</x:v>
+      </x:c>
+      <x:c r="F25" s="3" t="str">
+        <x:v>Giá trị nêu riêng trong TC được ưu tiên.</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="3"/>

--- a/docs/test-cases/members/Group01_23130226_VoMinhNhut.xlsx
+++ b/docs/test-cases/members/Group01_23130226_VoMinhNhut.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R739b45e188bb48db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test case List" sheetId="2" r:id="R9ac2463c9267459f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TestDesign" sheetId="3" r:id="Ra7589f21bff5486b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_EMP" sheetId="4" r:id="R588a0c4c3ae041d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_PERSONAL" sheetId="5" r:id="Ra576c08c4f93428c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_JOB" sheetId="6" r:id="Re87b1e7ac9514a89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="7" r:id="R3b7c9d1b71d4489e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Automation Plan" sheetId="8" r:id="R58677b5b5fa74174"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Report" sheetId="9" r:id="Rfd03dbf4708d45ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R8ad5995011ce416d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test case List" sheetId="2" r:id="R2cd72f1e78904743"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TestDesign" sheetId="3" r:id="R854b889adf6c4999"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_EMP" sheetId="4" r:id="Raafaa8d228bf4a6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_PERSONAL" sheetId="5" r:id="R38d37f2bd46f4e52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_JOB" sheetId="6" r:id="Rfffd753b6b794fdc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="7" r:id="R3db59ede649e410e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Automation Plan" sheetId="8" r:id="R1a600b6077ce4a87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Report" sheetId="9" r:id="Rfc099f8e00ab4016"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -752,7 +752,7 @@
         <x:v>Automation tool</x:v>
       </x:c>
       <x:c r="C19" s="3" t="str">
-        <x:v>Katalon Recorder</x:v>
+        <x:v>Katalon Recorder (phần PIM của Võ Minh Nhựt)</x:v>
       </x:c>
       <x:c r="D19" s="3"/>
       <x:c r="E19" s="3"/>
@@ -5209,7 +5209,7 @@
         <x:v>Review và Git</x:v>
       </x:c>
       <x:c r="C14" s="3" t="str">
-        <x:v>Review 75 TC; commit workbook trên nhánh nhat/asm6-pim. Tạo PR vào dev, xử lý góp ý rồi merge.</x:v>
+        <x:v>Review 75 TC; commit workbook trên nhánh nhut. Tạo PR vào dev, xử lý góp ý rồi merge.</x:v>
       </x:c>
       <x:c r="D14" s="3" t="str">
         <x:v>Workbook đúng tên; ảnh bằng chứng push/merge thật; nhóm trưởng tổng hợp sau review.</x:v>
@@ -5237,9 +5237,9 @@
       <x:c r="E16" s="3"/>
       <x:c r="F16" s="3"/>
     </x:row>
-    <x:row r="17" ht="38" customHeight="1">
+    <x:row r="17" ht="44" customHeight="1">
       <x:c r="A17" s="3" t="str">
-        <x:v>P1/P2 là thứ tự ưu tiên triển khai, không phải kết quả chạy. Workbook hiện là test design; automation scripts chưa được triển khai.</x:v>
+        <x:v>Katalon Recorder là lựa chọn cá nhân của Võ Minh Nhựt. Các thành viên tự chọn công cụ. P1/P2 là mức ưu tiên triển khai, không phải kết quả chạy. Chưa triển khai automation scripts.</x:v>
       </x:c>
       <x:c r="B17" s="3"/>
       <x:c r="C17" s="3"/>

--- a/docs/test-cases/members/Group01_23130226_VoMinhNhut.xlsx
+++ b/docs/test-cases/members/Group01_23130226_VoMinhNhut.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R5afcfa7487624732"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test case List" sheetId="2" r:id="R4b29a9228203498d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TestDesign" sheetId="3" r:id="R5f52212d97d8474c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_EMP" sheetId="4" r:id="Rc4a85e959e9c44d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_PERSONAL" sheetId="5" r:id="R7a0540d43dd2416a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_JOB" sheetId="6" r:id="R7d6ca090df72491e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="7" r:id="R67ab8591147d41f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Automation Plan" sheetId="8" r:id="R7d0d24743b1c4730"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Report" sheetId="9" r:id="Ref44bc6c6b674167"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R6ce442db74254706"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test case List" sheetId="2" r:id="Rcf3bc50c930e48c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TestDesign" sheetId="3" r:id="R5244d612e7a94695"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_EMP" sheetId="4" r:id="Rf177865332a54550"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_PERSONAL" sheetId="5" r:id="Rdf5d619283984c5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_JOB" sheetId="6" r:id="R387e8a31527649b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="7" r:id="R1b3dea0b060f41ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Automation Plan" sheetId="8" r:id="R623cd4ee93ef4295"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Report" sheetId="9" r:id="R53df4e1004b046f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -114,9 +114,6 @@
     <x:t xml:space="preserve">Automation tool</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Katalon Recorder (phần PIM của Võ Minh Nhựt)</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Scope</x:t>
   </x:si>
   <x:si>
@@ -211,10 +208,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Phân vùng tương đương</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TD_PIM_EMP_01
-TC_PIM_EMP_001, TC_PIM_EMP_002, TC_PIM_EMP_015</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Validation tên</x:t>
@@ -227,10 +220,6 @@
 Phân tích giá trị biên</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_EMP_02
-TC_PIM_EMP_003, TC_PIM_EMP_004, TC_PIM_EMP_005, TC_PIM_EMP_006, TC_PIM_EMP_007, TC_PIM_EMP_008, TC_PIM_EMP_009, TC_PIM_EMP_010, TC_PIM_EMP_011</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Employee Id</x:t>
   </x:si>
   <x:si>
@@ -241,18 +230,10 @@
 Phân vùng tương đương</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_EMP_03
-TC_PIM_EMP_012, TC_PIM_EMP_013, TC_PIM_EMP_014</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Ảnh đại diện</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">JPG/PNG hợp lệ; PDF sai loại; ảnh quá 1 MiB.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TD_PIM_EMP_04
-TC_PIM_EMP_016, TC_PIM_EMP_017, TC_PIM_EMP_018, TC_PIM_EMP_019</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Danh sách nhân viên</x:t>
@@ -266,27 +247,15 @@
 Chuyển trạng thái</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_EMP_05
-TC_PIM_EMP_020, TC_PIM_EMP_021, TC_PIM_EMP_022, TC_PIM_EMP_023, TC_PIM_EMP_024, TC_PIM_EMP_025</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Thông tin cá nhân</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Tên, nationality, marital status và gender lưu đúng sau tải lại.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_PERSONAL_01
-TC_PIM_PERSONAL_001, TC_PIM_PERSONAL_018, TC_PIM_PERSONAL_019, TC_PIM_PERSONAL_020</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Trường bắt buộc và độ dài tên.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_PERSONAL_02
-TC_PIM_PERSONAL_002, TC_PIM_PERSONAL_003, TC_PIM_PERSONAL_004, TC_PIM_PERSONAL_005, TC_PIM_PERSONAL_006, TC_PIM_PERSONAL_007</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Mã và giấy phép</x:t>
   </x:si>
   <x:si>
@@ -296,18 +265,10 @@
     <x:t xml:space="preserve">Phân tích giá trị biên</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_PERSONAL_03
-TC_PIM_PERSONAL_008, TC_PIM_PERSONAL_009, TC_PIM_PERSONAL_010, TC_PIM_PERSONAL_011, TC_PIM_PERSONAL_012, TC_PIM_PERSONAL_013</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Ngày</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Ngày nhuận hợp lệ và ngày không tồn tại cho DOB/License Expiry.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TD_PIM_PERSONAL_04
-TC_PIM_PERSONAL_014, TC_PIM_PERSONAL_015, TC_PIM_PERSONAL_016, TC_PIM_PERSONAL_017</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Attachments</x:t>
@@ -321,18 +282,10 @@
 Phân tích giá trị biên</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_PERSONAL_05
-TC_PIM_PERSONAL_021, TC_PIM_PERSONAL_022, TC_PIM_PERSONAL_023, TC_PIM_PERSONAL_024, TC_PIM_PERSONAL_025</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Joined Date</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Ngày hợp lệ, ngày không tồn tại và để trống tùy chọn.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_01
-TC_PIM_JOB_001, TC_PIM_JOB_002, TC_PIM_JOB_009</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Danh mục công việc</x:t>
@@ -345,10 +298,6 @@
 Bảng quyết định</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_02
-TC_PIM_JOB_003, TC_PIM_JOB_004, TC_PIM_JOB_005, TC_PIM_JOB_006, TC_PIM_JOB_007, TC_PIM_JOB_008</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Hiển thị hợp đồng</x:t>
   </x:si>
   <x:si>
@@ -357,10 +306,6 @@
   <x:si>
     <x:t xml:space="preserve">Phân vùng tương đương
 Chuyển trạng thái</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_03
-TC_PIM_JOB_010, TC_PIM_JOB_011</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Ngày hợp đồng</x:t>
@@ -372,10 +317,6 @@
     <x:t xml:space="preserve">Bảng quyết định
 Phân tích giá trị biên
 Phân vùng tương đương</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_04
-TC_PIM_JOB_012, TC_PIM_JOB_013, TC_PIM_JOB_014, TC_PIM_JOB_015, TC_PIM_JOB_016</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Tệp hợp đồng và Job attachments</x:t>
@@ -390,10 +331,6 @@
 Bảng quyết định</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_05
-TC_PIM_JOB_017, TC_PIM_JOB_018, TC_PIM_JOB_019, TC_PIM_JOB_020, TC_PIM_JOB_021, TC_PIM_JOB_022, TC_PIM_JOB_023, TC_PIM_JOB_024, TC_PIM_JOB_025</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Module Code</x:t>
   </x:si>
   <x:si>
@@ -445,297 +382,148 @@
     <x:t xml:space="preserve">Test date</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_001</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Tạo nhân viên với các trường bắt buộc</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Mở hồ sơ nhân viên vừa tạo. Danh sách có đúng nhân viên G01N01 NhutA001 với ID đã nhập.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_EMP_01
-Positive; Phân vùng tương đương
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_002</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Tạo nhân viên có đủ họ, tên đệm và tên</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Ba ô tên giữ đúng G01N01, Minh, NhutA002 sau tải lại. ID đúng G1N01A0002.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_003</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Bỏ trống First Name</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">First Name hiển thị Required. Không chuyển sang hồ sơ mới và không tạo nhân viên.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_EMP_02
-Negative; Phân vùng tương đương
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_004</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Bỏ trống Last Name</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Last Name hiển thị Required. Không tạo nhân viên.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_005</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">First Name chỉ có dấu cách</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">First Name bị từ chối do chỉ có khoảng trắng. Không tạo nhân viên.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_006</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">First Name dài 30 ký tự</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">First Name được lưu nguyên đủ 30 ký tự. Tạo đúng một nhân viên.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_EMP_02
-Positive; Phân tích giá trị biên
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_007</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">First Name dài 31 ký tự</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Có lỗi giới hạn 30 ký tự tại First Name. Không lưu giá trị 31 ký tự. Nếu UI chặn ký tự thứ 31, xác nhận maxlength và không coi là đã lưu chuỗi 31 ký tự.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_EMP_02
-Negative; Phân tích giá trị biên
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_008</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Last Name dài 30 ký tự</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Last Name được lưu nguyên đủ 30 ký tự. Tạo đúng một nhân viên.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_009</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Last Name dài 31 ký tự</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Có lỗi giới hạn 30 ký tự tại Last Name. Không lưu giá trị 31 ký tự. Nếu UI chặn ký tự thứ 31, xác nhận maxlength và không coi là đã lưu chuỗi 31 ký tự.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_010</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Middle Name dài 30 ký tự</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Middle Name được lưu nguyên đủ 30 ký tự. Tạo đúng một nhân viên.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_011</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Middle Name dài 31 ký tự</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Có lỗi giới hạn 30 ký tự tại Middle Name. Không lưu giá trị 31 ký tự. Nếu UI chặn ký tự thứ 31, xác nhận maxlength và không coi là đã lưu chuỗi 31 ký tự.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_012</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Employee Id đúng giới hạn 10 ký tự</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">ID giữ nguyên G1N01A0012, không cắt ngắn hoặc đổi.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_EMP_03
-Positive; Phân tích giá trị biên
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_013</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Employee Id vượt giới hạn 10 ký tự</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Có lỗi giới hạn 10 ký tự. Không lưu ID 11 ký tự. Nếu UI giới hạn nhập, ghi rõ giá trị thực nhập.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_EMP_03
-Negative; Phân tích giá trị biên
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_014</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Employee Id trùng nhân viên hiện có</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Thông báo ID đã tồn tại. Không tạo thêm nhân viên sử dụng ID của F_DUP.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_EMP_03
-Negative; Phân vùng tương đương
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_015</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Hủy tạo nhân viên chưa lưu</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Quay về Employee List. Không có nhân viên mới với ID G1N01A0015.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_016</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Tạo nhân viên kèm ảnh JPG hợp lệ</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Ảnh được chấp nhận, hồ sơ tạo thành công và hiển thị ảnh đã tải lên.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_EMP_04
-Positive; Phân vùng tương đương
-Automation: P2
-File upload: xác nhận bằng UI và mở lại hồ sơ.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_017</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Tạo nhân viên kèm ảnh PNG hợp lệ</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_018</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Từ chối tệp không phải ảnh đại diện</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Hiển thị lỗi loại tệp. Không thay ảnh đại diện bằng PDF.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_EMP_04
-Negative; Phân vùng tương đương
-Automation: P2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_019</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Từ chối ảnh đại diện vượt 1 MiB</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Hiển thị lỗi dung lượng tối đa 1 MiB. Ảnh quá cỡ không được chấp nhận.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_EMP_04
-Negative; Phân tích giá trị biên
-Automation: P2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_020</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Tìm nhân viên theo Employee Id</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Có F_DUP với đúng Employee Id đã nhập. Không có nhân viên mang ID khác trong tập kết quả.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_EMP_05
-Positive; Phân vùng tương đương
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_021</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Tìm nhân viên bằng autocomplete tên</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Hiển thị nhân viên đã chọn với Employee Id G1N01P0001.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_022</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Tìm Employee Id không tồn tại</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Hiển thị trạng thái không có bản ghi. Không hiển thị dòng nhân viên cũ.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_EMP_05
-Negative; Phân vùng tương đương
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_023</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Lọc kết hợp Employment Status và Job Title</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Có F_FILTER. Mọi kết quả đồng thời thỏa hai tiêu chí. Không có F_FILTER_NEG.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_EMP_05
-Integration; Bảng quyết định
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_024</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Reset xóa bộ lọc đã nhập</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Employee Id rỗng, status về mặc định. Search không còn bị giới hạn bởi ID và status trước đó.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_025</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Sắp xếp danh sách theo First Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TD_PIM_EMP_05
-Positive; Chuyển trạng thái
-Automation: P2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_001</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Cập nhật đầy đủ ba thành phần tên</x:t>
@@ -760,9 +548,6 @@
 Automation: P1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_002</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">First Name bắt buộc</x:t>
   </x:si>
   <x:si>
@@ -782,9 +567,6 @@
 Automation: P1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_003</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Last Name bắt buộc</x:t>
   </x:si>
   <x:si>
@@ -799,9 +581,6 @@
     <x:t xml:space="preserve">Last Name hiển thị Required. Không lưu tên rỗng; giá trị cũ còn nguyên sau tải lại.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_004</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">First Name đúng giới hạn 30 ký tự</x:t>
   </x:si>
   <x:si>
@@ -821,9 +600,6 @@
 Automation: P1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_005</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">First Name vượt giới hạn 30 ký tự</x:t>
   </x:si>
   <x:si>
@@ -843,9 +619,6 @@
 Automation: P1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_006</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Middle Name vượt giới hạn 30 ký tự</x:t>
   </x:si>
   <x:si>
@@ -857,9 +630,6 @@
 Kết thúc: khôi phục fixture theo Test Data.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_007</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Last Name vượt giới hạn 30 ký tự</x:t>
   </x:si>
   <x:si>
@@ -871,9 +641,6 @@
 Kết thúc: khôi phục fixture theo Test Data.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_008</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Employee Id dài 10 ký tự</x:t>
   </x:si>
   <x:si>
@@ -893,9 +660,6 @@
 Automation: P1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_009</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Employee Id dài 11 ký tự</x:t>
   </x:si>
   <x:si>
@@ -915,9 +679,6 @@
 Automation: P1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_010</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Other Id dài 30 ký tự</x:t>
   </x:si>
   <x:si>
@@ -932,9 +693,6 @@
     <x:t xml:space="preserve">Lưu nguyên 30 ký tự, không có lỗi giới hạn.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_011</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Other Id dài 31 ký tự</x:t>
   </x:si>
   <x:si>
@@ -949,9 +707,6 @@
     <x:t xml:space="preserve">Có lỗi giới hạn 30 ký tự. Giá trị vượt giới hạn không được lưu.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_012</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Driver's License Number dài 30 ký tự</x:t>
   </x:si>
   <x:si>
@@ -963,9 +718,6 @@
 Kết thúc: khôi phục fixture theo Test Data.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_013</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Driver's License Number dài 31 ký tự</x:t>
   </x:si>
   <x:si>
@@ -977,9 +729,6 @@
 Kết thúc: khôi phục fixture theo Test Data.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_014</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Date of Birth là ngày nhuận hợp lệ</x:t>
   </x:si>
   <x:si>
@@ -999,9 +748,6 @@
 Automation: P1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_015</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Date of Birth là ngày không tồn tại</x:t>
   </x:si>
   <x:si>
@@ -1021,9 +767,6 @@
 Automation: P1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_016</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">License Expiry Date hợp lệ</x:t>
   </x:si>
   <x:si>
@@ -1038,9 +781,6 @@
     <x:t xml:space="preserve">Lưu đúng ngày 31/12/2030, không có lỗi định dạng.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_017</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">License Expiry Date không hợp lệ</x:t>
   </x:si>
   <x:si>
@@ -1055,9 +795,6 @@
     <x:t xml:space="preserve">Hiển thị lỗi ngày/định dạng và không lưu ngày không tồn tại.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_018</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Thay đổi Nationality</x:t>
   </x:si>
   <x:si>
@@ -1072,9 +809,6 @@
     <x:t xml:space="preserve">Nationality giữ đúng nhãn đã chọn sau tải lại.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_019</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Thay đổi Marital Status</x:t>
   </x:si>
   <x:si>
@@ -1089,9 +823,6 @@
     <x:t xml:space="preserve">Trạng thái hôn nhân được lưu đúng lựa chọn đã ghi trong run.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_020</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Thay đổi Gender</x:t>
   </x:si>
   <x:si>
@@ -1106,9 +837,6 @@
     <x:t xml:space="preserve">Chỉ radio đã chọn được đánh dấu. Giá trị giữ đúng sau tải lại.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_021</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Thêm attachment hợp lệ vào Personal Details</x:t>
   </x:si>
   <x:si>
@@ -1128,9 +856,6 @@
 Automation: P2</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_022</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Không chọn file khi thêm attachment</x:t>
   </x:si>
   <x:si>
@@ -1150,9 +875,6 @@
 Automation: P1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_023</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Mô tả attachment đúng 200 ký tự</x:t>
   </x:si>
   <x:si>
@@ -1172,9 +894,6 @@
 Automation: P2</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_024</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Mô tả attachment vượt 200 ký tự</x:t>
   </x:si>
   <x:si>
@@ -1194,9 +913,6 @@
 Automation: P2</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_PERSONAL_025</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Hủy rồi xác nhận xóa attachment của nhóm</x:t>
   </x:si>
   <x:si>
@@ -1217,9 +933,6 @@
 Chỉ xóa tệp fixture của nhóm.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_001</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Lưu Joined Date hợp lệ</x:t>
   </x:si>
   <x:si>
@@ -1239,9 +952,6 @@
 Automation: P1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_002</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Joined Date không tồn tại</x:t>
   </x:si>
   <x:si>
@@ -1261,9 +971,6 @@
 Automation: P1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_003</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Thay đổi Job Title</x:t>
   </x:si>
   <x:si>
@@ -1283,9 +990,6 @@
 Automation: P1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_004</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Thay đổi Job Category</x:t>
   </x:si>
   <x:si>
@@ -1300,9 +1004,6 @@
     <x:t xml:space="preserve">Job Category giữ đúng nhãn đã chọn sau tải lại; không thay đổi nhân viên khác.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_005</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Thay đổi Sub Unit</x:t>
   </x:si>
   <x:si>
@@ -1317,9 +1018,6 @@
     <x:t xml:space="preserve">Sub Unit giữ đúng nhãn đã chọn sau tải lại; không thay đổi nhân viên khác.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_006</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Thay đổi Location</x:t>
   </x:si>
   <x:si>
@@ -1334,9 +1032,6 @@
     <x:t xml:space="preserve">Location giữ đúng nhãn đã chọn sau tải lại; không thay đổi nhân viên khác.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_007</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Thay đổi Employment Status</x:t>
   </x:si>
   <x:si>
@@ -1351,9 +1046,6 @@
     <x:t xml:space="preserve">Employment Status giữ đúng nhãn đã chọn sau tải lại; không thay đổi nhân viên khác.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_008</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Lưu đồng thời các trường Job Details</x:t>
   </x:si>
   <x:si>
@@ -1373,9 +1065,6 @@
 Automation: P1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_009</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Xóa Joined Date tùy chọn</x:t>
   </x:si>
   <x:si>
@@ -1390,9 +1079,6 @@
     <x:t xml:space="preserve">Có thể lưu Joined Date rỗng. Không tự gán ngày khác.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_010</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Bật hiển thị Employment Contract Details</x:t>
   </x:si>
   <x:si>
@@ -1412,9 +1098,6 @@
 Automation: P1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_011</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Tắt phần mở rộng hợp đồng không xóa dữ liệu</x:t>
   </x:si>
   <x:si>
@@ -1434,9 +1117,6 @@
 Automation: P1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_012</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Hợp đồng có End Date sau Start Date</x:t>
   </x:si>
   <x:si>
@@ -1456,9 +1136,6 @@
 Automation: P1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_013</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">End Date trước Start Date</x:t>
   </x:si>
   <x:si>
@@ -1478,9 +1155,6 @@
 Automation: P1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_014</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">End Date bằng Start Date</x:t>
   </x:si>
   <x:si>
@@ -1500,9 +1174,6 @@
 Automation: P1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_015</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Start Date không tồn tại</x:t>
   </x:si>
   <x:si>
@@ -1521,9 +1192,6 @@
 Automation: P1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_016</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">End Date không tồn tại</x:t>
   </x:si>
   <x:si>
@@ -1535,9 +1203,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Có lỗi ngày/định dạng tại End Date. Không lưu ngày không tồn tại.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_017</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Tải tệp hợp đồng PDF hợp lệ</x:t>
@@ -1559,9 +1224,6 @@
 Automation: P2</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_018</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Từ chối tệp hợp đồng vượt giới hạn</x:t>
   </x:si>
   <x:si>
@@ -1582,9 +1244,6 @@
 Không mặc định giới hạn contract giống ảnh đại diện.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_019</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Từ chối loại file hợp đồng không cho phép</x:t>
   </x:si>
   <x:si>
@@ -1604,9 +1263,6 @@
 Automation: P2</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_020</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Giữ tệp hợp đồng hiện tại khi đổi ngày</x:t>
   </x:si>
   <x:si>
@@ -1626,9 +1282,6 @@
 Automation: P2</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_021</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Thay thế tệp hợp đồng hiện tại</x:t>
   </x:si>
   <x:si>
@@ -1643,9 +1296,6 @@
     <x:t xml:space="preserve">Tệp hợp đồng hiện tại là contract_v2.pdf với nội dung v2; không còn dùng v1 làm tệp hiện tại.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_022</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Replace Current nhưng không chọn tệp mới</x:t>
   </x:si>
   <x:si>
@@ -1665,9 +1315,6 @@
 Automation: P2</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_023</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Xóa riêng tệp hợp đồng hiện tại</x:t>
   </x:si>
   <x:si>
@@ -1688,9 +1335,6 @@
 Chỉ xóa tệp fixture của nhóm.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_024</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Thêm attachment tại tab Job</x:t>
   </x:si>
   <x:si>
@@ -1705,9 +1349,6 @@
     <x:t xml:space="preserve">Có dòng attachment với đúng tên và mô tả tại tab Job, không nhầm attachment của Personal Details.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_025</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Hủy thêm attachment tại tab Job</x:t>
   </x:si>
   <x:si>
@@ -1781,18 +1422,12 @@
     <x:t xml:space="preserve">Không đổi mật khẩu, không khóa tài khoản demo.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Chưa có kết quả execution.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">F_DUP</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Tạo trước run bằng Add Employee, không tạo login. Ghi employee key.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_014, 020, 024</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Chỉ xóa nhân viên fixture của nhóm sau khi lưu bằng chứng.</x:t>
   </x:si>
   <x:si>
@@ -1808,9 +1443,6 @@
     <x:t xml:space="preserve">Tạo trước run; ghi employee key và snapshot các giá trị cá nhân gốc.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">PIM_PERSONAL; TC_PIM_EMP_021</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Khôi phục tên, ID, các trường cá nhân sau từng TC. Xóa tệp fixture còn lại.</x:t>
   </x:si>
   <x:si>
@@ -1967,9 +1599,6 @@
     <x:t xml:space="preserve">Ảnh thật 200×200 px, dung lượng &gt;0 và &lt;1 MiB; đúng MIME, không chỉ đổi đuôi.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_016–017</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Xóa hồ sơ thử của nhóm sau run.</x:t>
   </x:si>
   <x:si>
@@ -1982,12 +1611,6 @@
     <x:t xml:space="preserve">photo_invalid.pdf; photo_over_1m.png</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">PDF thực; PNG hợp lệ 1.048.577 byte. Xem Properties trước chạy.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TC_PIM_EMP_018–019</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Không tải lên dữ liệu nhạy cảm.</x:t>
   </x:si>
   <x:si>
@@ -2021,9 +1644,6 @@
     <x:t xml:space="preserve">Đọc Max Attachment Size và Allowed File Types tại cấu hình hoặc hint. Ghi giới hạn, MIME và thời điểm.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TC_PIM_JOB_018–019; các TC upload</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Tệp quá giới hạn = giới hạn byte +1. Không đổi config dùng chung.</x:t>
   </x:si>
   <x:si>
@@ -2204,15 +1824,9 @@
     <x:t xml:space="preserve">Không dùng dữ liệu cá nhân thật.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Chưa thực hiện</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Chuẩn bị test data</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Tạo F_DUP, F_PERSON, F_JOB, F_FILTER và baseline; chuẩn bị file đúng MIME và dung lượng.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Đối chiếu Employee Id, employee key và file Properties.</x:t>
   </x:si>
   <x:si>
@@ -2222,21 +1836,12 @@
     <x:t xml:space="preserve">Smoke / khả thi</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Record một luồng tạo nhân viên và một luồng sửa Job; chạy thử trên phiên bản Katalon Recorder đã cài.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Assertion giá trị đã lưu sau reload; không chỉ click thành công.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Xác nhận command từ Reference.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Tổ chức suite</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Tạo PIM_EMP, PIM_PERSONAL, PIM_JOB; đặt tên automation theo ID workbook. Tách setup, reset và cleanup.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Mỗi test độc lập, truy xuất được fixture theo employee key.</x:t>
   </x:si>
   <x:si>
@@ -2246,27 +1851,12 @@
     <x:t xml:space="preserve">Ưu tiên P1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Validation, tìm kiếm, dropdown và persist sau reload. Truyền data qua CSV khi nhiều bộ dùng cùng luồng.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">assertText/assertValue/assertElementPresent trên đúng trường và vùng lỗi.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Katalon Recorder: waitForElementPresent / waitForVisible theo Reference.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Ưu tiên P2</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Upload/download, sorting và thao tác xóa. Thử quyền truy cập file của extension trước khi mở rộng.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Kiểm tra tên/nội dung file, số dòng, thứ tự dữ liệu và dữ liệu không bị sửa ngoài phạm vi.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Nếu upload không ổn định, thực thi manual và ghi rõ.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Locator và đồng bộ</x:t>
   </x:si>
   <x:si>
@@ -2276,9 +1866,6 @@
     <x:t xml:space="preserve">Đúng Save của từng khối; đúng Attachments của Personal/Job.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Không trộn command Selenium IDE với Katalon Recorder.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Chạy và ghi kết quả</x:t>
   </x:si>
   <x:si>
@@ -2288,9 +1875,6 @@
     <x:t xml:space="preserve">So expected với actual. Failed ghi bước lỗi, lỗi script hay sản phẩm; Blocked ghi nguyên nhân.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Chưa có số liệu thời gian hoặc tỷ lệ pass thực tế.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Dọn dẹp và regression</x:t>
   </x:si>
   <x:si>
@@ -2334,18 +1918,16 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Execution coverage = (Passed + Failed) / Total. Pass rate = Passed / (Passed + Failed). Blocked và Skipped không được tính là đã thực thi.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sau run, điền actual result, Defect ID (nếu có), ảnh/log và ngày thực chạy tại sheet test case. Các tổng hợp tự cập nhật từ cột Result.</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <x:numFmt numFmtId="165" formatCode="0.0%"/>
+    <x:numFmt numFmtId="200" formatCode="dd/mm/yyyy hh:mm"/>
   </x:numFmts>
   <x:fonts count="6">
     <x:font>
@@ -2555,7 +2137,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="50">
+  <x:cellXfs count="51">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
@@ -2682,6 +2264,9 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="2" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -3019,7 +2604,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G7" s="35" t="str">
-        <x:v>1.1</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="H7" s="2"/>
     </x:row>
@@ -3113,13 +2698,25 @@
       </x:c>
       <x:c r="H13" s="2"/>
     </x:row>
-    <x:row r="14">
-      <x:c r="B14" s="2"/>
-      <x:c r="C14" s="2"/>
-      <x:c r="D14" s="2"/>
-      <x:c r="E14" s="2"/>
-      <x:c r="F14" s="2"/>
-      <x:c r="G14" s="2"/>
+    <x:row r="14" ht="52" customHeight="1">
+      <x:c r="B14" s="37" t="d">
+        <x:v>2026-10-21T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="C14" s="35" t="str">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="D14" s="35" t="str">
+        <x:v>Case ID / Execution</x:v>
+      </x:c>
+      <x:c r="E14" s="35" t="str">
+        <x:v>M</x:v>
+      </x:c>
+      <x:c r="F14" s="35" t="str">
+        <x:v>Đổi ID theo Module_Action_XX và ghi kết quả Playwright cho PIM_EMP.</x:v>
+      </x:c>
+      <x:c r="G14" s="35" t="str">
+        <x:v>ASM06 – tuần đầu</x:v>
+      </x:c>
       <x:c r="H14" s="2"/>
     </x:row>
     <x:row r="15" ht="24.75" customHeight="1">
@@ -3178,8 +2775,8 @@
       <x:c r="B19" s="34" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C19" s="35" t="s">
-        <x:v>32</x:v>
+      <x:c r="C19" s="35" t="str">
+        <x:v>Playwright (PIM_EMP); các thành viên tự chọn công cụ</x:v>
       </x:c>
       <x:c r="D19" s="39"/>
       <x:c r="E19" s="39"/>
@@ -3189,10 +2786,10 @@
     </x:row>
     <x:row r="20" ht="24.75" customHeight="1">
       <x:c r="B20" s="34" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C20" s="35" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="C20" s="35" t="s">
-        <x:v>34</x:v>
       </x:c>
       <x:c r="D20" s="39"/>
       <x:c r="E20" s="39"/>
@@ -4230,7 +3827,7 @@
   <x:sheetData>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="B2" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G2" s="2"/>
       <x:c r="H2" s="2"/>
@@ -4274,11 +3871,11 @@
     </x:row>
     <x:row r="6" ht="37.5" customHeight="1">
       <x:c r="B6" s="35" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C6" s="39"/>
       <x:c r="D6" s="35" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E6" s="39"/>
       <x:c r="F6" s="39"/>
@@ -4296,19 +3893,19 @@
     </x:row>
     <x:row r="8">
       <x:c r="B8" s="38" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C8" s="38" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C8" s="38" t="s">
+      <x:c r="D8" s="38" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D8" s="38" t="s">
+      <x:c r="E8" s="38" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E8" s="38" t="s">
+      <x:c r="F8" s="38" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="F8" s="38" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="G8" s="2"/>
       <x:c r="H8" s="2"/>
@@ -4318,16 +3915,16 @@
         <x:v>1.0</x:v>
       </x:c>
       <x:c r="C9" s="35" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D9" s="35" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="D9" s="35" t="s">
+      <x:c r="E9" s="35" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="E9" s="35" t="s">
+      <x:c r="F9" s="35" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="F9" s="35" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="G9" s="2"/>
       <x:c r="H9" s="2"/>
@@ -4337,16 +3934,16 @@
         <x:v>2.0</x:v>
       </x:c>
       <x:c r="C10" s="35" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D10" s="35" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D10" s="35" t="s">
+      <x:c r="E10" s="35" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="E10" s="35" t="s">
+      <x:c r="F10" s="35" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="F10" s="35" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="G10" s="2"/>
       <x:c r="H10" s="2"/>
@@ -4356,16 +3953,16 @@
         <x:v>3.0</x:v>
       </x:c>
       <x:c r="C11" s="35" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D11" s="35" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="D11" s="35" t="s">
+      <x:c r="E11" s="35" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E11" s="35" t="s">
+      <x:c r="F11" s="35" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="F11" s="35" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="G11" s="2"/>
       <x:c r="H11" s="2"/>
@@ -4406,7 +4003,7 @@
     </x:row>
     <x:row r="16" ht="39.75" customHeight="1">
       <x:c r="B16" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G16" s="2"/>
       <x:c r="H16" s="2"/>
@@ -5434,358 +5031,373 @@
     <x:col min="3" max="3" width="33" customWidth="1"/>
     <x:col min="4" max="4" width="68" customWidth="1"/>
     <x:col min="5" max="5" width="27" customWidth="1"/>
-    <x:col min="6" max="6" width="76" customWidth="1"/>
+    <x:col min="6" max="6" width="92" hidden="0" customWidth="1"/>
     <x:col min="7" max="26" width="8.630000114440918" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="38" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B1" s="38" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B1" s="38" t="s">
+      <x:c r="C1" s="38" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="C1" s="38" t="s">
+      <x:c r="D1" s="38" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D1" s="38" t="s">
+      <x:c r="E1" s="38" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="E1" s="38" t="s">
+      <x:c r="F1" s="38" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="F1" s="38" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="G1" s="2"/>
       <x:c r="H1" s="2"/>
     </x:row>
-    <x:row r="2" ht="73.5" customHeight="1">
+    <x:row r="2" ht="90" customHeight="1">
       <x:c r="A2" s="35" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B2" s="35" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C2" s="35" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D2" s="35" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D2" s="35" t="s">
+      <x:c r="E2" s="35" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="E2" s="35" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F2" s="35" t="s">
-        <x:v>65</x:v>
+      <x:c r="F2" s="35" t="str">
+        <x:v>TD_PIM_EMP_01
+PIM_EMP_Create_01, PIM_EMP_Create_02, PIM_EMP_CancelCreate_01</x:v>
       </x:c>
       <x:c r="G2" s="2"/>
       <x:c r="H2" s="2"/>
     </x:row>
-    <x:row r="3" ht="138" customHeight="1">
+    <x:row r="3" ht="90" customHeight="1">
       <x:c r="A3" s="35" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B3" s="35" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C3" s="35" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D3" s="35" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E3" s="35" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D3" s="35" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E3" s="35" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F3" s="35" t="s">
-        <x:v>69</x:v>
+      <x:c r="F3" s="35" t="str">
+        <x:v>TD_PIM_EMP_02
+PIM_EMP_Create_03, PIM_EMP_Create_04, PIM_EMP_Create_05, PIM_EMP_Create_06, PIM_EMP_Create_07, PIM_EMP_Create_08, PIM_EMP_Create_09, PIM_EMP_Create_10, PIM_EMP_Create_11</x:v>
       </x:c>
       <x:c r="G3" s="2"/>
       <x:c r="H3" s="2"/>
     </x:row>
-    <x:row r="4" ht="73.5" customHeight="1">
+    <x:row r="4" ht="90" customHeight="1">
       <x:c r="A4" s="35" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B4" s="35" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C4" s="35" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D4" s="35" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E4" s="35" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="F4" s="35" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F4" s="35" t="str">
+        <x:v>TD_PIM_EMP_03
+PIM_EMP_Create_12, PIM_EMP_Create_13, PIM_EMP_Create_14</x:v>
       </x:c>
       <x:c r="G4" s="2"/>
       <x:c r="H4" s="2"/>
     </x:row>
-    <x:row r="5" ht="78" customHeight="1">
+    <x:row r="5" ht="90" customHeight="1">
       <x:c r="A5" s="35" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B5" s="35" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C5" s="35" t="s">
-        <x:v>74</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D5" s="35" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E5" s="35" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F5" s="35" t="s">
-        <x:v>76</x:v>
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F5" s="35" t="str">
+        <x:v>TD_PIM_EMP_04
+PIM_EMP_UploadPhoto_01, PIM_EMP_UploadPhoto_02, PIM_EMP_UploadPhoto_03, PIM_EMP_UploadPhoto_04</x:v>
       </x:c>
       <x:c r="G5" s="2"/>
       <x:c r="H5" s="2"/>
     </x:row>
-    <x:row r="6" ht="102" customHeight="1">
+    <x:row r="6" ht="90" customHeight="1">
       <x:c r="A6" s="35" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B6" s="35" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C6" s="35" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D6" s="35" t="s">
-        <x:v>78</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E6" s="35" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F6" s="35" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F6" s="35" t="str">
+        <x:v>TD_PIM_EMP_05
+PIM_EMP_Search_01, PIM_EMP_Search_02, PIM_EMP_Search_03, PIM_EMP_Filter_01, PIM_EMP_Reset_01, PIM_EMP_Sort_01</x:v>
       </x:c>
       <x:c r="G6" s="2"/>
       <x:c r="H6" s="2"/>
     </x:row>
-    <x:row r="7" ht="78" customHeight="1">
+    <x:row r="7" ht="90" customHeight="1">
       <x:c r="A7" s="35" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B7" s="35" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C7" s="35" t="s">
-        <x:v>81</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D7" s="35" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E7" s="35" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F7" s="35" t="s">
-        <x:v>83</x:v>
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F7" s="35" t="str">
+        <x:v>TD_PIM_PERSONAL_01
+PIM_PERSONAL_Update_01, PIM_PERSONAL_Update_18, PIM_PERSONAL_Update_19, PIM_PERSONAL_Update_20</x:v>
       </x:c>
       <x:c r="G7" s="2"/>
       <x:c r="H7" s="2"/>
     </x:row>
-    <x:row r="8" ht="102" customHeight="1">
+    <x:row r="8" ht="90" customHeight="1">
       <x:c r="A8" s="35" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B8" s="35" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C8" s="35" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D8" s="35" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E8" s="35" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D8" s="35" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="E8" s="35" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F8" s="35" t="s">
-        <x:v>85</x:v>
+      <x:c r="F8" s="35" t="str">
+        <x:v>TD_PIM_PERSONAL_02
+PIM_PERSONAL_Update_02, PIM_PERSONAL_Update_03, PIM_PERSONAL_Update_04, PIM_PERSONAL_Update_05, PIM_PERSONAL_Update_06, PIM_PERSONAL_Update_07</x:v>
       </x:c>
       <x:c r="G8" s="2"/>
       <x:c r="H8" s="2"/>
     </x:row>
-    <x:row r="9" ht="102" customHeight="1">
+    <x:row r="9" ht="90" customHeight="1">
       <x:c r="A9" s="35" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B9" s="35" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C9" s="35" t="s">
-        <x:v>86</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D9" s="35" t="s">
-        <x:v>87</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E9" s="35" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="F9" s="35" t="s">
-        <x:v>89</x:v>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F9" s="35" t="str">
+        <x:v>TD_PIM_PERSONAL_03
+PIM_PERSONAL_Update_08, PIM_PERSONAL_Update_09, PIM_PERSONAL_Update_10, PIM_PERSONAL_Update_11, PIM_PERSONAL_Update_12, PIM_PERSONAL_Update_13</x:v>
       </x:c>
       <x:c r="G9" s="2"/>
       <x:c r="H9" s="2"/>
     </x:row>
-    <x:row r="10" ht="78" customHeight="1">
+    <x:row r="10" ht="90" customHeight="1">
       <x:c r="A10" s="35" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B10" s="35" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C10" s="35" t="s">
-        <x:v>90</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D10" s="35" t="s">
-        <x:v>91</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E10" s="35" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F10" s="35" t="s">
-        <x:v>92</x:v>
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F10" s="35" t="str">
+        <x:v>TD_PIM_PERSONAL_04
+PIM_PERSONAL_Update_14, PIM_PERSONAL_Update_15, PIM_PERSONAL_Update_16, PIM_PERSONAL_Update_17</x:v>
       </x:c>
       <x:c r="G10" s="2"/>
       <x:c r="H10" s="2"/>
     </x:row>
     <x:row r="11" ht="90" customHeight="1">
       <x:c r="A11" s="35" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B11" s="35" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C11" s="35" t="s">
-        <x:v>93</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D11" s="35" t="s">
-        <x:v>94</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E11" s="35" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="F11" s="35" t="s">
-        <x:v>96</x:v>
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F11" s="35" t="str">
+        <x:v>TD_PIM_PERSONAL_05
+PIM_PERSONAL_CreateAttachment_01, PIM_PERSONAL_CreateAttachment_02, PIM_PERSONAL_CreateAttachment_03, PIM_PERSONAL_CreateAttachment_04, PIM_PERSONAL_DeleteAttachment_01</x:v>
       </x:c>
       <x:c r="G11" s="2"/>
       <x:c r="H11" s="2"/>
     </x:row>
-    <x:row r="12" ht="73.5" customHeight="1">
+    <x:row r="12" ht="90" customHeight="1">
       <x:c r="A12" s="35" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B12" s="35" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C12" s="35" t="s">
-        <x:v>97</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D12" s="35" t="s">
-        <x:v>98</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E12" s="35" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F12" s="35" t="s">
-        <x:v>99</x:v>
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F12" s="35" t="str">
+        <x:v>TD_PIM_JOB_01
+PIM_JOB_UpdateJob_01, PIM_JOB_UpdateJob_02, PIM_JOB_UpdateJob_09</x:v>
       </x:c>
       <x:c r="G12" s="2"/>
       <x:c r="H12" s="2"/>
     </x:row>
-    <x:row r="13" ht="102" customHeight="1">
+    <x:row r="13" ht="90" customHeight="1">
       <x:c r="A13" s="35" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B13" s="35" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C13" s="35" t="s">
-        <x:v>100</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D13" s="35" t="s">
-        <x:v>101</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E13" s="35" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F13" s="35" t="s">
-        <x:v>103</x:v>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F13" s="35" t="str">
+        <x:v>TD_PIM_JOB_02
+PIM_JOB_UpdateJob_03, PIM_JOB_UpdateJob_04, PIM_JOB_UpdateJob_05, PIM_JOB_UpdateJob_06, PIM_JOB_UpdateJob_07, PIM_JOB_UpdateJob_08</x:v>
       </x:c>
       <x:c r="G13" s="2"/>
       <x:c r="H13" s="2"/>
     </x:row>
-    <x:row r="14" ht="73.5" customHeight="1">
+    <x:row r="14" ht="90" customHeight="1">
       <x:c r="A14" s="35" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B14" s="35" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C14" s="35" t="s">
-        <x:v>104</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D14" s="35" t="s">
-        <x:v>105</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E14" s="35" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="F14" s="35" t="s">
-        <x:v>107</x:v>
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F14" s="35" t="str">
+        <x:v>TD_PIM_JOB_03
+PIM_JOB_ToggleContract_01, PIM_JOB_ToggleContract_02</x:v>
       </x:c>
       <x:c r="G14" s="2"/>
       <x:c r="H14" s="2"/>
     </x:row>
     <x:row r="15" ht="90" customHeight="1">
       <x:c r="A15" s="35" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B15" s="35" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C15" s="35" t="s">
-        <x:v>108</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D15" s="35" t="s">
-        <x:v>109</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E15" s="35" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="F15" s="35" t="s">
-        <x:v>111</x:v>
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F15" s="35" t="str">
+        <x:v>TD_PIM_JOB_04
+PIM_JOB_UpdateContract_01, PIM_JOB_UpdateContract_02, PIM_JOB_UpdateContract_03, PIM_JOB_UpdateContract_04, PIM_JOB_UpdateContract_05</x:v>
       </x:c>
       <x:c r="G15" s="2"/>
       <x:c r="H15" s="2"/>
     </x:row>
-    <x:row r="16" ht="138" customHeight="1">
+    <x:row r="16" ht="90" customHeight="1">
       <x:c r="A16" s="35" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B16" s="35" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C16" s="35" t="s">
-        <x:v>112</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D16" s="35" t="s">
-        <x:v>113</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E16" s="35" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="F16" s="35" t="s">
-        <x:v>115</x:v>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F16" s="35" t="str">
+        <x:v>TD_PIM_JOB_05
+PIM_JOB_UploadContract_01, PIM_JOB_UploadContract_02, PIM_JOB_UploadContract_03, PIM_JOB_KeepContract_01, PIM_JOB_ReplaceContract_01, PIM_JOB_ReplaceContract_02, PIM_JOB_DeleteContract_01, PIM_JOB_CreateAttachment_01, PIM_JOB_CancelAttachment_01</x:v>
       </x:c>
       <x:c r="G16" s="2"/>
       <x:c r="H16" s="2"/>
@@ -6792,14 +6404,14 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultColWidth="12.630000114440918" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="25" customWidth="1"/>
+    <x:col min="1" max="1" width="37" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="36" customWidth="1"/>
     <x:col min="3" max="3" width="72" customWidth="1"/>
     <x:col min="4" max="4" width="65" customWidth="1"/>
     <x:col min="5" max="5" width="24" customWidth="1"/>
     <x:col min="6" max="6" width="14" customWidth="1"/>
     <x:col min="7" max="7" width="15" customWidth="1"/>
-    <x:col min="8" max="8" width="40" customWidth="1"/>
+    <x:col min="8" max="8" width="65" hidden="0" customWidth="1"/>
     <x:col min="9" max="26" width="8.630000114440918" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -6815,10 +6427,10 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="34" t="s">
-        <x:v>116</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B2" s="35" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C2" s="39"/>
       <x:c r="D2" s="39"/>
@@ -6829,10 +6441,10 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="34" t="s">
-        <x:v>117</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B3" s="35" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C3" s="39"/>
       <x:c r="D3" s="39"/>
@@ -6843,10 +6455,10 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="34" t="s">
-        <x:v>118</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B4" s="35" t="s">
-        <x:v>119</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C4" s="39"/>
       <x:c r="D4" s="39"/>
@@ -6857,22 +6469,22 @@
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="40" t="s">
-        <x:v>120</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B5" s="40" t="s">
-        <x:v>121</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C5" s="40" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D5" s="40" t="s">
-        <x:v>123</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E5" s="40" t="s">
-        <x:v>124</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F5" s="40" t="s">
-        <x:v>125</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G5" s="36"/>
       <x:c r="H5" s="36"/>
@@ -6880,7 +6492,7 @@
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="41" t="n">
         <x:f>COUNTIF($F$9:$F$33,"Passed")</x:f>
-        <x:v>0</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="41" t="n">
         <x:f>COUNTIF($F$9:$F$33,"Failed")</x:f>
@@ -6888,11 +6500,11 @@
       </x:c>
       <x:c r="C6" s="41" t="n">
         <x:f>COUNTIF($F$9:$F$33,"Untested")</x:f>
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="41" t="n">
         <x:f>COUNTIF($F$9:$F$33,"Blocked")</x:f>
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E6" s="41" t="n">
         <x:f>COUNTIF($F$9:$F$33,"Skipped")</x:f>
@@ -6917,36 +6529,36 @@
     </x:row>
     <x:row r="8" ht="33.75" customHeight="1">
       <x:c r="A8" s="38" t="s">
-        <x:v>126</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B8" s="38" t="s">
-        <x:v>127</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C8" s="38" t="s">
-        <x:v>128</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D8" s="38" t="s">
-        <x:v>129</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E8" s="38" t="s">
-        <x:v>130</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F8" s="38" t="s">
-        <x:v>131</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G8" s="38" t="s">
-        <x:v>132</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H8" s="38" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="170" customHeight="1">
-      <x:c r="A9" s="42" t="s">
-        <x:v>133</x:v>
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="210" customHeight="1">
+      <x:c r="A9" s="42" t="str">
+        <x:v>PIM_EMP_Create_01</x:v>
       </x:c>
       <x:c r="B9" s="42" t="s">
-        <x:v>134</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C9" s="42" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM. Create Login Details tắt. Employee Id dùng cho hồ sơ mới chưa tồn tại.
@@ -6958,25 +6570,34 @@
 Dọn dẹp: bỏ thay đổi chưa lưu. Nếu tạo thành công, chỉ xóa nhân viên của case này sau khi giữ bằng chứng; không xóa fixture dùng chung.</x:v>
       </x:c>
       <x:c r="D9" s="42" t="s">
-        <x:v>135</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E9" s="42" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F9" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G9" s="44"/>
-      <x:c r="H9" s="42" t="s">
-        <x:v>136</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="170" customHeight="1">
-      <x:c r="A10" s="45" t="s">
-        <x:v>137</x:v>
+      <x:c r="F9" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G9" s="44" t="d">
+        <x:v>2026-10-21T10:21:18.859Z</x:v>
+      </x:c>
+      <x:c r="H9" s="42" t="str">
+        <x:v>TD_PIM_EMP_01
+Positive; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 155.0.4283.62
+Actual: Save và reload: First/Middle/Last/Employee Id khớp chính xác input | Employee List trả đúng 1 dòng | Đúng ID và tên nhân viên vừa tạo
+Duration: 13.72s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_Create_01.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="210" customHeight="1">
+      <x:c r="A10" s="45" t="str">
+        <x:v>PIM_EMP_Create_02</x:v>
       </x:c>
       <x:c r="B10" s="45" t="s">
-        <x:v>138</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C10" s="45" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM. Create Login Details tắt. Employee Id dùng cho hồ sơ mới chưa tồn tại.
@@ -6987,25 +6608,34 @@
 Dọn dẹp: bỏ thay đổi chưa lưu. Nếu tạo thành công, chỉ xóa nhân viên của case này sau khi giữ bằng chứng; không xóa fixture dùng chung.</x:v>
       </x:c>
       <x:c r="D10" s="45" t="s">
-        <x:v>139</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E10" s="45" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F10" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G10" s="44"/>
-      <x:c r="H10" s="42" t="s">
-        <x:v>136</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="170" customHeight="1">
-      <x:c r="A11" s="42" t="s">
-        <x:v>140</x:v>
+      <x:c r="F10" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G10" s="44" t="d">
+        <x:v>2026-10-21T10:21:30.871Z</x:v>
+      </x:c>
+      <x:c r="H10" s="42" t="str">
+        <x:v>TD_PIM_EMP_01
+Positive; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 155.0.4283.62
+Actual: Save và reload: First/Middle/Last/Employee Id khớp chính xác input
+Duration: 12.01s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_Create_02.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="210" customHeight="1">
+      <x:c r="A11" s="42" t="str">
+        <x:v>PIM_EMP_Create_03</x:v>
       </x:c>
       <x:c r="B11" s="42" t="s">
-        <x:v>141</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C11" s="42" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM. Create Login Details tắt. Employee Id dùng cho hồ sơ mới chưa tồn tại.
@@ -7016,25 +6646,34 @@
 Dọn dẹp: bỏ thay đổi chưa lưu. Nếu tạo thành công, chỉ xóa nhân viên của case này sau khi giữ bằng chứng; không xóa fixture dùng chung.</x:v>
       </x:c>
       <x:c r="D11" s="42" t="s">
-        <x:v>142</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E11" s="42" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F11" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G11" s="44"/>
-      <x:c r="H11" s="42" t="s">
-        <x:v>143</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="170" customHeight="1">
-      <x:c r="A12" s="45" t="s">
-        <x:v>144</x:v>
+      <x:c r="F11" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G11" s="44" t="d">
+        <x:v>2026-10-21T10:21:37.719Z</x:v>
+      </x:c>
+      <x:c r="H11" s="42" t="str">
+        <x:v>TD_PIM_EMP_02
+Negative; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 155.0.4283.62
+Actual: Lỗi đúng trường: Required | Không chuyển sang hồ sơ mới | Search xác nhận không có hồ sơ mang ID input sai
+Duration: 6.85s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_Create_03.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="210" customHeight="1">
+      <x:c r="A12" s="45" t="str">
+        <x:v>PIM_EMP_Create_04</x:v>
       </x:c>
       <x:c r="B12" s="45" t="s">
-        <x:v>145</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C12" s="45" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM. Create Login Details tắt. Employee Id dùng cho hồ sơ mới chưa tồn tại.
@@ -7045,25 +6684,34 @@
 Dọn dẹp: bỏ thay đổi chưa lưu. Nếu tạo thành công, chỉ xóa nhân viên của case này sau khi giữ bằng chứng; không xóa fixture dùng chung.</x:v>
       </x:c>
       <x:c r="D12" s="45" t="s">
-        <x:v>146</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E12" s="45" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F12" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G12" s="44"/>
-      <x:c r="H12" s="42" t="s">
-        <x:v>143</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="170" customHeight="1">
-      <x:c r="A13" s="42" t="s">
-        <x:v>147</x:v>
+      <x:c r="F12" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G12" s="44" t="d">
+        <x:v>2026-10-21T10:21:44.471Z</x:v>
+      </x:c>
+      <x:c r="H12" s="42" t="str">
+        <x:v>TD_PIM_EMP_02
+Negative; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 155.0.4283.62
+Actual: Lỗi đúng trường: Required | Không chuyển sang hồ sơ mới | Search xác nhận không có hồ sơ mang ID input sai
+Duration: 6.75s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_Create_04.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="210" customHeight="1">
+      <x:c r="A13" s="42" t="str">
+        <x:v>PIM_EMP_Create_05</x:v>
       </x:c>
       <x:c r="B13" s="42" t="s">
-        <x:v>148</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C13" s="42" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM. Create Login Details tắt. Employee Id dùng cho hồ sơ mới chưa tồn tại.
@@ -7074,25 +6722,34 @@
 Dọn dẹp: bỏ thay đổi chưa lưu. Nếu tạo thành công, chỉ xóa nhân viên của case này sau khi giữ bằng chứng; không xóa fixture dùng chung.</x:v>
       </x:c>
       <x:c r="D13" s="42" t="s">
-        <x:v>149</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E13" s="42" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F13" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G13" s="44"/>
-      <x:c r="H13" s="42" t="s">
-        <x:v>143</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="174" customHeight="1">
-      <x:c r="A14" s="45" t="s">
-        <x:v>150</x:v>
+      <x:c r="F13" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G13" s="44" t="d">
+        <x:v>2026-10-21T10:21:50.105Z</x:v>
+      </x:c>
+      <x:c r="H13" s="42" t="str">
+        <x:v>TD_PIM_EMP_02
+Negative; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 155.0.4283.62
+Actual: Lỗi đúng trường: Required | Không chuyển sang hồ sơ mới | Search xác nhận không có hồ sơ mang ID input sai
+Duration: 5.63s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_Create_05.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="210" customHeight="1">
+      <x:c r="A14" s="45" t="str">
+        <x:v>PIM_EMP_Create_06</x:v>
       </x:c>
       <x:c r="B14" s="45" t="s">
-        <x:v>151</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C14" s="45" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM. Create Login Details tắt. Employee Id dùng cho hồ sơ mới chưa tồn tại.
@@ -7103,25 +6760,34 @@
 Dọn dẹp: bỏ thay đổi chưa lưu. Nếu tạo thành công, chỉ xóa nhân viên của case này sau khi giữ bằng chứng; không xóa fixture dùng chung.</x:v>
       </x:c>
       <x:c r="D14" s="45" t="s">
-        <x:v>152</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E14" s="45" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F14" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G14" s="44"/>
-      <x:c r="H14" s="42" t="s">
-        <x:v>153</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="188" customHeight="1">
-      <x:c r="A15" s="42" t="s">
-        <x:v>154</x:v>
+      <x:c r="F14" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G14" s="44" t="d">
+        <x:v>2026-10-21T10:22:01.724Z</x:v>
+      </x:c>
+      <x:c r="H14" s="42" t="str">
+        <x:v>TD_PIM_EMP_02
+Positive; Phân tích giá trị biên
+Automation: P1
+Playwright / Edge 155.0.4283.62
+Actual: Save và reload: First/Middle/Last/Employee Id khớp chính xác input
+Duration: 11.62s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_Create_06.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="210" customHeight="1">
+      <x:c r="A15" s="42" t="str">
+        <x:v>PIM_EMP_Create_07</x:v>
       </x:c>
       <x:c r="B15" s="42" t="s">
-        <x:v>155</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C15" s="42" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM. Create Login Details tắt. Employee Id dùng cho hồ sơ mới chưa tồn tại.
@@ -7132,25 +6798,34 @@
 Dọn dẹp: bỏ thay đổi chưa lưu. Nếu tạo thành công, chỉ xóa nhân viên của case này sau khi giữ bằng chứng; không xóa fixture dùng chung.</x:v>
       </x:c>
       <x:c r="D15" s="42" t="s">
-        <x:v>156</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E15" s="42" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F15" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G15" s="44"/>
-      <x:c r="H15" s="42" t="s">
-        <x:v>157</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="174" customHeight="1">
-      <x:c r="A16" s="45" t="s">
-        <x:v>158</x:v>
+      <x:c r="F15" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G15" s="44" t="d">
+        <x:v>2026-10-21T10:22:07.545Z</x:v>
+      </x:c>
+      <x:c r="H15" s="42" t="str">
+        <x:v>TD_PIM_EMP_02
+Negative; Phân tích giá trị biên
+Automation: P1
+Playwright / Edge 155.0.4283.62
+Actual: Lỗi đúng trường: Should not exceed 30 characters | Không chuyển sang hồ sơ mới | Search xác nhận không có hồ sơ mang ID input sai
+Duration: 5.82s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_Create_07.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="210" customHeight="1">
+      <x:c r="A16" s="45" t="str">
+        <x:v>PIM_EMP_Create_08</x:v>
       </x:c>
       <x:c r="B16" s="45" t="s">
-        <x:v>159</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C16" s="45" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM. Create Login Details tắt. Employee Id dùng cho hồ sơ mới chưa tồn tại.
@@ -7161,25 +6836,34 @@
 Dọn dẹp: bỏ thay đổi chưa lưu. Nếu tạo thành công, chỉ xóa nhân viên của case này sau khi giữ bằng chứng; không xóa fixture dùng chung.</x:v>
       </x:c>
       <x:c r="D16" s="45" t="s">
-        <x:v>160</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E16" s="45" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F16" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G16" s="44"/>
-      <x:c r="H16" s="42" t="s">
-        <x:v>153</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="188" customHeight="1">
-      <x:c r="A17" s="42" t="s">
-        <x:v>161</x:v>
+      <x:c r="F16" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G16" s="44" t="d">
+        <x:v>2026-10-21T10:22:21.527Z</x:v>
+      </x:c>
+      <x:c r="H16" s="42" t="str">
+        <x:v>TD_PIM_EMP_02
+Positive; Phân tích giá trị biên
+Automation: P1
+Playwright / Edge 155.0.4283.62
+Actual: Save và reload: First/Middle/Last/Employee Id khớp chính xác input
+Duration: 13.98s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_Create_08.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="210" customHeight="1">
+      <x:c r="A17" s="42" t="str">
+        <x:v>PIM_EMP_Create_09</x:v>
       </x:c>
       <x:c r="B17" s="42" t="s">
-        <x:v>162</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C17" s="42" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM. Create Login Details tắt. Employee Id dùng cho hồ sơ mới chưa tồn tại.
@@ -7190,25 +6874,34 @@
 Dọn dẹp: bỏ thay đổi chưa lưu. Nếu tạo thành công, chỉ xóa nhân viên của case này sau khi giữ bằng chứng; không xóa fixture dùng chung.</x:v>
       </x:c>
       <x:c r="D17" s="42" t="s">
-        <x:v>163</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E17" s="42" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F17" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G17" s="44"/>
-      <x:c r="H17" s="42" t="s">
-        <x:v>157</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="174" customHeight="1">
-      <x:c r="A18" s="45" t="s">
-        <x:v>164</x:v>
+      <x:c r="F17" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G17" s="44" t="d">
+        <x:v>2026-10-21T10:22:27.124Z</x:v>
+      </x:c>
+      <x:c r="H17" s="42" t="str">
+        <x:v>TD_PIM_EMP_02
+Negative; Phân tích giá trị biên
+Automation: P1
+Playwright / Edge 155.0.4283.62
+Actual: Lỗi đúng trường: Should not exceed 30 characters | Không chuyển sang hồ sơ mới | Search xác nhận không có hồ sơ mang ID input sai
+Duration: 5.59s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_Create_09.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="210" customHeight="1">
+      <x:c r="A18" s="45" t="str">
+        <x:v>PIM_EMP_Create_10</x:v>
       </x:c>
       <x:c r="B18" s="45" t="s">
-        <x:v>165</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C18" s="45" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM. Create Login Details tắt. Employee Id dùng cho hồ sơ mới chưa tồn tại.
@@ -7219,25 +6912,34 @@
 Dọn dẹp: bỏ thay đổi chưa lưu. Nếu tạo thành công, chỉ xóa nhân viên của case này sau khi giữ bằng chứng; không xóa fixture dùng chung.</x:v>
       </x:c>
       <x:c r="D18" s="45" t="s">
-        <x:v>166</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E18" s="45" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F18" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G18" s="44"/>
-      <x:c r="H18" s="42" t="s">
-        <x:v>153</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="188" customHeight="1">
-      <x:c r="A19" s="42" t="s">
-        <x:v>167</x:v>
+      <x:c r="F18" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G18" s="44" t="d">
+        <x:v>2026-10-21T10:22:39.152Z</x:v>
+      </x:c>
+      <x:c r="H18" s="42" t="str">
+        <x:v>TD_PIM_EMP_02
+Positive; Phân tích giá trị biên
+Automation: P1
+Playwright / Edge 155.0.4283.62
+Actual: Save và reload: First/Middle/Last/Employee Id khớp chính xác input
+Duration: 12.03s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_Create_10.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="210" customHeight="1">
+      <x:c r="A19" s="42" t="str">
+        <x:v>PIM_EMP_Create_11</x:v>
       </x:c>
       <x:c r="B19" s="42" t="s">
-        <x:v>168</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C19" s="42" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM. Create Login Details tắt. Employee Id dùng cho hồ sơ mới chưa tồn tại.
@@ -7248,25 +6950,34 @@
 Dọn dẹp: bỏ thay đổi chưa lưu. Nếu tạo thành công, chỉ xóa nhân viên của case này sau khi giữ bằng chứng; không xóa fixture dùng chung.</x:v>
       </x:c>
       <x:c r="D19" s="42" t="s">
-        <x:v>169</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="E19" s="42" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F19" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G19" s="44"/>
-      <x:c r="H19" s="42" t="s">
-        <x:v>157</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="170" customHeight="1">
-      <x:c r="A20" s="45" t="s">
-        <x:v>170</x:v>
+      <x:c r="F19" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G19" s="44" t="d">
+        <x:v>2026-10-21T10:22:47.199Z</x:v>
+      </x:c>
+      <x:c r="H19" s="42" t="str">
+        <x:v>TD_PIM_EMP_02
+Negative; Phân tích giá trị biên
+Automation: P1
+Playwright / Edge 155.0.4283.62
+Actual: Lỗi đúng trường: Should not exceed 30 characters | Không chuyển sang hồ sơ mới | Search xác nhận không có hồ sơ mang ID input sai
+Duration: 8.05s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_Create_11.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="210" customHeight="1">
+      <x:c r="A20" s="45" t="str">
+        <x:v>PIM_EMP_Create_12</x:v>
       </x:c>
       <x:c r="B20" s="45" t="s">
-        <x:v>171</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C20" s="45" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM. Create Login Details tắt. Employee Id dùng cho hồ sơ mới chưa tồn tại.
@@ -7277,25 +6988,34 @@
 Dọn dẹp: bỏ thay đổi chưa lưu. Nếu tạo thành công, chỉ xóa nhân viên của case này sau khi giữ bằng chứng; không xóa fixture dùng chung.</x:v>
       </x:c>
       <x:c r="D20" s="45" t="s">
-        <x:v>172</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E20" s="45" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F20" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G20" s="44"/>
-      <x:c r="H20" s="42" t="s">
-        <x:v>173</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="170" customHeight="1">
-      <x:c r="A21" s="42" t="s">
-        <x:v>174</x:v>
+      <x:c r="F20" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G20" s="44" t="d">
+        <x:v>2026-10-21T10:23:02.056Z</x:v>
+      </x:c>
+      <x:c r="H20" s="42" t="str">
+        <x:v>TD_PIM_EMP_03
+Positive; Phân tích giá trị biên
+Automation: P1
+Playwright / Edge 155.0.4283.62
+Actual: Save và reload: First/Middle/Last/Employee Id khớp chính xác input
+Duration: 14.86s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_Create_12.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="210" customHeight="1">
+      <x:c r="A21" s="42" t="str">
+        <x:v>PIM_EMP_Create_13</x:v>
       </x:c>
       <x:c r="B21" s="42" t="s">
-        <x:v>175</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C21" s="42" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM. Create Login Details tắt. Employee Id dùng cho hồ sơ mới chưa tồn tại.
@@ -7306,54 +7026,72 @@
 Dọn dẹp: bỏ thay đổi chưa lưu. Nếu tạo thành công, chỉ xóa nhân viên của case này sau khi giữ bằng chứng; không xóa fixture dùng chung.</x:v>
       </x:c>
       <x:c r="D21" s="42" t="s">
-        <x:v>176</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E21" s="42" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F21" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G21" s="44"/>
-      <x:c r="H21" s="42" t="s">
-        <x:v>177</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="170" customHeight="1">
-      <x:c r="A22" s="45" t="s">
-        <x:v>178</x:v>
+      <x:c r="F21" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G21" s="44" t="d">
+        <x:v>2026-10-21T10:23:09.767Z</x:v>
+      </x:c>
+      <x:c r="H21" s="42" t="str">
+        <x:v>TD_PIM_EMP_03
+Negative; Phân tích giá trị biên
+Automation: P1
+Playwright / Edge 155.0.4283.62
+Actual: Lỗi đúng trường: Should not exceed 10 characters | Không chuyển sang hồ sơ mới | Search xác nhận không có hồ sơ mang ID input sai; ID 11 ký tự đã bị chặn tại form
+Duration: 7.71s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_Create_13.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="210" customHeight="1">
+      <x:c r="A22" s="45" t="str">
+        <x:v>PIM_EMP_Create_14</x:v>
       </x:c>
       <x:c r="B22" s="45" t="s">
-        <x:v>179</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C22" s="45" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM. Create Login Details tắt. F_DUP (G1N01D0001) đã tạo trong setup.
-Input: ID=G1N01D0001 của F_DUP; First=G01N01; Last=NhutDuplicateAttemptAttempt
+Input: ID=G1N01D0001 của F_DUP; First=G01N01; Last=NhutDuplicateAttempt
 1. Xác nhận F_DUP đã tồn tại.
 2. Mở Add Employee, nhập ID trùng và tên khác.
 3. Rời ô ID để kích hoạt kiểm tra, rồi Save.
 Dọn dẹp: bỏ thay đổi chưa lưu. Nếu tạo thành công, chỉ xóa nhân viên của case này sau khi giữ bằng chứng; không xóa fixture dùng chung.</x:v>
       </x:c>
       <x:c r="D22" s="45" t="s">
-        <x:v>180</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="E22" s="45" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F22" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G22" s="44"/>
-      <x:c r="H22" s="42" t="s">
-        <x:v>181</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="170" customHeight="1">
-      <x:c r="A23" s="42" t="s">
-        <x:v>182</x:v>
+      <x:c r="F22" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G22" s="44" t="d">
+        <x:v>2026-10-21T10:23:14.758Z</x:v>
+      </x:c>
+      <x:c r="H22" s="42" t="str">
+        <x:v>TD_PIM_EMP_03
+Negative; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 155.0.4283.62
+Actual: Lỗi đúng trường: Employee Id already exists | Không chuyển sang hồ sơ mới | Chỉ còn một dòng F_DUP sau khi thử ID trùng | F_DUP không bị thay bằng tên nhập thử
+Duration: 4.99s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_Create_14.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="210" customHeight="1">
+      <x:c r="A23" s="42" t="str">
+        <x:v>PIM_EMP_CancelCreate_01</x:v>
       </x:c>
       <x:c r="B23" s="42" t="s">
-        <x:v>183</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C23" s="42" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM. Create Login Details tắt. Employee Id dùng cho hồ sơ mới chưa tồn tại.
@@ -7364,25 +7102,34 @@
 Dọn dẹp: bỏ thay đổi chưa lưu. Nếu tạo thành công, chỉ xóa nhân viên của case này sau khi giữ bằng chứng; không xóa fixture dùng chung.</x:v>
       </x:c>
       <x:c r="D23" s="42" t="s">
-        <x:v>184</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E23" s="42" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F23" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G23" s="44"/>
-      <x:c r="H23" s="42" t="s">
-        <x:v>136</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="174" customHeight="1">
-      <x:c r="A24" s="45" t="s">
-        <x:v>185</x:v>
+      <x:c r="F23" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G23" s="44" t="d">
+        <x:v>2026-10-21T10:23:20.884Z</x:v>
+      </x:c>
+      <x:c r="H23" s="42" t="str">
+        <x:v>TD_PIM_EMP_01
+Positive; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 155.0.4283.62
+Actual: Cancel quay về Employee List | Không có hồ sơ với ID vừa hủy
+Duration: 6.13s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_CancelCreate_01.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="210" customHeight="1">
+      <x:c r="A24" s="45" t="str">
+        <x:v>PIM_EMP_UploadPhoto_01</x:v>
       </x:c>
       <x:c r="B24" s="45" t="s">
-        <x:v>186</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C24" s="45" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM. Create Login Details tắt. Employee Id dùng cho hồ sơ mới chưa tồn tại. Tệp thử đúng định dạng/dung lượng trong Test Data đã chuẩn bị.
@@ -7393,25 +7140,35 @@
 Dọn dẹp: bỏ thay đổi chưa lưu. Nếu tạo thành công, chỉ xóa nhân viên của case này sau khi giữ bằng chứng; không xóa fixture dùng chung.</x:v>
       </x:c>
       <x:c r="D24" s="45" t="s">
-        <x:v>187</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E24" s="45" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F24" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G24" s="44"/>
-      <x:c r="H24" s="42" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="174" customHeight="1">
-      <x:c r="A25" s="42" t="s">
-        <x:v>189</x:v>
+      <x:c r="F24" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G24" s="44" t="d">
+        <x:v>2026-10-21T10:23:36.586Z</x:v>
+      </x:c>
+      <x:c r="H24" s="42" t="str">
+        <x:v>TD_PIM_EMP_04
+Positive; Phân vùng tương đương
+Automation: P2
+File upload: xác nhận bằng UI và mở lại hồ sơ.
+Playwright / Edge 155.0.4283.62
+Actual: Save và reload: First/Middle/Last/Employee Id khớp chính xác input | Ảnh profile được lưu: /web/index.php/pim/viewPhoto/empNumber/207 | Ảnh profile tải được sau reload
+Duration: 15.70s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_UploadPhoto_01.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="210" customHeight="1">
+      <x:c r="A25" s="42" t="str">
+        <x:v>PIM_EMP_UploadPhoto_02</x:v>
       </x:c>
       <x:c r="B25" s="42" t="s">
-        <x:v>190</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C25" s="42" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM. Create Login Details tắt. Employee Id dùng cho hồ sơ mới chưa tồn tại. Tệp thử đúng định dạng/dung lượng trong Test Data đã chuẩn bị.
@@ -7422,25 +7179,35 @@
 Dọn dẹp: bỏ thay đổi chưa lưu. Nếu tạo thành công, chỉ xóa nhân viên của case này sau khi giữ bằng chứng; không xóa fixture dùng chung.</x:v>
       </x:c>
       <x:c r="D25" s="42" t="s">
-        <x:v>187</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E25" s="42" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F25" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G25" s="44"/>
-      <x:c r="H25" s="42" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="174" customHeight="1">
-      <x:c r="A26" s="45" t="s">
-        <x:v>191</x:v>
+      <x:c r="F25" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G25" s="44" t="d">
+        <x:v>2026-10-21T10:23:49.270Z</x:v>
+      </x:c>
+      <x:c r="H25" s="42" t="str">
+        <x:v>TD_PIM_EMP_04
+Positive; Phân vùng tương đương
+Automation: P2
+File upload: xác nhận bằng UI và mở lại hồ sơ.
+Playwright / Edge 155.0.4283.62
+Actual: Save và reload: First/Middle/Last/Employee Id khớp chính xác input | Ảnh profile được lưu: /web/index.php/pim/viewPhoto/empNumber/208 | Ảnh profile tải được sau reload
+Duration: 12.68s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_UploadPhoto_02.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="210" customHeight="1">
+      <x:c r="A26" s="45" t="str">
+        <x:v>PIM_EMP_UploadPhoto_03</x:v>
       </x:c>
       <x:c r="B26" s="45" t="s">
-        <x:v>192</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C26" s="45" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM. Create Login Details tắt. Employee Id dùng cho hồ sơ mới chưa tồn tại. Tệp thử đúng định dạng/dung lượng trong Test Data đã chuẩn bị.
@@ -7451,25 +7218,34 @@
 Dọn dẹp: bỏ thay đổi chưa lưu. Nếu tạo thành công, chỉ xóa nhân viên của case này sau khi giữ bằng chứng; không xóa fixture dùng chung.</x:v>
       </x:c>
       <x:c r="D26" s="45" t="s">
-        <x:v>193</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E26" s="45" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F26" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G26" s="44"/>
-      <x:c r="H26" s="42" t="s">
-        <x:v>194</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="170" customHeight="1">
-      <x:c r="A27" s="42" t="s">
-        <x:v>195</x:v>
+      <x:c r="F26" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G26" s="44" t="d">
+        <x:v>2026-10-21T10:23:55.092Z</x:v>
+      </x:c>
+      <x:c r="H26" s="42" t="str">
+        <x:v>TD_PIM_EMP_04
+Negative; Phân vùng tương đương
+Automation: P2
+Playwright / Edge 155.0.4283.62
+Actual: Upload validation: File type not allowed | Save bị chặn ở Add Employee | Validation vẫn hiển thị sau Save | Không tạo hồ sơ và không lưu ảnh không hợp lệ
+Duration: 5.82s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_UploadPhoto_03.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="210" customHeight="1">
+      <x:c r="A27" s="42" t="str">
+        <x:v>PIM_EMP_UploadPhoto_04</x:v>
       </x:c>
       <x:c r="B27" s="42" t="s">
-        <x:v>196</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C27" s="42" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM. Create Login Details tắt. Employee Id dùng cho hồ sơ mới chưa tồn tại. Tệp thử đúng định dạng/dung lượng trong Test Data đã chuẩn bị.
@@ -7480,25 +7256,34 @@
 Dọn dẹp: bỏ thay đổi chưa lưu. Nếu tạo thành công, chỉ xóa nhân viên của case này sau khi giữ bằng chứng; không xóa fixture dùng chung.</x:v>
       </x:c>
       <x:c r="D27" s="42" t="s">
-        <x:v>197</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="E27" s="42" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F27" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G27" s="44"/>
-      <x:c r="H27" s="42" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="170" customHeight="1">
-      <x:c r="A28" s="45" t="s">
-        <x:v>199</x:v>
+      <x:c r="F27" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G27" s="44" t="d">
+        <x:v>2026-10-21T10:24:00.655Z</x:v>
+      </x:c>
+      <x:c r="H27" s="42" t="str">
+        <x:v>TD_PIM_EMP_04
+Negative; Phân tích giá trị biên
+Automation: P2
+Playwright / Edge 155.0.4283.62
+Actual: Upload validation: Attachment Size Exceeded | Save bị chặn ở Add Employee | Validation vẫn hiển thị sau Save | Không tạo hồ sơ và không lưu ảnh không hợp lệ
+Duration: 5.56s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_UploadPhoto_04.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="210" customHeight="1">
+      <x:c r="A28" s="45" t="str">
+        <x:v>PIM_EMP_Search_01</x:v>
       </x:c>
       <x:c r="B28" s="45" t="s">
-        <x:v>200</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C28" s="45" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM &gt; Employee List. F_DUP (G1N01D0001) đã tạo trong setup.
@@ -7509,25 +7294,34 @@
 Dọn dẹp: bấm Reset để trả bộ lọc về mặc định; giữ các fixture cho case khác.</x:v>
       </x:c>
       <x:c r="D28" s="45" t="s">
-        <x:v>201</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="E28" s="45" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F28" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G28" s="44"/>
-      <x:c r="H28" s="42" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="170" customHeight="1">
-      <x:c r="A29" s="42" t="s">
-        <x:v>203</x:v>
+      <x:c r="F28" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G28" s="44" t="d">
+        <x:v>2026-10-21T10:24:02.951Z</x:v>
+      </x:c>
+      <x:c r="H28" s="42" t="str">
+        <x:v>TD_PIM_EMP_05
+Positive; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 155.0.4283.62
+Actual: Tìm theo Employee Id trả 1 dòng | ID kết quả khớp chính xác
+Duration: 2.29s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_Search_01.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="210" customHeight="1">
+      <x:c r="A29" s="42" t="str">
+        <x:v>PIM_EMP_Search_02</x:v>
       </x:c>
       <x:c r="B29" s="42" t="s">
-        <x:v>204</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C29" s="42" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM &gt; Employee List. F_PERSON (G1N01P0001) đã tạo trong setup.
@@ -7538,25 +7332,34 @@
 Dọn dẹp: bấm Reset để trả bộ lọc về mặc định; giữ các fixture cho case khác.</x:v>
       </x:c>
       <x:c r="D29" s="42" t="s">
-        <x:v>205</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="E29" s="42" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F29" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G29" s="44"/>
-      <x:c r="H29" s="42" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="170" customHeight="1">
-      <x:c r="A30" s="45" t="s">
-        <x:v>206</x:v>
+      <x:c r="F29" s="43" t="str">
+        <x:v>Blocked</x:v>
+      </x:c>
+      <x:c r="G29" s="44" t="d">
+        <x:v>2026-10-21T10:24:24.705Z</x:v>
+      </x:c>
+      <x:c r="H29" s="42" t="str">
+        <x:v>TD_PIM_EMP_05
+Positive; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 155.0.4283.62
+Actual: Blocked: G01N01 có nhiều gợi ý nhưng UI chỉ hiện 5 tên đầu, chưa có F_PERSON. Script timeout khi đợi tên cần chọn. Chưa kết luận lỗi sản phẩm. Cần tên fixture duy nhất hoặc thu hẹp truy vấn rồi chạy lại.
+Duration: 21.75s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_Search_02.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="210" customHeight="1">
+      <x:c r="A30" s="45" t="str">
+        <x:v>PIM_EMP_Search_03</x:v>
       </x:c>
       <x:c r="B30" s="45" t="s">
-        <x:v>207</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C30" s="45" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM &gt; Employee List.
@@ -7566,25 +7369,34 @@
 Dọn dẹp: bấm Reset để trả bộ lọc về mặc định; giữ các fixture cho case khác.</x:v>
       </x:c>
       <x:c r="D30" s="45" t="s">
-        <x:v>208</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="E30" s="45" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F30" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G30" s="44"/>
-      <x:c r="H30" s="42" t="s">
-        <x:v>209</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="170" customHeight="1">
-      <x:c r="A31" s="42" t="s">
-        <x:v>210</x:v>
+      <x:c r="F30" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G30" s="44" t="d">
+        <x:v>2026-10-21T10:24:27.039Z</x:v>
+      </x:c>
+      <x:c r="H30" s="42" t="str">
+        <x:v>TD_PIM_EMP_05
+Negative; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 155.0.4283.62
+Actual: ID không tồn tại hiển thị No Records Found và bảng không có dòng
+Duration: 2.33s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_Search_03.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="210" customHeight="1">
+      <x:c r="A31" s="42" t="str">
+        <x:v>PIM_EMP_Filter_01</x:v>
       </x:c>
       <x:c r="B31" s="42" t="s">
-        <x:v>211</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C31" s="42" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM &gt; Employee List. Hai fixture F_FILTER/F_FILTER_NEG đã chuẩn bị theo Test Data; ghi nhãn TITLE_A và STATUS_A trước run.
@@ -7595,25 +7407,34 @@
 Dọn dẹp: bấm Reset để trả bộ lọc về mặc định; giữ các fixture cho case khác.</x:v>
       </x:c>
       <x:c r="D31" s="42" t="s">
-        <x:v>212</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="E31" s="42" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F31" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G31" s="44"/>
-      <x:c r="H31" s="42" t="s">
-        <x:v>213</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="170" customHeight="1">
-      <x:c r="A32" s="45" t="s">
-        <x:v>214</x:v>
+      <x:c r="F31" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G31" s="44" t="d">
+        <x:v>2026-10-21T10:24:29.467Z</x:v>
+      </x:c>
+      <x:c r="H31" s="42" t="str">
+        <x:v>TD_PIM_EMP_05
+Integration; Bảng quyết định
+Automation: P1
+Playwright / Edge 155.0.4283.62
+Actual: Có positive control F_FILTER | Không có negative control F_FILTER_NEG | Mọi dòng khớp đồng thời Job Title và Employment Status | Đã kiểm tra toàn bộ 1 dòng kết quả
+Duration: 2.43s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_Filter_01.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="210" customHeight="1">
+      <x:c r="A32" s="45" t="str">
+        <x:v>PIM_EMP_Reset_01</x:v>
       </x:c>
       <x:c r="B32" s="45" t="s">
-        <x:v>215</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C32" s="45" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM &gt; Employee List. F_DUP (G1N01D0001) đã tạo trong setup. STATUS_A là nhãn hợp lệ đã ghi trước run.
@@ -7625,25 +7446,34 @@
 Dọn dẹp: bấm Reset để trả bộ lọc về mặc định; giữ các fixture cho case khác.</x:v>
       </x:c>
       <x:c r="D32" s="45" t="s">
-        <x:v>216</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="E32" s="45" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F32" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G32" s="44"/>
-      <x:c r="H32" s="42" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="174" customHeight="1">
-      <x:c r="A33" s="42" t="s">
-        <x:v>217</x:v>
+      <x:c r="F32" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G32" s="44" t="d">
+        <x:v>2026-10-21T10:24:32.849Z</x:v>
+      </x:c>
+      <x:c r="H32" s="42" t="str">
+        <x:v>TD_PIM_EMP_05
+Positive; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 155.0.4283.62
+Actual: Reset xóa Employee Id | Employment Status về mặc định | Search mới không giữ bộ lọc ID/status trước đó
+Duration: 3.38s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_Reset_01.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="210" customHeight="1">
+      <x:c r="A33" s="42" t="str">
+        <x:v>PIM_EMP_Sort_01</x:v>
       </x:c>
       <x:c r="B33" s="42" t="s">
-        <x:v>218</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C33" s="42" t="str">
         <x:v>Tiền điều kiện: Admin đã đăng nhập; vào PIM &gt; Employee List. Có ít nhất hai nhân viên tên khác nhau; ghi tổng số bản ghi trước sắp xếp.
@@ -7659,12 +7489,21 @@
       <x:c r="E33" s="42" t="str">
         <x:v>Không phụ thuộc thứ tự TC; fixture tạo trong setup, không lấy kết quả TC trước.</x:v>
       </x:c>
-      <x:c r="F33" s="43" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G33" s="44"/>
-      <x:c r="H33" s="42" t="s">
-        <x:v>219</x:v>
+      <x:c r="F33" s="43" t="str">
+        <x:v>Blocked</x:v>
+      </x:c>
+      <x:c r="G33" s="44" t="d">
+        <x:v>2026-10-21T10:24:34.988Z</x:v>
+      </x:c>
+      <x:c r="H33" s="42" t="str">
+        <x:v>TD_PIM_EMP_05
+Positive; Chuyển trạng thái
+Automation: P2
+Playwright / Edge 155.0.4283.62
+Actual: Blocked: Playwright không đọc được body của response trước khi trang điều hướng (Network.getResponseBody). Chưa hoàn thành assertion thứ tự tăng/giảm. Đây là lỗi đồng bộ/thu thập response của script; chưa kết luận sorting của OrangeHRM lỗi.
+Duration: 2.14s
+Log: evidence/executions/23130226/PIM_EMP_20261021_04/results.json
+Ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/screenshots/PIM_EMP_Sort_01.png</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15.75" customHeight="1"/>
@@ -8678,7 +8517,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultColWidth="12.630000114440918" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="25" customWidth="1"/>
+    <x:col min="1" max="1" width="37" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="36" customWidth="1"/>
     <x:col min="3" max="3" width="72" customWidth="1"/>
     <x:col min="4" max="4" width="65" customWidth="1"/>
@@ -8701,10 +8540,10 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="34" t="s">
-        <x:v>116</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B2" s="35" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C2" s="39"/>
       <x:c r="D2" s="39"/>
@@ -8715,10 +8554,10 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="34" t="s">
-        <x:v>117</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B3" s="35" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C3" s="39"/>
       <x:c r="D3" s="39"/>
@@ -8729,10 +8568,10 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="34" t="s">
-        <x:v>118</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B4" s="35" t="s">
-        <x:v>119</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C4" s="39"/>
       <x:c r="D4" s="39"/>
@@ -8743,22 +8582,22 @@
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="40" t="s">
-        <x:v>120</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B5" s="40" t="s">
-        <x:v>121</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C5" s="40" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D5" s="40" t="s">
-        <x:v>123</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E5" s="40" t="s">
-        <x:v>124</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F5" s="40" t="s">
-        <x:v>125</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G5" s="36"/>
       <x:c r="H5" s="36"/>
@@ -8803,628 +8642,628 @@
     </x:row>
     <x:row r="8" ht="33.75" customHeight="1">
       <x:c r="A8" s="38" t="s">
-        <x:v>126</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B8" s="38" t="s">
-        <x:v>127</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C8" s="38" t="s">
-        <x:v>128</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D8" s="38" t="s">
-        <x:v>129</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E8" s="38" t="s">
-        <x:v>130</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F8" s="38" t="s">
-        <x:v>131</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G8" s="38" t="s">
-        <x:v>132</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H8" s="38" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="139.5" customHeight="1">
-      <x:c r="A9" s="42" t="s">
-        <x:v>220</x:v>
+      <x:c r="A9" s="42" t="str">
+        <x:v>PIM_PERSONAL_Update_01</x:v>
       </x:c>
       <x:c r="B9" s="42" t="s">
-        <x:v>221</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C9" s="42" t="s">
-        <x:v>222</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D9" s="42" t="s">
-        <x:v>223</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="E9" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F9" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G9" s="44"/>
       <x:c r="H9" s="42" t="s">
-        <x:v>225</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="139.5" customHeight="1">
-      <x:c r="A10" s="45" t="s">
-        <x:v>226</x:v>
+      <x:c r="A10" s="45" t="str">
+        <x:v>PIM_PERSONAL_Update_02</x:v>
       </x:c>
       <x:c r="B10" s="45" t="s">
-        <x:v>227</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C10" s="45" t="s">
-        <x:v>228</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="D10" s="45" t="s">
-        <x:v>229</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="E10" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F10" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G10" s="44"/>
       <x:c r="H10" s="42" t="s">
-        <x:v>230</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="139.5" customHeight="1">
-      <x:c r="A11" s="42" t="s">
-        <x:v>231</x:v>
+      <x:c r="A11" s="42" t="str">
+        <x:v>PIM_PERSONAL_Update_03</x:v>
       </x:c>
       <x:c r="B11" s="42" t="s">
-        <x:v>232</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C11" s="42" t="s">
-        <x:v>233</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D11" s="42" t="s">
-        <x:v>234</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="E11" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F11" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G11" s="44"/>
       <x:c r="H11" s="42" t="s">
-        <x:v>230</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="139.5" customHeight="1">
-      <x:c r="A12" s="45" t="s">
-        <x:v>235</x:v>
+      <x:c r="A12" s="45" t="str">
+        <x:v>PIM_PERSONAL_Update_04</x:v>
       </x:c>
       <x:c r="B12" s="45" t="s">
-        <x:v>236</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C12" s="45" t="s">
-        <x:v>237</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D12" s="45" t="s">
-        <x:v>238</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="E12" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F12" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G12" s="44"/>
       <x:c r="H12" s="42" t="s">
-        <x:v>239</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="139.5" customHeight="1">
-      <x:c r="A13" s="42" t="s">
-        <x:v>240</x:v>
+      <x:c r="A13" s="42" t="str">
+        <x:v>PIM_PERSONAL_Update_05</x:v>
       </x:c>
       <x:c r="B13" s="42" t="s">
-        <x:v>241</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C13" s="42" t="s">
-        <x:v>242</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="D13" s="42" t="s">
-        <x:v>243</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="E13" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F13" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G13" s="44"/>
       <x:c r="H13" s="42" t="s">
-        <x:v>244</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="139.5" customHeight="1">
-      <x:c r="A14" s="45" t="s">
-        <x:v>245</x:v>
+      <x:c r="A14" s="45" t="str">
+        <x:v>PIM_PERSONAL_Update_06</x:v>
       </x:c>
       <x:c r="B14" s="45" t="s">
-        <x:v>246</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C14" s="45" t="s">
-        <x:v>247</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="D14" s="45" t="s">
-        <x:v>243</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="E14" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F14" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G14" s="44"/>
       <x:c r="H14" s="42" t="s">
-        <x:v>244</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="139.5" customHeight="1">
-      <x:c r="A15" s="42" t="s">
-        <x:v>248</x:v>
+      <x:c r="A15" s="42" t="str">
+        <x:v>PIM_PERSONAL_Update_07</x:v>
       </x:c>
       <x:c r="B15" s="42" t="s">
-        <x:v>249</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C15" s="42" t="s">
-        <x:v>250</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="D15" s="42" t="s">
-        <x:v>243</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="E15" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F15" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G15" s="44"/>
       <x:c r="H15" s="42" t="s">
-        <x:v>244</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="139.5" customHeight="1">
-      <x:c r="A16" s="45" t="s">
-        <x:v>251</x:v>
+      <x:c r="A16" s="45" t="str">
+        <x:v>PIM_PERSONAL_Update_08</x:v>
       </x:c>
       <x:c r="B16" s="45" t="s">
-        <x:v>252</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C16" s="45" t="s">
-        <x:v>253</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="D16" s="45" t="s">
-        <x:v>254</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E16" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F16" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G16" s="44"/>
       <x:c r="H16" s="42" t="s">
-        <x:v>255</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="139.5" customHeight="1">
-      <x:c r="A17" s="42" t="s">
-        <x:v>256</x:v>
+      <x:c r="A17" s="42" t="str">
+        <x:v>PIM_PERSONAL_Update_09</x:v>
       </x:c>
       <x:c r="B17" s="42" t="s">
-        <x:v>257</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C17" s="42" t="s">
-        <x:v>258</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="D17" s="42" t="s">
-        <x:v>259</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E17" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F17" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G17" s="44"/>
       <x:c r="H17" s="42" t="s">
-        <x:v>260</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="139.5" customHeight="1">
-      <x:c r="A18" s="45" t="s">
-        <x:v>261</x:v>
+      <x:c r="A18" s="45" t="str">
+        <x:v>PIM_PERSONAL_Update_10</x:v>
       </x:c>
       <x:c r="B18" s="45" t="s">
-        <x:v>262</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C18" s="45" t="s">
-        <x:v>263</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="D18" s="45" t="s">
-        <x:v>264</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="E18" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F18" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G18" s="44"/>
       <x:c r="H18" s="42" t="s">
-        <x:v>255</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="139.5" customHeight="1">
-      <x:c r="A19" s="42" t="s">
-        <x:v>265</x:v>
+      <x:c r="A19" s="42" t="str">
+        <x:v>PIM_PERSONAL_Update_11</x:v>
       </x:c>
       <x:c r="B19" s="42" t="s">
-        <x:v>266</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C19" s="42" t="s">
-        <x:v>267</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="D19" s="42" t="s">
-        <x:v>268</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="E19" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F19" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G19" s="44"/>
       <x:c r="H19" s="42" t="s">
-        <x:v>260</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="139.5" customHeight="1">
-      <x:c r="A20" s="45" t="s">
-        <x:v>269</x:v>
+      <x:c r="A20" s="45" t="str">
+        <x:v>PIM_PERSONAL_Update_12</x:v>
       </x:c>
       <x:c r="B20" s="45" t="s">
-        <x:v>270</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C20" s="45" t="s">
-        <x:v>271</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="D20" s="45" t="s">
-        <x:v>264</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="E20" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F20" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G20" s="44"/>
       <x:c r="H20" s="42" t="s">
-        <x:v>255</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="139.5" customHeight="1">
-      <x:c r="A21" s="42" t="s">
-        <x:v>272</x:v>
+      <x:c r="A21" s="42" t="str">
+        <x:v>PIM_PERSONAL_Update_13</x:v>
       </x:c>
       <x:c r="B21" s="42" t="s">
-        <x:v>273</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C21" s="42" t="s">
-        <x:v>274</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D21" s="42" t="s">
-        <x:v>268</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="E21" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F21" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G21" s="44"/>
       <x:c r="H21" s="42" t="s">
-        <x:v>260</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="139.5" customHeight="1">
-      <x:c r="A22" s="45" t="s">
-        <x:v>275</x:v>
+      <x:c r="A22" s="45" t="str">
+        <x:v>PIM_PERSONAL_Update_14</x:v>
       </x:c>
       <x:c r="B22" s="45" t="s">
-        <x:v>276</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C22" s="45" t="s">
-        <x:v>277</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D22" s="45" t="s">
-        <x:v>278</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E22" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F22" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G22" s="44"/>
       <x:c r="H22" s="42" t="s">
-        <x:v>279</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="139.5" customHeight="1">
-      <x:c r="A23" s="42" t="s">
-        <x:v>280</x:v>
+      <x:c r="A23" s="42" t="str">
+        <x:v>PIM_PERSONAL_Update_15</x:v>
       </x:c>
       <x:c r="B23" s="42" t="s">
-        <x:v>281</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C23" s="42" t="s">
-        <x:v>282</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="D23" s="42" t="s">
-        <x:v>283</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="E23" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F23" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G23" s="44"/>
       <x:c r="H23" s="42" t="s">
-        <x:v>284</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="139.5" customHeight="1">
-      <x:c r="A24" s="45" t="s">
-        <x:v>285</x:v>
+      <x:c r="A24" s="45" t="str">
+        <x:v>PIM_PERSONAL_Update_16</x:v>
       </x:c>
       <x:c r="B24" s="45" t="s">
-        <x:v>286</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C24" s="45" t="s">
-        <x:v>287</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="D24" s="45" t="s">
-        <x:v>288</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="E24" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F24" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G24" s="44"/>
       <x:c r="H24" s="42" t="s">
-        <x:v>279</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="139.5" customHeight="1">
-      <x:c r="A25" s="42" t="s">
-        <x:v>289</x:v>
+      <x:c r="A25" s="42" t="str">
+        <x:v>PIM_PERSONAL_Update_17</x:v>
       </x:c>
       <x:c r="B25" s="42" t="s">
-        <x:v>290</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C25" s="42" t="s">
-        <x:v>291</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="D25" s="42" t="s">
-        <x:v>292</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="E25" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F25" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G25" s="44"/>
       <x:c r="H25" s="42" t="s">
-        <x:v>284</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="139.5" customHeight="1">
-      <x:c r="A26" s="45" t="s">
-        <x:v>293</x:v>
+      <x:c r="A26" s="45" t="str">
+        <x:v>PIM_PERSONAL_Update_18</x:v>
       </x:c>
       <x:c r="B26" s="45" t="s">
-        <x:v>294</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C26" s="45" t="s">
-        <x:v>295</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="D26" s="45" t="s">
-        <x:v>296</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="E26" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F26" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G26" s="44"/>
       <x:c r="H26" s="42" t="s">
+        <x:v>169</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="139.5" customHeight="1">
+      <x:c r="A27" s="42" t="str">
+        <x:v>PIM_PERSONAL_Update_19</x:v>
+      </x:c>
+      <x:c r="B27" s="42" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C27" s="42" t="s">
         <x:v>225</x:v>
       </x:c>
-    </x:row>
-    <x:row r="27" ht="139.5" customHeight="1">
-      <x:c r="A27" s="42" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="B27" s="42" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="C27" s="42" t="s">
-        <x:v>299</x:v>
-      </x:c>
       <x:c r="D27" s="42" t="s">
-        <x:v>300</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="E27" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F27" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G27" s="44"/>
       <x:c r="H27" s="42" t="s">
-        <x:v>225</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="139.5" customHeight="1">
-      <x:c r="A28" s="45" t="s">
-        <x:v>301</x:v>
+      <x:c r="A28" s="45" t="str">
+        <x:v>PIM_PERSONAL_Update_20</x:v>
       </x:c>
       <x:c r="B28" s="45" t="s">
-        <x:v>302</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C28" s="45" t="s">
-        <x:v>303</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="D28" s="45" t="s">
-        <x:v>304</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="E28" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F28" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G28" s="44"/>
       <x:c r="H28" s="42" t="s">
-        <x:v>225</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="139.5" customHeight="1">
-      <x:c r="A29" s="42" t="s">
-        <x:v>305</x:v>
+      <x:c r="A29" s="42" t="str">
+        <x:v>PIM_PERSONAL_CreateAttachment_01</x:v>
       </x:c>
       <x:c r="B29" s="42" t="s">
-        <x:v>306</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C29" s="42" t="s">
-        <x:v>307</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="D29" s="42" t="s">
-        <x:v>308</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="E29" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F29" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G29" s="44"/>
       <x:c r="H29" s="42" t="s">
-        <x:v>309</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="139.5" customHeight="1">
-      <x:c r="A30" s="45" t="s">
-        <x:v>310</x:v>
+      <x:c r="A30" s="45" t="str">
+        <x:v>PIM_PERSONAL_CreateAttachment_02</x:v>
       </x:c>
       <x:c r="B30" s="45" t="s">
-        <x:v>311</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C30" s="45" t="s">
-        <x:v>312</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="D30" s="45" t="s">
-        <x:v>313</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E30" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F30" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G30" s="44"/>
       <x:c r="H30" s="42" t="s">
-        <x:v>314</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="156" customHeight="1">
-      <x:c r="A31" s="42" t="s">
-        <x:v>315</x:v>
+      <x:c r="A31" s="42" t="str">
+        <x:v>PIM_PERSONAL_CreateAttachment_03</x:v>
       </x:c>
       <x:c r="B31" s="42" t="s">
-        <x:v>316</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C31" s="42" t="s">
-        <x:v>317</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="D31" s="42" t="s">
-        <x:v>318</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E31" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F31" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G31" s="44"/>
       <x:c r="H31" s="42" t="s">
-        <x:v>319</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="156" customHeight="1">
-      <x:c r="A32" s="45" t="s">
-        <x:v>320</x:v>
+      <x:c r="A32" s="45" t="str">
+        <x:v>PIM_PERSONAL_CreateAttachment_04</x:v>
       </x:c>
       <x:c r="B32" s="45" t="s">
-        <x:v>321</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C32" s="45" t="s">
-        <x:v>322</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="D32" s="45" t="s">
-        <x:v>323</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="E32" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F32" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G32" s="44"/>
       <x:c r="H32" s="42" t="s">
-        <x:v>324</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="139.5" customHeight="1">
-      <x:c r="A33" s="42" t="s">
-        <x:v>325</x:v>
+      <x:c r="A33" s="42" t="str">
+        <x:v>PIM_PERSONAL_DeleteAttachment_01</x:v>
       </x:c>
       <x:c r="B33" s="42" t="s">
-        <x:v>326</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C33" s="42" t="s">
-        <x:v>327</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="D33" s="42" t="s">
-        <x:v>328</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="E33" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F33" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G33" s="44"/>
       <x:c r="H33" s="42" t="s">
-        <x:v>329</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15.75" customHeight="1"/>
@@ -10438,7 +10277,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultColWidth="12.630000114440918" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="25" customWidth="1"/>
+    <x:col min="1" max="1" width="37" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="36" customWidth="1"/>
     <x:col min="3" max="3" width="72" customWidth="1"/>
     <x:col min="4" max="4" width="65" customWidth="1"/>
@@ -10461,10 +10300,10 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="34" t="s">
-        <x:v>116</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B2" s="35" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C2" s="39"/>
       <x:c r="D2" s="39"/>
@@ -10475,10 +10314,10 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="34" t="s">
-        <x:v>117</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B3" s="35" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C3" s="39"/>
       <x:c r="D3" s="39"/>
@@ -10489,10 +10328,10 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="34" t="s">
-        <x:v>118</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B4" s="35" t="s">
-        <x:v>119</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C4" s="39"/>
       <x:c r="D4" s="39"/>
@@ -10503,22 +10342,22 @@
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="40" t="s">
-        <x:v>120</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B5" s="40" t="s">
-        <x:v>121</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C5" s="40" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D5" s="40" t="s">
-        <x:v>123</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E5" s="40" t="s">
-        <x:v>124</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F5" s="40" t="s">
-        <x:v>125</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G5" s="36"/>
       <x:c r="H5" s="36"/>
@@ -10563,628 +10402,628 @@
     </x:row>
     <x:row r="8" ht="33.75" customHeight="1">
       <x:c r="A8" s="38" t="s">
-        <x:v>126</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B8" s="38" t="s">
-        <x:v>127</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C8" s="38" t="s">
-        <x:v>128</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D8" s="38" t="s">
-        <x:v>129</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E8" s="38" t="s">
-        <x:v>130</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F8" s="38" t="s">
-        <x:v>131</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G8" s="38" t="s">
-        <x:v>132</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H8" s="38" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="139.5" customHeight="1">
-      <x:c r="A9" s="42" t="s">
-        <x:v>330</x:v>
+      <x:c r="A9" s="42" t="str">
+        <x:v>PIM_JOB_UpdateJob_01</x:v>
       </x:c>
       <x:c r="B9" s="42" t="s">
-        <x:v>331</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C9" s="42" t="s">
-        <x:v>332</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="D9" s="42" t="s">
-        <x:v>333</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E9" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F9" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G9" s="44"/>
       <x:c r="H9" s="42" t="s">
-        <x:v>334</x:v>
+        <x:v>253</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="139.5" customHeight="1">
-      <x:c r="A10" s="45" t="s">
-        <x:v>335</x:v>
+      <x:c r="A10" s="45" t="str">
+        <x:v>PIM_JOB_UpdateJob_02</x:v>
       </x:c>
       <x:c r="B10" s="45" t="s">
-        <x:v>336</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C10" s="45" t="s">
-        <x:v>337</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="D10" s="45" t="s">
-        <x:v>338</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E10" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F10" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G10" s="44"/>
       <x:c r="H10" s="42" t="s">
-        <x:v>339</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="139.5" customHeight="1">
-      <x:c r="A11" s="42" t="s">
-        <x:v>340</x:v>
+      <x:c r="A11" s="42" t="str">
+        <x:v>PIM_JOB_UpdateJob_03</x:v>
       </x:c>
       <x:c r="B11" s="42" t="s">
-        <x:v>341</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C11" s="42" t="s">
-        <x:v>342</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="D11" s="42" t="s">
-        <x:v>343</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="E11" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F11" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G11" s="44"/>
       <x:c r="H11" s="42" t="s">
-        <x:v>344</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="139.5" customHeight="1">
-      <x:c r="A12" s="45" t="s">
-        <x:v>345</x:v>
+      <x:c r="A12" s="45" t="str">
+        <x:v>PIM_JOB_UpdateJob_04</x:v>
       </x:c>
       <x:c r="B12" s="45" t="s">
-        <x:v>346</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C12" s="45" t="s">
-        <x:v>347</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="D12" s="45" t="s">
-        <x:v>348</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="E12" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F12" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G12" s="44"/>
       <x:c r="H12" s="42" t="s">
-        <x:v>344</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="139.5" customHeight="1">
-      <x:c r="A13" s="42" t="s">
-        <x:v>349</x:v>
+      <x:c r="A13" s="42" t="str">
+        <x:v>PIM_JOB_UpdateJob_05</x:v>
       </x:c>
       <x:c r="B13" s="42" t="s">
-        <x:v>350</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C13" s="42" t="s">
-        <x:v>351</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="D13" s="42" t="s">
-        <x:v>352</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="E13" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F13" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G13" s="44"/>
       <x:c r="H13" s="42" t="s">
-        <x:v>344</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="139.5" customHeight="1">
-      <x:c r="A14" s="45" t="s">
-        <x:v>353</x:v>
+      <x:c r="A14" s="45" t="str">
+        <x:v>PIM_JOB_UpdateJob_06</x:v>
       </x:c>
       <x:c r="B14" s="45" t="s">
-        <x:v>354</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C14" s="45" t="s">
-        <x:v>355</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D14" s="45" t="s">
-        <x:v>356</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="E14" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F14" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G14" s="44"/>
       <x:c r="H14" s="42" t="s">
-        <x:v>344</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="139.5" customHeight="1">
-      <x:c r="A15" s="42" t="s">
-        <x:v>357</x:v>
+      <x:c r="A15" s="42" t="str">
+        <x:v>PIM_JOB_UpdateJob_07</x:v>
       </x:c>
       <x:c r="B15" s="42" t="s">
-        <x:v>358</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C15" s="42" t="s">
-        <x:v>359</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="D15" s="42" t="s">
-        <x:v>360</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="E15" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F15" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G15" s="44"/>
       <x:c r="H15" s="42" t="s">
-        <x:v>344</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="139.5" customHeight="1">
-      <x:c r="A16" s="45" t="s">
-        <x:v>361</x:v>
+      <x:c r="A16" s="45" t="str">
+        <x:v>PIM_JOB_UpdateJob_08</x:v>
       </x:c>
       <x:c r="B16" s="45" t="s">
-        <x:v>362</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C16" s="45" t="s">
-        <x:v>363</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="D16" s="45" t="s">
-        <x:v>364</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E16" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F16" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G16" s="44"/>
       <x:c r="H16" s="42" t="s">
-        <x:v>365</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="139.5" customHeight="1">
-      <x:c r="A17" s="42" t="s">
-        <x:v>366</x:v>
+      <x:c r="A17" s="42" t="str">
+        <x:v>PIM_JOB_UpdateJob_09</x:v>
       </x:c>
       <x:c r="B17" s="42" t="s">
-        <x:v>367</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C17" s="42" t="s">
-        <x:v>368</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="D17" s="42" t="s">
-        <x:v>369</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E17" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F17" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G17" s="44"/>
       <x:c r="H17" s="42" t="s">
-        <x:v>334</x:v>
+        <x:v>253</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="139.5" customHeight="1">
-      <x:c r="A18" s="45" t="s">
-        <x:v>370</x:v>
+      <x:c r="A18" s="45" t="str">
+        <x:v>PIM_JOB_ToggleContract_01</x:v>
       </x:c>
       <x:c r="B18" s="45" t="s">
-        <x:v>371</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C18" s="45" t="s">
-        <x:v>372</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="D18" s="45" t="s">
-        <x:v>373</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="E18" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F18" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G18" s="44"/>
       <x:c r="H18" s="42" t="s">
-        <x:v>374</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="139.5" customHeight="1">
-      <x:c r="A19" s="42" t="s">
-        <x:v>375</x:v>
+      <x:c r="A19" s="42" t="str">
+        <x:v>PIM_JOB_ToggleContract_02</x:v>
       </x:c>
       <x:c r="B19" s="42" t="s">
-        <x:v>376</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C19" s="42" t="s">
-        <x:v>377</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D19" s="42" t="s">
-        <x:v>378</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="E19" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F19" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G19" s="44"/>
       <x:c r="H19" s="42" t="s">
-        <x:v>379</x:v>
+        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="139.5" customHeight="1">
-      <x:c r="A20" s="45" t="s">
-        <x:v>380</x:v>
+      <x:c r="A20" s="45" t="str">
+        <x:v>PIM_JOB_UpdateContract_01</x:v>
       </x:c>
       <x:c r="B20" s="45" t="s">
-        <x:v>381</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C20" s="45" t="s">
-        <x:v>382</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="D20" s="45" t="s">
-        <x:v>383</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="E20" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F20" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G20" s="44"/>
       <x:c r="H20" s="42" t="s">
-        <x:v>384</x:v>
+        <x:v>292</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="139.5" customHeight="1">
-      <x:c r="A21" s="42" t="s">
-        <x:v>385</x:v>
+      <x:c r="A21" s="42" t="str">
+        <x:v>PIM_JOB_UpdateContract_02</x:v>
       </x:c>
       <x:c r="B21" s="42" t="s">
-        <x:v>386</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C21" s="42" t="s">
-        <x:v>387</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="D21" s="42" t="s">
-        <x:v>388</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E21" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F21" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G21" s="44"/>
       <x:c r="H21" s="42" t="s">
-        <x:v>389</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="139.5" customHeight="1">
-      <x:c r="A22" s="45" t="s">
-        <x:v>390</x:v>
+      <x:c r="A22" s="45" t="str">
+        <x:v>PIM_JOB_UpdateContract_03</x:v>
       </x:c>
       <x:c r="B22" s="45" t="s">
-        <x:v>391</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C22" s="45" t="s">
-        <x:v>392</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="D22" s="45" t="s">
-        <x:v>393</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="E22" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F22" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G22" s="44"/>
       <x:c r="H22" s="42" t="s">
-        <x:v>394</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="139.5" customHeight="1">
-      <x:c r="A23" s="42" t="s">
-        <x:v>395</x:v>
+      <x:c r="A23" s="42" t="str">
+        <x:v>PIM_JOB_UpdateContract_04</x:v>
       </x:c>
       <x:c r="B23" s="42" t="s">
-        <x:v>396</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="C23" s="42" t="s">
-        <x:v>397</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="D23" s="42" t="s">
-        <x:v>398</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="E23" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F23" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G23" s="44"/>
       <x:c r="H23" s="42" t="s">
-        <x:v>399</x:v>
+        <x:v>304</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="139.5" customHeight="1">
-      <x:c r="A24" s="45" t="s">
-        <x:v>400</x:v>
+      <x:c r="A24" s="45" t="str">
+        <x:v>PIM_JOB_UpdateContract_05</x:v>
       </x:c>
       <x:c r="B24" s="45" t="s">
-        <x:v>401</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C24" s="45" t="s">
-        <x:v>402</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="D24" s="45" t="s">
-        <x:v>403</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="E24" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F24" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G24" s="44"/>
       <x:c r="H24" s="42" t="s">
-        <x:v>399</x:v>
+        <x:v>304</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="139.5" customHeight="1">
-      <x:c r="A25" s="42" t="s">
-        <x:v>404</x:v>
+      <x:c r="A25" s="42" t="str">
+        <x:v>PIM_JOB_UploadContract_01</x:v>
       </x:c>
       <x:c r="B25" s="42" t="s">
-        <x:v>405</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="C25" s="42" t="s">
-        <x:v>406</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="D25" s="42" t="s">
-        <x:v>407</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="E25" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F25" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G25" s="44"/>
       <x:c r="H25" s="42" t="s">
-        <x:v>408</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="141.75" customHeight="1">
-      <x:c r="A26" s="45" t="s">
-        <x:v>409</x:v>
+      <x:c r="A26" s="45" t="str">
+        <x:v>PIM_JOB_UploadContract_02</x:v>
       </x:c>
       <x:c r="B26" s="45" t="s">
-        <x:v>410</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="C26" s="45" t="s">
-        <x:v>411</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="D26" s="45" t="s">
-        <x:v>412</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="E26" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F26" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G26" s="44"/>
       <x:c r="H26" s="42" t="s">
-        <x:v>413</x:v>
+        <x:v>315</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="141.75" customHeight="1">
-      <x:c r="A27" s="42" t="s">
-        <x:v>414</x:v>
+      <x:c r="A27" s="42" t="str">
+        <x:v>PIM_JOB_UploadContract_03</x:v>
       </x:c>
       <x:c r="B27" s="42" t="s">
-        <x:v>415</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="C27" s="42" t="s">
-        <x:v>416</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="D27" s="42" t="s">
-        <x:v>417</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="E27" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F27" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G27" s="44"/>
       <x:c r="H27" s="42" t="s">
-        <x:v>418</x:v>
+        <x:v>319</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="139.5" customHeight="1">
-      <x:c r="A28" s="45" t="s">
-        <x:v>419</x:v>
+      <x:c r="A28" s="45" t="str">
+        <x:v>PIM_JOB_KeepContract_01</x:v>
       </x:c>
       <x:c r="B28" s="45" t="s">
-        <x:v>420</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C28" s="45" t="s">
-        <x:v>421</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="D28" s="45" t="s">
-        <x:v>422</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="E28" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F28" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G28" s="44"/>
       <x:c r="H28" s="42" t="s">
-        <x:v>423</x:v>
+        <x:v>323</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="139.5" customHeight="1">
-      <x:c r="A29" s="42" t="s">
-        <x:v>424</x:v>
+      <x:c r="A29" s="42" t="str">
+        <x:v>PIM_JOB_ReplaceContract_01</x:v>
       </x:c>
       <x:c r="B29" s="42" t="s">
-        <x:v>425</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C29" s="42" t="s">
-        <x:v>426</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D29" s="42" t="s">
-        <x:v>427</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="E29" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F29" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G29" s="44"/>
       <x:c r="H29" s="42" t="s">
-        <x:v>408</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="139.5" customHeight="1">
-      <x:c r="A30" s="45" t="s">
-        <x:v>428</x:v>
+      <x:c r="A30" s="45" t="str">
+        <x:v>PIM_JOB_ReplaceContract_02</x:v>
       </x:c>
       <x:c r="B30" s="45" t="s">
-        <x:v>429</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="C30" s="45" t="s">
-        <x:v>430</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="D30" s="45" t="s">
-        <x:v>431</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="E30" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F30" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G30" s="44"/>
       <x:c r="H30" s="42" t="s">
-        <x:v>432</x:v>
+        <x:v>330</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="139.5" customHeight="1">
-      <x:c r="A31" s="42" t="s">
-        <x:v>433</x:v>
+      <x:c r="A31" s="42" t="str">
+        <x:v>PIM_JOB_DeleteContract_01</x:v>
       </x:c>
       <x:c r="B31" s="42" t="s">
-        <x:v>434</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C31" s="42" t="s">
-        <x:v>435</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="D31" s="42" t="s">
-        <x:v>436</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="E31" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F31" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G31" s="44"/>
       <x:c r="H31" s="42" t="s">
-        <x:v>437</x:v>
+        <x:v>334</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="139.5" customHeight="1">
-      <x:c r="A32" s="45" t="s">
-        <x:v>438</x:v>
+      <x:c r="A32" s="45" t="str">
+        <x:v>PIM_JOB_CreateAttachment_01</x:v>
       </x:c>
       <x:c r="B32" s="45" t="s">
-        <x:v>439</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="C32" s="45" t="s">
-        <x:v>440</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="D32" s="45" t="s">
-        <x:v>441</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="E32" s="45" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F32" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G32" s="44"/>
       <x:c r="H32" s="42" t="s">
-        <x:v>408</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="139.5" customHeight="1">
-      <x:c r="A33" s="42" t="s">
-        <x:v>442</x:v>
+      <x:c r="A33" s="42" t="str">
+        <x:v>PIM_JOB_CancelAttachment_01</x:v>
       </x:c>
       <x:c r="B33" s="42" t="s">
-        <x:v>443</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C33" s="42" t="s">
-        <x:v>444</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="D33" s="42" t="s">
-        <x:v>445</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="E33" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F33" s="43" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G33" s="44"/>
       <x:c r="H33" s="42" t="s">
-        <x:v>446</x:v>
+        <x:v>341</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15.75" customHeight="1"/>
@@ -12214,7 +12053,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="3" t="s">
-        <x:v>447</x:v>
+        <x:v>342</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -12227,442 +12066,442 @@
     </x:row>
     <x:row r="4" ht="31.5" customHeight="1">
       <x:c r="A4" s="38" t="s">
-        <x:v>448</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B4" s="38" t="s">
-        <x:v>449</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="C4" s="38" t="s">
-        <x:v>450</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="D4" s="38" t="s">
-        <x:v>451</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="E4" s="38" t="s">
-        <x:v>452</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="F4" s="38" t="s">
-        <x:v>453</x:v>
+        <x:v>348</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="109.5" customHeight="1">
       <x:c r="A5" s="35" t="s">
-        <x:v>454</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B5" s="35" t="s">
-        <x:v>455</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="C5" s="35" t="s">
-        <x:v>456</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="D5" s="35" t="s">
-        <x:v>457</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E5" s="35" t="s">
-        <x:v>458</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="F5" s="35" t="s">
-        <x:v>459</x:v>
+        <x:v>354</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="109.5" customHeight="1">
       <x:c r="A6" s="35" t="s">
-        <x:v>460</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B6" s="35" t="s">
-        <x:v>461</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="C6" s="35" t="s">
-        <x:v>462</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="D6" s="35" t="s">
-        <x:v>463</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="E6" s="35" t="s">
-        <x:v>464</x:v>
-      </x:c>
-      <x:c r="F6" s="35" t="s">
-        <x:v>465</x:v>
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="F6" s="35" t="str">
+        <x:v>Tài khoản demo công khai; không thay mật khẩu.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="109.5" customHeight="1">
       <x:c r="A7" s="35" t="s">
-        <x:v>466</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B7" s="35" t="str">
         <x:v>ID=G1N01D0001; First=G01N01; Last=NhutDuplicate</x:v>
       </x:c>
       <x:c r="C7" s="35" t="s">
-        <x:v>467</x:v>
-      </x:c>
-      <x:c r="D7" s="35" t="s">
-        <x:v>468</x:v>
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D7" s="35" t="str">
+        <x:v>PIM_EMP_Create_14; PIM_EMP_Search_01; PIM_EMP_Reset_01</x:v>
       </x:c>
       <x:c r="E7" s="35" t="s">
-        <x:v>469</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="F7" s="35" t="s">
-        <x:v>470</x:v>
+        <x:v>363</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="109.5" customHeight="1">
       <x:c r="A8" s="35" t="s">
-        <x:v>471</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B8" s="35" t="s">
-        <x:v>472</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="C8" s="35" t="s">
-        <x:v>473</x:v>
-      </x:c>
-      <x:c r="D8" s="35" t="s">
-        <x:v>474</x:v>
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="D8" s="35" t="str">
+        <x:v>PIM_PERSONAL; PIM_EMP_Search_02</x:v>
       </x:c>
       <x:c r="E8" s="35" t="s">
-        <x:v>475</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="F8" s="35" t="s">
-        <x:v>476</x:v>
+        <x:v>368</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="109.5" customHeight="1">
       <x:c r="A9" s="35" t="s">
-        <x:v>477</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B9" s="35" t="s">
-        <x:v>478</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="C9" s="35" t="s">
-        <x:v>479</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="D9" s="35" t="s">
-        <x:v>480</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="E9" s="35" t="s">
-        <x:v>481</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="F9" s="35" t="s">
-        <x:v>482</x:v>
+        <x:v>374</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="109.5" customHeight="1">
       <x:c r="A10" s="35" t="s">
-        <x:v>483</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B10" s="35" t="s">
-        <x:v>484</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="C10" s="35" t="s">
-        <x:v>485</x:v>
-      </x:c>
-      <x:c r="D10" s="35" t="s">
-        <x:v>210</x:v>
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D10" s="35" t="str">
+        <x:v>PIM_EMP_Filter_01</x:v>
       </x:c>
       <x:c r="E10" s="35" t="s">
-        <x:v>486</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="F10" s="35" t="s">
-        <x:v>487</x:v>
+        <x:v>379</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="109.5" customHeight="1">
       <x:c r="A11" s="35" t="s">
-        <x:v>488</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B11" s="35" t="s">
-        <x:v>489</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="C11" s="35" t="s">
-        <x:v>490</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D11" s="35" t="s">
-        <x:v>491</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="E11" s="35" t="s">
-        <x:v>492</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="F11" s="35" t="s">
-        <x:v>493</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="109.5" customHeight="1">
       <x:c r="A12" s="35" t="s">
-        <x:v>494</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B12" s="35" t="s">
-        <x:v>495</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="C12" s="35" t="s">
-        <x:v>496</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="D12" s="35" t="s">
-        <x:v>497</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="E12" s="35" t="s">
-        <x:v>498</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="F12" s="35" t="s">
-        <x:v>499</x:v>
+        <x:v>391</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="109.5" customHeight="1">
       <x:c r="A13" s="35" t="s">
-        <x:v>500</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B13" s="35" t="s">
-        <x:v>501</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="C13" s="35" t="s">
-        <x:v>502</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D13" s="35" t="s">
-        <x:v>503</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="E13" s="35" t="s">
-        <x:v>504</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="F13" s="35" t="s">
-        <x:v>505</x:v>
+        <x:v>397</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="109.5" customHeight="1">
       <x:c r="A14" s="35" t="s">
-        <x:v>506</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B14" s="35" t="s">
-        <x:v>507</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="C14" s="35" t="s">
-        <x:v>508</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="D14" s="35" t="s">
-        <x:v>509</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="E14" s="35" t="s">
-        <x:v>510</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F14" s="35" t="s">
-        <x:v>511</x:v>
+        <x:v>403</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="109.5" customHeight="1">
       <x:c r="A15" s="35" t="s">
-        <x:v>512</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B15" s="35" t="s">
-        <x:v>513</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C15" s="35" t="s">
-        <x:v>514</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="D15" s="35" t="s">
-        <x:v>515</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="E15" s="35" t="s">
-        <x:v>516</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="F15" s="35" t="s">
-        <x:v>517</x:v>
+        <x:v>409</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="109.5" customHeight="1">
       <x:c r="A16" s="35" t="s">
-        <x:v>518</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B16" s="35" t="s">
-        <x:v>519</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="C16" s="35" t="s">
-        <x:v>520</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="D16" s="35" t="s">
-        <x:v>521</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="E16" s="35" t="s">
-        <x:v>522</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="F16" s="35" t="s">
-        <x:v>523</x:v>
+        <x:v>415</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="109.5" customHeight="1">
       <x:c r="A17" s="35" t="s">
-        <x:v>524</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B17" s="35" t="s">
-        <x:v>525</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="C17" s="35" t="s">
-        <x:v>526</x:v>
-      </x:c>
-      <x:c r="D17" s="35" t="s">
-        <x:v>527</x:v>
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="D17" s="35" t="str">
+        <x:v>PIM_EMP_UploadPhoto_01–02</x:v>
       </x:c>
       <x:c r="E17" s="35" t="s">
-        <x:v>528</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="F17" s="35" t="s">
-        <x:v>529</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="109.5" customHeight="1">
       <x:c r="A18" s="35" t="s">
-        <x:v>530</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B18" s="35" t="s">
-        <x:v>531</x:v>
-      </x:c>
-      <x:c r="C18" s="35" t="s">
-        <x:v>532</x:v>
-      </x:c>
-      <x:c r="D18" s="35" t="s">
-        <x:v>533</x:v>
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="C18" s="35" t="str">
+        <x:v>PDF thực. PNG hợp lệ 1.048.577 byte (1 MiB + 1 byte), có ancillary chunk; không đổi đuôi tệp.</x:v>
+      </x:c>
+      <x:c r="D18" s="35" t="str">
+        <x:v>PIM_EMP_UploadPhoto_03–04</x:v>
       </x:c>
       <x:c r="E18" s="35" t="s">
-        <x:v>534</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="F18" s="35" t="s">
-        <x:v>535</x:v>
+        <x:v>424</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="109.5" customHeight="1">
       <x:c r="A19" s="35" t="s">
-        <x:v>536</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B19" s="35" t="s">
-        <x:v>537</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="C19" s="35" t="s">
-        <x:v>538</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="D19" s="35" t="s">
-        <x:v>539</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="E19" s="35" t="s">
-        <x:v>540</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="F19" s="35" t="s">
-        <x:v>541</x:v>
+        <x:v>430</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="109.5" customHeight="1">
       <x:c r="A20" s="35" t="s">
-        <x:v>542</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B20" s="35" t="s">
-        <x:v>543</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="C20" s="35" t="s">
-        <x:v>544</x:v>
-      </x:c>
-      <x:c r="D20" s="35" t="s">
-        <x:v>545</x:v>
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="D20" s="35" t="str">
+        <x:v>PIM_JOB_UploadContract_02–03; các TC upload</x:v>
       </x:c>
       <x:c r="E20" s="35" t="s">
-        <x:v>546</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="F20" s="35" t="s">
-        <x:v>547</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="109.5" customHeight="1">
       <x:c r="A21" s="35" t="s">
-        <x:v>548</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B21" s="35" t="s">
-        <x:v>549</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="C21" s="35" t="s">
-        <x:v>550</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="D21" s="35" t="s">
-        <x:v>551</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="E21" s="35" t="s">
-        <x:v>552</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="F21" s="35" t="s">
-        <x:v>553</x:v>
+        <x:v>441</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="109.5" customHeight="1">
       <x:c r="A22" s="35" t="s">
-        <x:v>554</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B22" s="35" t="s">
-        <x:v>555</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="C22" s="35" t="s">
-        <x:v>556</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="D22" s="35" t="s">
-        <x:v>557</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E22" s="35" t="s">
-        <x:v>558</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F22" s="35" t="s">
-        <x:v>559</x:v>
+        <x:v>447</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="109.5" customHeight="1">
       <x:c r="A23" s="35" t="s">
-        <x:v>560</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B23" s="35" t="s">
-        <x:v>561</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="C23" s="35" t="s">
-        <x:v>562</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D23" s="35" t="s">
-        <x:v>563</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="E23" s="35" t="s">
-        <x:v>564</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="F23" s="35" t="s">
-        <x:v>565</x:v>
+        <x:v>453</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="109.5" customHeight="1">
       <x:c r="A24" s="35" t="s">
-        <x:v>566</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B24" s="35" t="s">
-        <x:v>567</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="C24" s="35" t="s">
-        <x:v>568</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="D24" s="35" t="s">
-        <x:v>569</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="E24" s="35" t="s">
-        <x:v>570</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="F24" s="35" t="s">
-        <x:v>571</x:v>
+        <x:v>459</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="109.5" customHeight="1">
       <x:c r="A25" s="35" t="s">
-        <x:v>572</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B25" s="35" t="s">
-        <x:v>573</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="C25" s="35" t="s">
-        <x:v>574</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="D25" s="35" t="s">
-        <x:v>575</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="E25" s="35" t="s">
-        <x:v>576</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="F25" s="35" t="s">
-        <x:v>577</x:v>
+        <x:v>465</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15.75" customHeight="1">
@@ -12675,13 +12514,13 @@
     </x:row>
     <x:row r="27" ht="15.75" customHeight="1">
       <x:c r="A27" s="38" t="s">
-        <x:v>578</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B27" s="38" t="s">
-        <x:v>579</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="C27" s="38" t="s">
-        <x:v>580</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="D27" s="1"/>
       <x:c r="E27" s="1"/>
@@ -12695,7 +12534,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C28" s="35" t="s">
-        <x:v>581</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="D28" s="2"/>
       <x:c r="E28" s="2"/>
@@ -12703,13 +12542,13 @@
     </x:row>
     <x:row r="29" ht="69.75" customHeight="1">
       <x:c r="A29" s="35" t="s">
-        <x:v>582</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B29" s="35" t="s">
-        <x:v>583</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="C29" s="35" t="s">
-        <x:v>584</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="D29" s="2"/>
       <x:c r="E29" s="2"/>
@@ -12717,13 +12556,13 @@
     </x:row>
     <x:row r="30" ht="69.75" customHeight="1">
       <x:c r="A30" s="35" t="s">
-        <x:v>585</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B30" s="35" t="s">
-        <x:v>586</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="C30" s="35" t="s">
-        <x:v>587</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="D30" s="2"/>
       <x:c r="E30" s="2"/>
@@ -12731,13 +12570,13 @@
     </x:row>
     <x:row r="31" ht="69.75" customHeight="1">
       <x:c r="A31" s="35" t="s">
-        <x:v>588</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B31" s="35" t="s">
-        <x:v>589</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C31" s="35" t="s">
-        <x:v>590</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="D31" s="2"/>
       <x:c r="E31" s="2"/>
@@ -12745,13 +12584,13 @@
     </x:row>
     <x:row r="32" ht="69.75" customHeight="1">
       <x:c r="A32" s="35" t="s">
-        <x:v>93</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B32" s="35" t="s">
-        <x:v>591</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="C32" s="35" t="s">
-        <x:v>592</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D32" s="2"/>
       <x:c r="E32" s="2"/>
@@ -12759,13 +12598,13 @@
     </x:row>
     <x:row r="33" ht="69.75" customHeight="1">
       <x:c r="A33" s="35" t="s">
-        <x:v>593</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="B33" s="35" t="s">
-        <x:v>594</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="C33" s="35" t="s">
-        <x:v>595</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="D33" s="2"/>
       <x:c r="E33" s="2"/>
@@ -13818,7 +13657,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="3" t="s">
-        <x:v>596</x:v>
+        <x:v>484</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -13831,22 +13670,22 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="38" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B4" s="38" t="s">
-        <x:v>597</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="C4" s="38" t="s">
-        <x:v>598</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="D4" s="38" t="s">
-        <x:v>599</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="E4" s="38" t="s">
-        <x:v>600</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="F4" s="38" t="s">
-        <x:v>601</x:v>
+        <x:v>489</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="103.5" customHeight="1">
@@ -13854,19 +13693,19 @@
         <x:v>1.0</x:v>
       </x:c>
       <x:c r="B5" s="35" t="s">
-        <x:v>602</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="C5" s="35" t="s">
-        <x:v>603</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="D5" s="35" t="s">
-        <x:v>604</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="E5" s="35" t="s">
-        <x:v>605</x:v>
-      </x:c>
-      <x:c r="F5" s="35" t="s">
-        <x:v>606</x:v>
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="F5" s="35" t="str">
+        <x:v>Đã thực hiện PIM_EMP</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="103.5" customHeight="1">
@@ -13874,19 +13713,19 @@
         <x:v>2.0</x:v>
       </x:c>
       <x:c r="B6" s="35" t="s">
-        <x:v>607</x:v>
-      </x:c>
-      <x:c r="C6" s="35" t="s">
-        <x:v>608</x:v>
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="C6" s="35" t="str">
+        <x:v>Tạo F_DUP, F_PERSON, F_FILTER qua UI; ghi numeric employee key. Chuẩn bị JPG/PNG/PDF và PNG 1 MiB + 1 byte. F_JOB chưa tạo.</x:v>
       </x:c>
       <x:c r="D6" s="35" t="s">
-        <x:v>609</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="E6" s="35" t="s">
-        <x:v>610</x:v>
-      </x:c>
-      <x:c r="F6" s="35" t="s">
-        <x:v>606</x:v>
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="F6" s="35" t="str">
+        <x:v>Đã chuẩn bị PIM_EMP</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="103.5" customHeight="1">
@@ -13894,19 +13733,19 @@
         <x:v>3.0</x:v>
       </x:c>
       <x:c r="B7" s="35" t="s">
-        <x:v>611</x:v>
-      </x:c>
-      <x:c r="C7" s="35" t="s">
-        <x:v>612</x:v>
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="C7" s="35" t="str">
+        <x:v>Chạy Playwright PIM_EMP, thêm assertion cho từng expected, lưu log và screenshot thật.</x:v>
       </x:c>
       <x:c r="D7" s="35" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="E7" s="35" t="s">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="F7" s="35" t="s">
-        <x:v>606</x:v>
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="E7" s="35" t="str">
+        <x:v>Playwright 1.62.1; Microsoft Edge headless.</x:v>
+      </x:c>
+      <x:c r="F7" s="35" t="str">
+        <x:v>Đã thực hiện PIM_EMP</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="103.5" customHeight="1">
@@ -13914,19 +13753,19 @@
         <x:v>4.0</x:v>
       </x:c>
       <x:c r="B8" s="35" t="s">
-        <x:v>615</x:v>
-      </x:c>
-      <x:c r="C8" s="35" t="s">
-        <x:v>616</x:v>
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="C8" s="35" t="str">
+        <x:v>Runner PIM_EMP gồm 25 case theo ID workbook, setup và cleanup riêng. PIM_PERSONAL/PIM_JOB chưa triển khai.</x:v>
       </x:c>
       <x:c r="D8" s="35" t="s">
-        <x:v>617</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="E8" s="35" t="s">
-        <x:v>618</x:v>
-      </x:c>
-      <x:c r="F8" s="35" t="s">
-        <x:v>606</x:v>
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="F8" s="35" t="str">
+        <x:v>Đã thực hiện PIM_EMP</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="103.5" customHeight="1">
@@ -13934,19 +13773,19 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="B9" s="35" t="s">
-        <x:v>619</x:v>
-      </x:c>
-      <x:c r="C9" s="35" t="s">
-        <x:v>620</x:v>
-      </x:c>
-      <x:c r="D9" s="35" t="s">
-        <x:v>621</x:v>
-      </x:c>
-      <x:c r="E9" s="35" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="F9" s="35" t="s">
-        <x:v>606</x:v>
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="C9" s="35" t="str">
+        <x:v>Playwright kiểm tra validation, tìm kiếm, filter và giá trị sau Save/reload.</x:v>
+      </x:c>
+      <x:c r="D9" s="35" t="str">
+        <x:v>Node assert: so sánh tên/ID, validation và tập kết quả UI.</x:v>
+      </x:c>
+      <x:c r="E9" s="35" t="str">
+        <x:v>Đợi phản hồi Search và UI cập nhật trước khi assertion.</x:v>
+      </x:c>
+      <x:c r="F9" s="35" t="str">
+        <x:v>Đã thực hiện PIM_EMP</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="103.5" customHeight="1">
@@ -13954,19 +13793,19 @@
         <x:v>6.0</x:v>
       </x:c>
       <x:c r="B10" s="35" t="s">
-        <x:v>623</x:v>
-      </x:c>
-      <x:c r="C10" s="35" t="s">
-        <x:v>624</x:v>
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="C10" s="35" t="str">
+        <x:v>Kiểm thử upload JPG/PNG/PDF/ảnh quá cỡ và sorting. Attachment/contract chưa chạy.</x:v>
       </x:c>
       <x:c r="D10" s="35" t="s">
-        <x:v>625</x:v>
-      </x:c>
-      <x:c r="E10" s="35" t="s">
-        <x:v>626</x:v>
-      </x:c>
-      <x:c r="F10" s="35" t="s">
-        <x:v>606</x:v>
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="E10" s="35" t="str">
+        <x:v>Playwright setInputFiles; kiểm tra validation và lưu/reload.</x:v>
+      </x:c>
+      <x:c r="F10" s="35" t="str">
+        <x:v>Đã thực hiện PIM_EMP</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="103.5" customHeight="1">
@@ -13974,19 +13813,19 @@
         <x:v>7.0</x:v>
       </x:c>
       <x:c r="B11" s="35" t="s">
-        <x:v>627</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="C11" s="35" t="s">
-        <x:v>628</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="D11" s="35" t="s">
-        <x:v>629</x:v>
-      </x:c>
-      <x:c r="E11" s="35" t="s">
-        <x:v>630</x:v>
-      </x:c>
-      <x:c r="F11" s="35" t="s">
-        <x:v>606</x:v>
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="E11" s="35" t="str">
+        <x:v>Đợi giá trị form thực, không chỉ phần tử hiện hữu.</x:v>
+      </x:c>
+      <x:c r="F11" s="35" t="str">
+        <x:v>Đã thực hiện PIM_EMP</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="103.5" customHeight="1">
@@ -13994,19 +13833,19 @@
         <x:v>8.0</x:v>
       </x:c>
       <x:c r="B12" s="35" t="s">
-        <x:v>631</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="C12" s="35" t="s">
-        <x:v>632</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="D12" s="35" t="s">
-        <x:v>633</x:v>
-      </x:c>
-      <x:c r="E12" s="35" t="s">
-        <x:v>634</x:v>
-      </x:c>
-      <x:c r="F12" s="35" t="s">
-        <x:v>606</x:v>
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="E12" s="35" t="str">
+        <x:v>Run PIM_EMP_20261021_04; thời gian từng case trong Note và JSON.</x:v>
+      </x:c>
+      <x:c r="F12" s="35" t="str">
+        <x:v>Đã thực hiện PIM_EMP</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="103.5" customHeight="1">
@@ -14014,19 +13853,19 @@
         <x:v>9.0</x:v>
       </x:c>
       <x:c r="B13" s="35" t="s">
-        <x:v>635</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="C13" s="35" t="s">
-        <x:v>636</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D13" s="35" t="s">
-        <x:v>637</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="E13" s="35" t="s">
-        <x:v>638</x:v>
-      </x:c>
-      <x:c r="F13" s="35" t="s">
-        <x:v>606</x:v>
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="F13" s="35" t="str">
+        <x:v>Xem log cleanup</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="103.5" customHeight="1">
@@ -14034,16 +13873,16 @@
         <x:v>10.0</x:v>
       </x:c>
       <x:c r="B14" s="35" t="s">
-        <x:v>639</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="C14" s="35" t="s">
-        <x:v>640</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="D14" s="35" t="s">
-        <x:v>641</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="E14" s="35" t="s">
-        <x:v>642</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="F14" s="35" t="str">
         <x:v>Thiết kế đã rà soát</x:v>
@@ -14067,7 +13906,7 @@
     </x:row>
     <x:row r="17" ht="44" customHeight="1">
       <x:c r="A17" s="2" t="str">
-        <x:v>Tuần đầu: hoàn thiện TestDesign và 25 test case PIM_EMP. Katalon Recorder là lựa chọn của Võ Minh Nhựt; các thành viên tự chọn công cụ. P1/P2 là ưu tiên triển khai; chưa có kết quả thực thi.</x:v>
+        <x:v>PIM_EMP đã chạy bằng Playwright. Hai chức năng PIM_PERSONAL/PIM_JOB chưa chạy, giữ Untested. ID dùng Module_Action_XX; số thứ tự bắt đầu từ 01 trong từng nhóm hành động.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -15099,7 +14938,7 @@
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
       <x:c r="B1" s="3" t="s">
-        <x:v>643</x:v>
+        <x:v>519</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -15144,22 +14983,28 @@
     </x:row>
     <x:row r="5">
       <x:c r="B5" s="35" t="s">
-        <x:v>644</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C5" s="39"/>
-      <x:c r="D5" s="46"/>
+      <x:c r="D5" s="46" t="str">
+        <x:v>PIM_EMP_20261021_04</x:v>
+      </x:c>
       <x:c r="E5" s="36"/>
       <x:c r="F5" s="36"/>
-      <x:c r="G5" s="46"/>
+      <x:c r="G5" s="50" t="d">
+        <x:v>2026-10-21T10:26:20.547Z</x:v>
+      </x:c>
       <x:c r="H5" s="36"/>
       <x:c r="I5" s="36"/>
     </x:row>
     <x:row r="6">
       <x:c r="B6" s="35" t="s">
-        <x:v>645</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C6" s="39"/>
-      <x:c r="D6" s="46"/>
+      <x:c r="D6" s="46" t="str">
+        <x:v>Playwright / Microsoft Edge 155.0.4283.62 (headless)</x:v>
+      </x:c>
       <x:c r="E6" s="36"/>
       <x:c r="F6" s="36"/>
       <x:c r="G6" s="36"/>
@@ -15188,28 +15033,28 @@
     </x:row>
     <x:row r="9" ht="31.5" customHeight="1">
       <x:c r="B9" s="38" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C9" s="38" t="s">
-        <x:v>116</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D9" s="38" t="s">
-        <x:v>120</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E9" s="38" t="s">
-        <x:v>121</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F9" s="38" t="s">
-        <x:v>122</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G9" s="38" t="s">
-        <x:v>123</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H9" s="38" t="s">
-        <x:v>124</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="I9" s="38" t="s">
-        <x:v>646</x:v>
+        <x:v>522</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
@@ -15217,11 +15062,11 @@
         <x:v>1.0</x:v>
       </x:c>
       <x:c r="C10" s="35" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D10" s="35" t="n">
         <x:f>PIM_EMP!A6</x:f>
-        <x:v>0</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E10" s="35" t="n">
         <x:f>PIM_EMP!B6</x:f>
@@ -15229,11 +15074,11 @@
       </x:c>
       <x:c r="F10" s="35" t="n">
         <x:f>PIM_EMP!C6</x:f>
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G10" s="35" t="n">
         <x:f>PIM_EMP!D6</x:f>
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H10" s="35" t="n">
         <x:f>PIM_EMP!E6</x:f>
@@ -15249,7 +15094,7 @@
         <x:v>2.0</x:v>
       </x:c>
       <x:c r="C11" s="35" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D11" s="35" t="n">
         <x:f>PIM_PERSONAL!A6</x:f>
@@ -15281,7 +15126,7 @@
         <x:v>3.0</x:v>
       </x:c>
       <x:c r="C12" s="35" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D12" s="35" t="n">
         <x:f>PIM_JOB!A6</x:f>
@@ -15320,31 +15165,31 @@
     </x:row>
     <x:row r="14">
       <x:c r="B14" s="47" t="s">
-        <x:v>646</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="C14" s="36"/>
       <x:c r="D14" s="47" t="n">
         <x:f t="shared" ref="D14:I14" si="1">SUM(D10:D12)</x:f>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E14" s="47" t="n">
+        <x:f t="shared" si="1">SUM(E10:E12)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="47">
-        <x:f t="shared" si="1"/>
+      <x:c r="F14" s="47" t="n">
+        <x:f t="shared" si="1">SUM(F10:F12)</x:f>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G14" s="47" t="n">
+        <x:f t="shared" si="1">SUM(G10:G12)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H14" s="47" t="n">
+        <x:f t="shared" si="1">SUM(H10:H12)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="47">
-        <x:f t="shared" si="1"/>
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G14" s="47">
-        <x:f t="shared" si="1"/>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H14" s="47">
-        <x:f t="shared" si="1"/>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I14" s="47">
-        <x:f t="shared" si="1"/>
+      <x:c r="I14" s="47" t="n">
+        <x:f t="shared" si="1">SUM(I10:I12)</x:f>
         <x:v>75</x:v>
       </x:c>
     </x:row>
@@ -15370,13 +15215,13 @@
     </x:row>
     <x:row r="17">
       <x:c r="B17" s="35" t="s">
-        <x:v>647</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="C17" s="39"/>
       <x:c r="D17" s="39"/>
       <x:c r="E17" s="48" t="n">
         <x:f>IF(I14=0,"",(D14+E14)/I14)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.30666666666666664</x:v>
       </x:c>
       <x:c r="F17" s="39"/>
       <x:c r="G17" s="2"/>
@@ -15385,13 +15230,13 @@
     </x:row>
     <x:row r="18">
       <x:c r="B18" s="35" t="s">
-        <x:v>648</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="C18" s="39"/>
       <x:c r="D18" s="39"/>
-      <x:c r="E18" s="48" t="str">
+      <x:c r="E18" s="48" t="n">
         <x:f>IF(D14+E14=0,"Chưa thực thi",D14/(D14+E14))</x:f>
-        <x:v>Chưa thực thi</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F18" s="39"/>
       <x:c r="G18" s="2"/>
@@ -15410,7 +15255,7 @@
     </x:row>
     <x:row r="20" ht="39.75" customHeight="1">
       <x:c r="B20" s="2" t="s">
-        <x:v>649</x:v>
+        <x:v>525</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1">
@@ -15423,9 +15268,9 @@
       <x:c r="H21" s="2"/>
       <x:c r="I21" s="2"/>
     </x:row>
-    <x:row r="22" ht="39.75" customHeight="1">
-      <x:c r="B22" s="2" t="s">
-        <x:v>650</x:v>
+    <x:row r="22" ht="65" customHeight="1">
+      <x:c r="B22" s="2" t="str">
+        <x:v>Kết quả PIM_EMP: 23 Passed, 0 Failed, 2 Blocked. PIM_PERSONAL/PIM_JOB: 50 Untested. Log và ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/. Các run trước dùng chẩn đoán script, không cộng dồn vào report.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15.75" customHeight="1">

--- a/docs/test-cases/members/Group01_23130226_VoMinhNhut.xlsx
+++ b/docs/test-cases/members/Group01_23130226_VoMinhNhut.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R6ce442db74254706"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test case List" sheetId="2" r:id="Rcf3bc50c930e48c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TestDesign" sheetId="3" r:id="R5244d612e7a94695"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_EMP" sheetId="4" r:id="Rf177865332a54550"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_PERSONAL" sheetId="5" r:id="Rdf5d619283984c5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_JOB" sheetId="6" r:id="R387e8a31527649b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="7" r:id="R1b3dea0b060f41ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Automation Plan" sheetId="8" r:id="R623cd4ee93ef4295"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Report" sheetId="9" r:id="R53df4e1004b046f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R6d0d11ae6bbf48a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test case List" sheetId="2" r:id="Rb41220be63b54171"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TestDesign" sheetId="3" r:id="R6532fe6029fa4c22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_EMP" sheetId="4" r:id="R65dd86b030be458d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_PERSONAL" sheetId="5" r:id="Rc83fd22ed7d84e85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIM_JOB" sheetId="6" r:id="R229fe1a914024d89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="7" r:id="R9fbcc5d7e76244eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Automation Plan" sheetId="8" r:id="R4919aa0f294747b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Report" sheetId="9" r:id="R995e104dded1496a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -543,11 +543,6 @@
     <x:t xml:space="preserve">Không phụ thuộc TC khác; dùng fixture setup.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_PERSONAL_01
-Positive; Phân vùng tương đương
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">First Name bắt buộc</x:t>
   </x:si>
   <x:si>
@@ -562,11 +557,6 @@
     <x:t xml:space="preserve">First Name hiển thị Required. Không lưu tên rỗng; giá trị cũ còn nguyên sau tải lại.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_PERSONAL_02
-Negative; Phân vùng tương đương
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Last Name bắt buộc</x:t>
   </x:si>
   <x:si>
@@ -595,11 +585,6 @@
     <x:t xml:space="preserve">Lưu nguyên 30 ký tự và không có lỗi giới hạn.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_PERSONAL_02
-Positive; Phân tích giá trị biên
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">First Name vượt giới hạn 30 ký tự</x:t>
   </x:si>
   <x:si>
@@ -614,11 +599,6 @@
     <x:t xml:space="preserve">Có lỗi giới hạn 30 ký tự; không lưu chuỗi vượt giới hạn. Nếu UI chặn nhập, ghi rõ giới hạn thực tế.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_PERSONAL_02
-Negative; Phân tích giá trị biên
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Middle Name vượt giới hạn 30 ký tự</x:t>
   </x:si>
   <x:si>
@@ -655,11 +635,6 @@
     <x:t xml:space="preserve">ID mới 10 ký tự được lưu nguyên và hồ sơ vẫn là F_PERSON.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_PERSONAL_03
-Positive; Phân tích giá trị biên
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Employee Id dài 11 ký tự</x:t>
   </x:si>
   <x:si>
@@ -674,11 +649,6 @@
     <x:t xml:space="preserve">Có lỗi giới hạn 10 ký tự, không lưu ID 11 ký tự.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_PERSONAL_03
-Negative; Phân tích giá trị biên
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Other Id dài 30 ký tự</x:t>
   </x:si>
   <x:si>
@@ -743,11 +713,6 @@
     <x:t xml:space="preserve">Lưu đúng ngày 29/02/2000. Không có lỗi định dạng ngày.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_PERSONAL_04
-Positive; Phân vùng tương đương
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Date of Birth là ngày không tồn tại</x:t>
   </x:si>
   <x:si>
@@ -762,11 +727,6 @@
     <x:t xml:space="preserve">Hiển thị lỗi ngày/định dạng; không lưu ngày 30/02/2000.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_PERSONAL_04
-Negative; Phân vùng tương đương
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">License Expiry Date hợp lệ</x:t>
   </x:si>
   <x:si>
@@ -851,11 +811,6 @@
     <x:t xml:space="preserve">Có đúng một dòng tệp mới với tên và mô tả đã nhập. Tệp tải về đọc được.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_PERSONAL_05
-Positive; Chuyển trạng thái
-Automation: P2</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Không chọn file khi thêm attachment</x:t>
   </x:si>
   <x:si>
@@ -870,11 +825,6 @@
     <x:t xml:space="preserve">Trường file hiển thị Required. Không xuất hiện dòng attachment mới.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_PERSONAL_05
-Negative; Phân vùng tương đương
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Mô tả attachment đúng 200 ký tự</x:t>
   </x:si>
   <x:si>
@@ -889,11 +839,6 @@
     <x:t xml:space="preserve">Attachment được lưu. Mô tả có đủ 200 ký tự, không bị cắt.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_PERSONAL_05
-Positive; Phân tích giá trị biên
-Automation: P2</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Mô tả attachment vượt 200 ký tự</x:t>
   </x:si>
   <x:si>
@@ -908,11 +853,6 @@
     <x:t xml:space="preserve">Có lỗi giới hạn 200 ký tự. Không lưu mô tả vượt giới hạn.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_PERSONAL_05
-Negative; Phân tích giá trị biên
-Automation: P2</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Hủy rồi xác nhận xóa attachment của nhóm</x:t>
   </x:si>
   <x:si>
@@ -927,12 +867,6 @@
     <x:t xml:space="preserve">Sau Cancel, tệp vẫn có. Sau xác nhận xóa, đúng tệp đích biến mất và các tệp khác không thay đổi.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_PERSONAL_05
-Integration; Chuyển trạng thái
-Automation: P2
-Chỉ xóa tệp fixture của nhóm.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Lưu Joined Date hợp lệ</x:t>
   </x:si>
   <x:si>
@@ -947,11 +881,6 @@
     <x:t xml:space="preserve">Joined Date được lưu đúng ngày 01/10/2024.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_01
-Positive; Phân vùng tương đương
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Joined Date không tồn tại</x:t>
   </x:si>
   <x:si>
@@ -966,11 +895,6 @@
     <x:t xml:space="preserve">Có lỗi ngày/định dạng. Không lưu ngày 31/02/2024.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_01
-Negative; Phân vùng tương đương
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Thay đổi Job Title</x:t>
   </x:si>
   <x:si>
@@ -985,11 +909,6 @@
     <x:t xml:space="preserve">Job Title giữ đúng nhãn đã chọn sau tải lại; không thay đổi nhân viên khác.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_02
-Positive; Phân vùng tương đương
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Thay đổi Job Category</x:t>
   </x:si>
   <x:si>
@@ -1060,11 +979,6 @@
     <x:t xml:space="preserve">Ngày và toàn bộ 5 danh mục đều giữ đúng giá trị đã lưu trên F_JOB.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_02
-Integration; Bảng quyết định
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Xóa Joined Date tùy chọn</x:t>
   </x:si>
   <x:si>
@@ -1093,11 +1007,6 @@
     <x:t xml:space="preserve">Hiển thị Start Date, End Date và vùng Contract Details/upload. Không coi thao tác bật là bằng chứng đã lưu hợp đồng.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_03
-Positive; Phân vùng tương đương
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Tắt phần mở rộng hợp đồng không xóa dữ liệu</x:t>
   </x:si>
   <x:si>
@@ -1112,11 +1021,6 @@
     <x:t xml:space="preserve">Phần hợp đồng ẩn rồi hiện. Ngày và tệp vẫn còn khi bật lại. Không tự xóa dữ liệu do thao tác toggle.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_03
-Positive; Chuyển trạng thái
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Hợp đồng có End Date sau Start Date</x:t>
   </x:si>
   <x:si>
@@ -1131,11 +1035,6 @@
     <x:t xml:space="preserve">Lưu đúng hai ngày. End Date sau Start Date, không có lỗi.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_04
-Positive; Bảng quyết định
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">End Date trước Start Date</x:t>
   </x:si>
   <x:si>
@@ -1150,11 +1049,6 @@
     <x:t xml:space="preserve">End Date có lỗi yêu cầu sau Start Date. Không lưu cặp ngày sai.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_04
-Negative; Bảng quyết định
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">End Date bằng Start Date</x:t>
   </x:si>
   <x:si>
@@ -1169,11 +1063,6 @@
     <x:t xml:space="preserve">End Date bị từ chối vì phải sau Start Date (không chấp nhận cùng ngày theo baseline 5.9).</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_04
-Negative; Phân tích giá trị biên
-Automation: P1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Start Date không tồn tại</x:t>
   </x:si>
   <x:si>
@@ -1185,11 +1074,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Có lỗi ngày/định dạng tại Start Date. Không lưu ngày không tồn tại.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_04
-Negative; Phân vùng tương đương
-Automation: P1</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">End Date không tồn tại</x:t>
@@ -1219,11 +1103,6 @@
     <x:t xml:space="preserve">Tên contract_v1.pdf còn sau tải lại. Nội dung tải xuống là hợp đồng mẫu v1.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_05
-Positive; Chuyển trạng thái
-Automation: P2</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Từ chối tệp hợp đồng vượt giới hạn</x:t>
   </x:si>
   <x:si>
@@ -1238,12 +1117,6 @@
     <x:t xml:space="preserve">Có lỗi dung lượng. Tệp hợp đồng cũ không bị thay bằng tệp quá cỡ.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_05
-Negative; Phân tích giá trị biên
-Automation: P2
-Không mặc định giới hạn contract giống ảnh đại diện.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Từ chối loại file hợp đồng không cho phép</x:t>
   </x:si>
   <x:si>
@@ -1258,11 +1131,6 @@
     <x:t xml:space="preserve">Có lỗi loại tệp. Không lưu tệp không được phép, hợp đồng cũ còn nguyên.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_05
-Negative; Phân vùng tương đương
-Automation: P2</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Giữ tệp hợp đồng hiện tại khi đổi ngày</x:t>
   </x:si>
   <x:si>
@@ -1277,11 +1145,6 @@
     <x:t xml:space="preserve">Ngày kết thúc mới được lưu. Tệp vẫn là contract_v1.pdf, nội dung không đổi.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_05
-Integration; Chuyển trạng thái
-Automation: P2</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Thay thế tệp hợp đồng hiện tại</x:t>
   </x:si>
   <x:si>
@@ -1310,11 +1173,6 @@
     <x:t xml:space="preserve">Vùng tệp mới hiển thị Required. Không mất tệp hợp đồng cũ.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_05
-Negative; Bảng quyết định
-Automation: P2</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Xóa riêng tệp hợp đồng hiện tại</x:t>
   </x:si>
   <x:si>
@@ -1329,12 +1187,6 @@
     <x:t xml:space="preserve">Tệp hiện tại được xóa. Hai ngày hợp đồng không bị đổi ngoài ý muốn.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_05
-Positive; Chuyển trạng thái
-Automation: P2
-Chỉ xóa tệp fixture của nhóm.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Thêm attachment tại tab Job</x:t>
   </x:si>
   <x:si>
@@ -1363,11 +1215,6 @@
     <x:t xml:space="preserve">Form thêm đóng. Không có dòng mới với mô tả G01N01 Job cancel.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TD_PIM_JOB_05
-Negative; Chuyển trạng thái
-Automation: P2</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">PIM TEST DATA</x:t>
   </x:si>
   <x:si>
@@ -1638,16 +1485,7 @@
     <x:t xml:space="preserve">ATTACH_LIMIT</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Giá trị hiện tại: điền trước run</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Đọc Max Attachment Size và Allowed File Types tại cấu hình hoặc hint. Ghi giới hạn, MIME và thời điểm.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Tệp quá giới hạn = giới hạn byte +1. Không đổi config dùng chung.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Nếu không đọc được config thì Blocked, không phỏng đoán.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">RESTORE</x:t>
@@ -2604,7 +2442,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G7" s="35" t="str">
-        <x:v>1.2</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="H7" s="2"/>
     </x:row>
@@ -2776,7 +2614,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C19" s="35" t="str">
-        <x:v>Playwright (PIM_EMP); các thành viên tự chọn công cụ</x:v>
+        <x:v>Playwright</x:v>
       </x:c>
       <x:c r="D19" s="39"/>
       <x:c r="E19" s="39"/>
@@ -2811,7 +2649,7 @@
         <x:v>Nội dung tuần này</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>PIM_EMP: Employee List &amp; Add Employee – 25 test case.</x:v>
+        <x:v>Thực thi PIM_PERSONAL và PIM_JOB: 50 test case.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15.75" customHeight="1"/>
@@ -8605,7 +8443,7 @@
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="41" t="n">
         <x:f>COUNTIF($F$9:$F$33,"Passed")</x:f>
-        <x:v>0</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="41" t="n">
         <x:f>COUNTIF($F$9:$F$33,"Failed")</x:f>
@@ -8613,7 +8451,7 @@
       </x:c>
       <x:c r="C6" s="41" t="n">
         <x:f>COUNTIF($F$9:$F$33,"Untested")</x:f>
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="41" t="n">
         <x:f>COUNTIF($F$9:$F$33,"Blocked")</x:f>
@@ -8666,7 +8504,7 @@
         <x:v>60</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="139.5" customHeight="1">
+    <x:row r="9" ht="210" customHeight="1">
       <x:c r="A9" s="42" t="str">
         <x:v>PIM_PERSONAL_Update_01</x:v>
       </x:c>
@@ -8682,588 +8520,848 @@
       <x:c r="E9" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F9" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G9" s="44"/>
-      <x:c r="H9" s="42" t="s">
-        <x:v>169</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="139.5" customHeight="1">
+      <x:c r="F9" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G9" s="44" t="d">
+        <x:v>2026-10-28T03:07:03.617Z</x:v>
+      </x:c>
+      <x:c r="H9" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_01
+Positive; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Cập nhật đầy đủ ba thành phần tên
+Time: 6.36s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_Update_01-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="210" customHeight="1">
       <x:c r="A10" s="45" t="str">
         <x:v>PIM_PERSONAL_Update_02</x:v>
       </x:c>
       <x:c r="B10" s="45" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C10" s="45" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="C10" s="45" t="s">
+      <x:c r="D10" s="45" t="s">
         <x:v>171</x:v>
-      </x:c>
-      <x:c r="D10" s="45" t="s">
-        <x:v>172</x:v>
       </x:c>
       <x:c r="E10" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F10" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G10" s="44"/>
-      <x:c r="H10" s="42" t="s">
-        <x:v>173</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="139.5" customHeight="1">
+      <x:c r="F10" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G10" s="44" t="d">
+        <x:v>2026-10-28T03:07:08.549Z</x:v>
+      </x:c>
+      <x:c r="H10" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_02
+Negative; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: First Name bắt buộc | Required | Saved value unchanged after reopening
+Time: 4.93s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_Update_02-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="210" customHeight="1">
       <x:c r="A11" s="42" t="str">
         <x:v>PIM_PERSONAL_Update_03</x:v>
       </x:c>
       <x:c r="B11" s="42" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C11" s="42" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="D11" s="42" t="s">
         <x:v>174</x:v>
-      </x:c>
-      <x:c r="C11" s="42" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="D11" s="42" t="s">
-        <x:v>176</x:v>
       </x:c>
       <x:c r="E11" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F11" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G11" s="44"/>
-      <x:c r="H11" s="42" t="s">
-        <x:v>173</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="139.5" customHeight="1">
+      <x:c r="F11" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G11" s="44" t="d">
+        <x:v>2026-10-28T03:07:13.578Z</x:v>
+      </x:c>
+      <x:c r="H11" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_02
+Negative; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Last Name bắt buộc | Required | Saved value unchanged after reopening
+Time: 5.03s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_Update_03-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="233" customHeight="1">
       <x:c r="A12" s="45" t="str">
         <x:v>PIM_PERSONAL_Update_04</x:v>
       </x:c>
       <x:c r="B12" s="45" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="C12" s="45" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D12" s="45" t="s">
         <x:v>177</x:v>
-      </x:c>
-      <x:c r="C12" s="45" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="D12" s="45" t="s">
-        <x:v>179</x:v>
       </x:c>
       <x:c r="E12" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F12" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G12" s="44"/>
-      <x:c r="H12" s="42" t="s">
-        <x:v>180</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="139.5" customHeight="1">
+      <x:c r="F12" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G12" s="44" t="d">
+        <x:v>2026-10-28T03:07:19.477Z</x:v>
+      </x:c>
+      <x:c r="H12" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_02
+Positive; Phân tích giá trị biên
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: First Name đúng giới hạn 30 ký tự
+Input:
+value: AAAAAAAAAAAAAAAAAAAAAAAAAAAAAA
+Time: 5.90s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_Update_04-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="259" customHeight="1">
       <x:c r="A13" s="42" t="str">
         <x:v>PIM_PERSONAL_Update_05</x:v>
       </x:c>
       <x:c r="B13" s="42" t="s">
-        <x:v>181</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C13" s="42" t="s">
-        <x:v>182</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="D13" s="42" t="s">
-        <x:v>183</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E13" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F13" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G13" s="44"/>
-      <x:c r="H13" s="42" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="139.5" customHeight="1">
+      <x:c r="F13" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G13" s="44" t="d">
+        <x:v>2026-10-28T03:07:24.518Z</x:v>
+      </x:c>
+      <x:c r="H13" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_02
+Negative; Phân tích giá trị biên
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: First Name vượt giới hạn 30 ký tự | Should not exceed 30 characters | Saved value unchanged after reopening
+Input:
+value: AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA
+Time: 5.04s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_Update_05-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="259" customHeight="1">
       <x:c r="A14" s="45" t="str">
         <x:v>PIM_PERSONAL_Update_06</x:v>
       </x:c>
       <x:c r="B14" s="45" t="s">
-        <x:v>185</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C14" s="45" t="s">
-        <x:v>186</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="D14" s="45" t="s">
-        <x:v>183</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E14" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F14" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G14" s="44"/>
-      <x:c r="H14" s="42" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="139.5" customHeight="1">
+      <x:c r="F14" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G14" s="44" t="d">
+        <x:v>2026-10-28T03:07:29.794Z</x:v>
+      </x:c>
+      <x:c r="H14" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_02
+Negative; Phân tích giá trị biên
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Middle Name vượt giới hạn 30 ký tự | Should not exceed 30 characters | Saved value unchanged after reopening
+Input:
+value: AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA
+Time: 5.27s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_Update_06-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="259" customHeight="1">
       <x:c r="A15" s="42" t="str">
         <x:v>PIM_PERSONAL_Update_07</x:v>
       </x:c>
       <x:c r="B15" s="42" t="s">
-        <x:v>187</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C15" s="42" t="s">
-        <x:v>188</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D15" s="42" t="s">
-        <x:v>183</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E15" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F15" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G15" s="44"/>
-      <x:c r="H15" s="42" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="139.5" customHeight="1">
+      <x:c r="F15" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G15" s="44" t="d">
+        <x:v>2026-10-28T03:07:34.794Z</x:v>
+      </x:c>
+      <x:c r="H15" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_02
+Negative; Phân tích giá trị biên
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Last Name vượt giới hạn 30 ký tự | Should not exceed 30 characters | Saved value unchanged after reopening
+Input:
+value: AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA
+Time: 5.00s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_Update_07-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="210" customHeight="1">
       <x:c r="A16" s="45" t="str">
         <x:v>PIM_PERSONAL_Update_08</x:v>
       </x:c>
       <x:c r="B16" s="45" t="s">
-        <x:v>189</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C16" s="45" t="s">
-        <x:v>190</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="D16" s="45" t="s">
-        <x:v>191</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="E16" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F16" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G16" s="44"/>
-      <x:c r="H16" s="42" t="s">
-        <x:v>192</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="139.5" customHeight="1">
+      <x:c r="F16" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G16" s="44" t="d">
+        <x:v>2026-10-28T03:07:49.309Z</x:v>
+      </x:c>
+      <x:c r="H16" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_03
+Positive; Phân tích giá trị biên
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Employee Id dài 10 ký tự
+Input:
+value: T2536ee39b
+Time: 14.51s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_Update_08-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="246" customHeight="1">
       <x:c r="A17" s="42" t="str">
         <x:v>PIM_PERSONAL_Update_09</x:v>
       </x:c>
       <x:c r="B17" s="42" t="s">
-        <x:v>193</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C17" s="42" t="s">
-        <x:v>194</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="D17" s="42" t="s">
-        <x:v>195</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E17" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F17" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G17" s="44"/>
-      <x:c r="H17" s="42" t="s">
-        <x:v>196</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="139.5" customHeight="1">
+      <x:c r="F17" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G17" s="44" t="d">
+        <x:v>2026-10-28T03:07:54.319Z</x:v>
+      </x:c>
+      <x:c r="H17" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_03
+Negative; Phân tích giá trị biên
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Employee Id dài 11 ký tự | Should not exceed 10 characters | Saved value unchanged after reopening
+Input:
+value: T2536ee39bX
+Time: 5.01s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_Update_09-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="220" customHeight="1">
       <x:c r="A18" s="45" t="str">
         <x:v>PIM_PERSONAL_Update_10</x:v>
       </x:c>
       <x:c r="B18" s="45" t="s">
-        <x:v>197</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C18" s="45" t="s">
-        <x:v>198</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D18" s="45" t="s">
-        <x:v>199</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="E18" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F18" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G18" s="44"/>
-      <x:c r="H18" s="42" t="s">
-        <x:v>192</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="139.5" customHeight="1">
+      <x:c r="F18" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G18" s="44" t="d">
+        <x:v>2026-10-28T03:08:00.257Z</x:v>
+      </x:c>
+      <x:c r="H18" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_03
+Positive; Phân tích giá trị biên
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Other Id dài 30 ký tự
+Input:
+value: BBBBBBBBBBBBBBBBBBBBBBBBBBBBBB
+Time: 5.94s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_Update_10-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="246" customHeight="1">
       <x:c r="A19" s="42" t="str">
         <x:v>PIM_PERSONAL_Update_11</x:v>
       </x:c>
       <x:c r="B19" s="42" t="s">
-        <x:v>200</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C19" s="42" t="s">
-        <x:v>201</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="D19" s="42" t="s">
-        <x:v>202</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="E19" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F19" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G19" s="44"/>
-      <x:c r="H19" s="42" t="s">
-        <x:v>196</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="139.5" customHeight="1">
+      <x:c r="F19" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G19" s="44" t="d">
+        <x:v>2026-10-28T03:08:05.310Z</x:v>
+      </x:c>
+      <x:c r="H19" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_03
+Negative; Phân tích giá trị biên
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Other Id dài 31 ký tự | Should not exceed 30 characters | Saved value unchanged after reopening
+Input:
+value: BBBBBBBBBBBBBBBBBBBBBBBBBBBBBBB
+Time: 5.05s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_Update_11-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="233" customHeight="1">
       <x:c r="A20" s="45" t="str">
         <x:v>PIM_PERSONAL_Update_12</x:v>
       </x:c>
       <x:c r="B20" s="45" t="s">
-        <x:v>203</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C20" s="45" t="s">
-        <x:v>204</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="D20" s="45" t="s">
-        <x:v>199</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="E20" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F20" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G20" s="44"/>
-      <x:c r="H20" s="42" t="s">
-        <x:v>192</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="139.5" customHeight="1">
+      <x:c r="F20" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G20" s="44" t="d">
+        <x:v>2026-10-28T03:08:11.187Z</x:v>
+      </x:c>
+      <x:c r="H20" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_03
+Positive; Phân tích giá trị biên
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Driver's License Number dài 30 ký tự
+Input:
+value: BBBBBBBBBBBBBBBBBBBBBBBBBBBBBB
+Time: 5.88s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_Update_12-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="259" customHeight="1">
       <x:c r="A21" s="42" t="str">
         <x:v>PIM_PERSONAL_Update_13</x:v>
       </x:c>
       <x:c r="B21" s="42" t="s">
-        <x:v>205</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C21" s="42" t="s">
-        <x:v>206</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D21" s="42" t="s">
-        <x:v>202</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="E21" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F21" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G21" s="44"/>
-      <x:c r="H21" s="42" t="s">
-        <x:v>196</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="139.5" customHeight="1">
+      <x:c r="F21" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G21" s="44" t="d">
+        <x:v>2026-10-28T03:08:16.163Z</x:v>
+      </x:c>
+      <x:c r="H21" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_03
+Negative; Phân tích giá trị biên
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Driver's License Number dài 31 ký tự | Should not exceed 30 characters | Saved value unchanged after reopening
+Input:
+value: BBBBBBBBBBBBBBBBBBBBBBBBBBBBBBB
+Time: 4.97s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_Update_13-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="220" customHeight="1">
       <x:c r="A22" s="45" t="str">
         <x:v>PIM_PERSONAL_Update_14</x:v>
       </x:c>
       <x:c r="B22" s="45" t="s">
-        <x:v>207</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C22" s="45" t="s">
-        <x:v>208</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D22" s="45" t="s">
-        <x:v>209</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="E22" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F22" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G22" s="44"/>
-      <x:c r="H22" s="42" t="s">
-        <x:v>210</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="139.5" customHeight="1">
+      <x:c r="F22" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G22" s="44" t="d">
+        <x:v>2026-10-28T03:08:21.974Z</x:v>
+      </x:c>
+      <x:c r="H22" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_04
+Positive; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Date of Birth là ngày nhuận hợp lệ
+Input:
+Date of Birth: 2000-29-02
+Time: 5.81s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_Update_14-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="246" customHeight="1">
       <x:c r="A23" s="42" t="str">
         <x:v>PIM_PERSONAL_Update_15</x:v>
       </x:c>
       <x:c r="B23" s="42" t="s">
-        <x:v>211</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C23" s="42" t="s">
-        <x:v>212</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="D23" s="42" t="s">
-        <x:v>213</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E23" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F23" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G23" s="44"/>
-      <x:c r="H23" s="42" t="s">
-        <x:v>214</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="139.5" customHeight="1">
+      <x:c r="F23" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G23" s="44" t="d">
+        <x:v>2026-10-28T03:08:29.477Z</x:v>
+      </x:c>
+      <x:c r="H23" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_04
+Negative; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Date of Birth là ngày không tồn tại | Should be a valid date in yyyy-dd-mm format | Saved value unchanged after reopening
+Input:
+Date of Birth: 2000-30-02
+Time: 7.50s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_Update_15-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="210" customHeight="1">
       <x:c r="A24" s="45" t="str">
         <x:v>PIM_PERSONAL_Update_16</x:v>
       </x:c>
       <x:c r="B24" s="45" t="s">
-        <x:v>215</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C24" s="45" t="s">
-        <x:v>216</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D24" s="45" t="s">
-        <x:v>217</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E24" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F24" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G24" s="44"/>
-      <x:c r="H24" s="42" t="s">
-        <x:v>210</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="139.5" customHeight="1">
+      <x:c r="F24" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G24" s="44" t="d">
+        <x:v>2026-10-28T03:08:41.006Z</x:v>
+      </x:c>
+      <x:c r="H24" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_04
+Positive; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: License Expiry Date hợp lệ
+Input:
+License Expiry Date: 2030-31-12
+Time: 11.53s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_Update_16-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="246" customHeight="1">
       <x:c r="A25" s="42" t="str">
         <x:v>PIM_PERSONAL_Update_17</x:v>
       </x:c>
       <x:c r="B25" s="42" t="s">
-        <x:v>218</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C25" s="42" t="s">
-        <x:v>219</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="D25" s="42" t="s">
-        <x:v>220</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E25" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F25" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G25" s="44"/>
-      <x:c r="H25" s="42" t="s">
-        <x:v>214</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="139.5" customHeight="1">
+      <x:c r="F25" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G25" s="44" t="d">
+        <x:v>2026-10-28T03:08:56.398Z</x:v>
+      </x:c>
+      <x:c r="H25" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_04
+Negative; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: License Expiry Date không hợp lệ | Should be a valid date in yyyy-dd-mm format | Saved value unchanged after reopening
+Input:
+License Expiry Date: 2030-31-04
+Time: 15.39s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_Update_17-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="210" customHeight="1">
       <x:c r="A26" s="45" t="str">
         <x:v>PIM_PERSONAL_Update_18</x:v>
       </x:c>
       <x:c r="B26" s="45" t="s">
-        <x:v>221</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C26" s="45" t="s">
-        <x:v>222</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="D26" s="45" t="s">
-        <x:v>223</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E26" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F26" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G26" s="44"/>
-      <x:c r="H26" s="42" t="s">
-        <x:v>169</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="139.5" customHeight="1">
+      <x:c r="F26" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G26" s="44" t="d">
+        <x:v>2026-10-28T03:09:12.002Z</x:v>
+      </x:c>
+      <x:c r="H26" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_01
+Positive; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Thay đổi Nationality
+Input:
+Nationality: Afghan
+Time: 15.60s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_Update_18-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="210" customHeight="1">
       <x:c r="A27" s="42" t="str">
         <x:v>PIM_PERSONAL_Update_19</x:v>
       </x:c>
       <x:c r="B27" s="42" t="s">
-        <x:v>224</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C27" s="42" t="s">
-        <x:v>225</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="D27" s="42" t="s">
-        <x:v>226</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="E27" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F27" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G27" s="44"/>
-      <x:c r="H27" s="42" t="s">
-        <x:v>169</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="139.5" customHeight="1">
+      <x:c r="F27" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G27" s="44" t="d">
+        <x:v>2026-10-28T03:09:19.261Z</x:v>
+      </x:c>
+      <x:c r="H27" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_01
+Positive; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Thay đổi Marital Status
+Input:
+Marital Status: Married
+Time: 7.26s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_Update_19-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="210" customHeight="1">
       <x:c r="A28" s="45" t="str">
         <x:v>PIM_PERSONAL_Update_20</x:v>
       </x:c>
       <x:c r="B28" s="45" t="s">
-        <x:v>227</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C28" s="45" t="s">
-        <x:v>228</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D28" s="45" t="s">
-        <x:v>229</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E28" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F28" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G28" s="44"/>
-      <x:c r="H28" s="42" t="s">
-        <x:v>169</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="139.5" customHeight="1">
+      <x:c r="F28" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G28" s="44" t="d">
+        <x:v>2026-10-28T03:09:25.120Z</x:v>
+      </x:c>
+      <x:c r="H28" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_01
+Positive; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Thay đổi Gender
+Input:
+Gender: Female
+Time: 5.86s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_Update_20-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="210" customHeight="1">
       <x:c r="A29" s="42" t="str">
         <x:v>PIM_PERSONAL_CreateAttachment_01</x:v>
       </x:c>
       <x:c r="B29" s="42" t="s">
-        <x:v>230</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C29" s="42" t="s">
-        <x:v>231</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="D29" s="42" t="s">
-        <x:v>232</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E29" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F29" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G29" s="44"/>
-      <x:c r="H29" s="42" t="s">
-        <x:v>233</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="139.5" customHeight="1">
+      <x:c r="F29" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G29" s="44" t="d">
+        <x:v>2026-10-28T03:09:34.459Z</x:v>
+      </x:c>
+      <x:c r="H29" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_05
+Positive; Chuyển trạng thái
+Automation: P2
+Playwright / Edge 156.0.4314.50
+Actual: Thêm attachment hợp lệ vào Personal Details
+Time: 9.34s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_CreateAttachment_01-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="210" customHeight="1">
       <x:c r="A30" s="45" t="str">
         <x:v>PIM_PERSONAL_CreateAttachment_02</x:v>
       </x:c>
       <x:c r="B30" s="45" t="s">
-        <x:v>234</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C30" s="45" t="s">
-        <x:v>235</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="D30" s="45" t="s">
-        <x:v>236</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E30" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F30" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G30" s="44"/>
-      <x:c r="H30" s="42" t="s">
-        <x:v>237</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="156" customHeight="1">
+      <x:c r="F30" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G30" s="44" t="d">
+        <x:v>2026-10-28T03:09:39.644Z</x:v>
+      </x:c>
+      <x:c r="H30" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_05
+Negative; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Không chọn file khi thêm attachment
+Time: 5.18s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_CreateAttachment_02-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="210" customHeight="1">
       <x:c r="A31" s="42" t="str">
         <x:v>PIM_PERSONAL_CreateAttachment_03</x:v>
       </x:c>
       <x:c r="B31" s="42" t="s">
-        <x:v>238</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C31" s="42" t="s">
-        <x:v>239</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="D31" s="42" t="s">
-        <x:v>240</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E31" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F31" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G31" s="44"/>
-      <x:c r="H31" s="42" t="s">
-        <x:v>241</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="156" customHeight="1">
+      <x:c r="F31" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G31" s="44" t="d">
+        <x:v>2026-10-28T03:09:48.631Z</x:v>
+      </x:c>
+      <x:c r="H31" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_05
+Positive; Phân tích giá trị biên
+Automation: P2
+Playwright / Edge 156.0.4314.50
+Actual: Mô tả attachment đúng 200 ký tự
+Time: 8.99s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_CreateAttachment_03-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="210" customHeight="1">
       <x:c r="A32" s="45" t="str">
         <x:v>PIM_PERSONAL_CreateAttachment_04</x:v>
       </x:c>
       <x:c r="B32" s="45" t="s">
-        <x:v>242</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C32" s="45" t="s">
-        <x:v>243</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="D32" s="45" t="s">
-        <x:v>244</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="E32" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F32" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G32" s="44"/>
-      <x:c r="H32" s="42" t="s">
-        <x:v>245</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="139.5" customHeight="1">
+      <x:c r="F32" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G32" s="44" t="d">
+        <x:v>2026-10-28T03:09:53.738Z</x:v>
+      </x:c>
+      <x:c r="H32" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_05
+Negative; Phân tích giá trị biên
+Automation: P2
+Playwright / Edge 156.0.4314.50
+Actual: Mô tả attachment vượt 200 ký tự
+Time: 5.11s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_CreateAttachment_04-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="210" customHeight="1">
       <x:c r="A33" s="42" t="str">
         <x:v>PIM_PERSONAL_DeleteAttachment_01</x:v>
       </x:c>
       <x:c r="B33" s="42" t="s">
-        <x:v>246</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C33" s="42" t="s">
-        <x:v>247</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="D33" s="42" t="s">
-        <x:v>248</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E33" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F33" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G33" s="44"/>
-      <x:c r="H33" s="42" t="s">
-        <x:v>249</x:v>
+      <x:c r="F33" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G33" s="44" t="d">
+        <x:v>2026-10-28T03:10:05.740Z</x:v>
+      </x:c>
+      <x:c r="H33" s="42" t="str">
+        <x:v>TD_PIM_PERSONAL_05
+Integration; Chuyển trạng thái
+Automation: P2
+Chỉ xóa tệp fixture của nhóm.
+Playwright / Edge 156.0.4314.50
+Actual: Hủy rồi xác nhận xóa attachment của nhóm
+Time: 12.00s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-06-34-596Z/screenshots/PIM_PERSONAL_DeleteAttachment_01-result.png</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15.75" customHeight="1"/>
@@ -10365,7 +10463,7 @@
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="41" t="n">
         <x:f>COUNTIF($F$9:$F$33,"Passed")</x:f>
-        <x:v>0</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="41" t="n">
         <x:f>COUNTIF($F$9:$F$33,"Failed")</x:f>
@@ -10373,7 +10471,7 @@
       </x:c>
       <x:c r="C6" s="41" t="n">
         <x:f>COUNTIF($F$9:$F$33,"Untested")</x:f>
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="41" t="n">
         <x:f>COUNTIF($F$9:$F$33,"Blocked")</x:f>
@@ -10426,604 +10524,874 @@
         <x:v>60</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="139.5" customHeight="1">
+    <x:row r="9" ht="210" customHeight="1">
       <x:c r="A9" s="42" t="str">
         <x:v>PIM_JOB_UpdateJob_01</x:v>
       </x:c>
       <x:c r="B9" s="42" t="s">
-        <x:v>250</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C9" s="42" t="s">
-        <x:v>251</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D9" s="42" t="s">
-        <x:v>252</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E9" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F9" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G9" s="44"/>
-      <x:c r="H9" s="42" t="s">
-        <x:v>253</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="139.5" customHeight="1">
+      <x:c r="F9" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G9" s="44" t="d">
+        <x:v>2026-10-28T03:14:59.490Z</x:v>
+      </x:c>
+      <x:c r="H9" s="42" t="str">
+        <x:v>TD_PIM_JOB_01
+Positive; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Lưu Joined Date hợp lệ
+Input:
+JoinedDate: 2024-01-10
+Time: 7.10s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_UpdateJob_01-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="246" customHeight="1">
       <x:c r="A10" s="45" t="str">
         <x:v>PIM_JOB_UpdateJob_02</x:v>
       </x:c>
       <x:c r="B10" s="45" t="s">
-        <x:v>254</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C10" s="45" t="s">
-        <x:v>255</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="D10" s="45" t="s">
-        <x:v>256</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="E10" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F10" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G10" s="44"/>
-      <x:c r="H10" s="42" t="s">
-        <x:v>257</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="139.5" customHeight="1">
+      <x:c r="F10" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G10" s="44" t="d">
+        <x:v>2026-10-28T03:15:04.751Z</x:v>
+      </x:c>
+      <x:c r="H10" s="42" t="str">
+        <x:v>TD_PIM_JOB_01
+Negative; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Joined Date không tồn tại | Should be a valid date in yyyy-dd-mm format | Saved value unchanged after reopening
+Input:
+JoinedDate: 2024-31-02
+Time: 5.26s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_UpdateJob_02-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="210" customHeight="1">
       <x:c r="A11" s="42" t="str">
         <x:v>PIM_JOB_UpdateJob_03</x:v>
       </x:c>
       <x:c r="B11" s="42" t="s">
-        <x:v>258</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C11" s="42" t="s">
-        <x:v>259</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D11" s="42" t="s">
-        <x:v>260</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E11" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F11" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G11" s="44"/>
-      <x:c r="H11" s="42" t="s">
-        <x:v>261</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="139.5" customHeight="1">
+      <x:c r="F11" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G11" s="44" t="d">
+        <x:v>2026-10-28T03:15:11.313Z</x:v>
+      </x:c>
+      <x:c r="H11" s="42" t="str">
+        <x:v>TD_PIM_JOB_02
+Positive; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Thay đổi Job Title
+Input:
+Job Title: Account Assistant
+Time: 6.56s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_UpdateJob_03-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="210" customHeight="1">
       <x:c r="A12" s="45" t="str">
         <x:v>PIM_JOB_UpdateJob_04</x:v>
       </x:c>
       <x:c r="B12" s="45" t="s">
-        <x:v>262</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C12" s="45" t="s">
-        <x:v>263</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="D12" s="45" t="s">
-        <x:v>264</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="E12" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F12" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G12" s="44"/>
-      <x:c r="H12" s="42" t="s">
-        <x:v>261</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="139.5" customHeight="1">
+      <x:c r="F12" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G12" s="44" t="d">
+        <x:v>2026-10-28T03:15:18.205Z</x:v>
+      </x:c>
+      <x:c r="H12" s="42" t="str">
+        <x:v>TD_PIM_JOB_02
+Positive; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Thay đổi Job Category
+Input:
+Job Category: Craft Workers
+Time: 6.89s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_UpdateJob_04-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="210" customHeight="1">
       <x:c r="A13" s="42" t="str">
         <x:v>PIM_JOB_UpdateJob_05</x:v>
       </x:c>
       <x:c r="B13" s="42" t="s">
-        <x:v>265</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C13" s="42" t="s">
-        <x:v>266</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D13" s="42" t="s">
-        <x:v>267</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="E13" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F13" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G13" s="44"/>
-      <x:c r="H13" s="42" t="s">
-        <x:v>261</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="139.5" customHeight="1">
+      <x:c r="F13" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G13" s="44" t="d">
+        <x:v>2026-10-28T03:15:24.592Z</x:v>
+      </x:c>
+      <x:c r="H13" s="42" t="str">
+        <x:v>TD_PIM_JOB_02
+Positive; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Thay đổi Sub Unit
+Input:
+Sub Unit: Administration
+Time: 6.39s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_UpdateJob_05-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="210" customHeight="1">
       <x:c r="A14" s="45" t="str">
         <x:v>PIM_JOB_UpdateJob_06</x:v>
       </x:c>
       <x:c r="B14" s="45" t="s">
-        <x:v>268</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C14" s="45" t="s">
-        <x:v>269</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="D14" s="45" t="s">
-        <x:v>270</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="E14" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F14" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G14" s="44"/>
-      <x:c r="H14" s="42" t="s">
-        <x:v>261</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="139.5" customHeight="1">
+      <x:c r="F14" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G14" s="44" t="d">
+        <x:v>2026-10-28T03:15:31.153Z</x:v>
+      </x:c>
+      <x:c r="H14" s="42" t="str">
+        <x:v>TD_PIM_JOB_02
+Positive; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Thay đổi Location
+Input:
+Location: Canadian Regional HQ
+Time: 6.56s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_UpdateJob_06-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="210" customHeight="1">
       <x:c r="A15" s="42" t="str">
         <x:v>PIM_JOB_UpdateJob_07</x:v>
       </x:c>
       <x:c r="B15" s="42" t="s">
-        <x:v>271</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C15" s="42" t="s">
-        <x:v>272</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="D15" s="42" t="s">
-        <x:v>273</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="E15" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F15" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G15" s="44"/>
-      <x:c r="H15" s="42" t="s">
-        <x:v>261</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="139.5" customHeight="1">
+      <x:c r="F15" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G15" s="44" t="d">
+        <x:v>2026-10-28T03:15:37.764Z</x:v>
+      </x:c>
+      <x:c r="H15" s="42" t="str">
+        <x:v>TD_PIM_JOB_02
+Positive; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Thay đổi Employment Status
+Input:
+Employment Status: Freelance
+Time: 6.61s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_UpdateJob_07-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="285" customHeight="1">
       <x:c r="A16" s="45" t="str">
         <x:v>PIM_JOB_UpdateJob_08</x:v>
       </x:c>
       <x:c r="B16" s="45" t="s">
-        <x:v>274</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C16" s="45" t="s">
-        <x:v>275</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="D16" s="45" t="s">
-        <x:v>276</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="E16" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F16" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G16" s="44"/>
-      <x:c r="H16" s="42" t="s">
-        <x:v>277</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="139.5" customHeight="1">
+      <x:c r="F16" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G16" s="44" t="d">
+        <x:v>2026-10-28T03:15:47.340Z</x:v>
+      </x:c>
+      <x:c r="H16" s="42" t="str">
+        <x:v>TD_PIM_JOB_02
+Integration; Bảng quyết định
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Lưu đồng thời các trường Job Details
+Input:
+Job Title: Automaton Tester
+Job Category: Laborers and Helpers
+Sub Unit: Engineering
+Location: HQ - CA, USA
+Employment Status: Full-Time Contract
+Time: 9.57s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_UpdateJob_08-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="210" customHeight="1">
       <x:c r="A17" s="42" t="str">
         <x:v>PIM_JOB_UpdateJob_09</x:v>
       </x:c>
       <x:c r="B17" s="42" t="s">
-        <x:v>278</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C17" s="42" t="s">
-        <x:v>279</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="D17" s="42" t="s">
-        <x:v>280</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="E17" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F17" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G17" s="44"/>
-      <x:c r="H17" s="42" t="s">
-        <x:v>253</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="139.5" customHeight="1">
+      <x:c r="F17" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G17" s="44" t="d">
+        <x:v>2026-10-28T03:15:58.927Z</x:v>
+      </x:c>
+      <x:c r="H17" s="42" t="str">
+        <x:v>TD_PIM_JOB_01
+Positive; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Xóa Joined Date tùy chọn
+Input:
+JoinedDate: 
+Time: 11.59s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_UpdateJob_09-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="210" customHeight="1">
       <x:c r="A18" s="45" t="str">
         <x:v>PIM_JOB_ToggleContract_01</x:v>
       </x:c>
       <x:c r="B18" s="45" t="s">
-        <x:v>281</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C18" s="45" t="s">
-        <x:v>282</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="D18" s="45" t="s">
-        <x:v>283</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E18" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F18" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G18" s="44"/>
-      <x:c r="H18" s="42" t="s">
-        <x:v>284</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="139.5" customHeight="1">
+      <x:c r="F18" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G18" s="44" t="d">
+        <x:v>2026-10-28T03:16:02.811Z</x:v>
+      </x:c>
+      <x:c r="H18" s="42" t="str">
+        <x:v>TD_PIM_JOB_03
+Positive; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Bật hiển thị Employment Contract Details
+Time: 3.88s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_ToggleContract_01-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="210" customHeight="1">
       <x:c r="A19" s="42" t="str">
         <x:v>PIM_JOB_ToggleContract_02</x:v>
       </x:c>
       <x:c r="B19" s="42" t="s">
-        <x:v>285</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C19" s="42" t="s">
-        <x:v>286</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D19" s="42" t="s">
-        <x:v>287</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="E19" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F19" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G19" s="44"/>
-      <x:c r="H19" s="42" t="s">
-        <x:v>288</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="139.5" customHeight="1">
+      <x:c r="F19" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G19" s="44" t="d">
+        <x:v>2026-10-28T03:16:14.130Z</x:v>
+      </x:c>
+      <x:c r="H19" s="42" t="str">
+        <x:v>TD_PIM_JOB_03
+Positive; Chuyển trạng thái
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Tắt phần mở rộng hợp đồng không xóa dữ liệu
+Time: 11.32s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_ToggleContract_02-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="233" customHeight="1">
       <x:c r="A20" s="45" t="str">
         <x:v>PIM_JOB_UpdateContract_01</x:v>
       </x:c>
       <x:c r="B20" s="45" t="s">
-        <x:v>289</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C20" s="45" t="s">
-        <x:v>290</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="D20" s="45" t="s">
-        <x:v>291</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="E20" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F20" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G20" s="44"/>
-      <x:c r="H20" s="42" t="s">
-        <x:v>292</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="139.5" customHeight="1">
+      <x:c r="F20" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G20" s="44" t="d">
+        <x:v>2026-10-28T03:16:22.733Z</x:v>
+      </x:c>
+      <x:c r="H20" s="42" t="str">
+        <x:v>TD_PIM_JOB_04
+Positive; Bảng quyết định
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Hợp đồng có End Date sau Start Date
+Input:
+start: 2026-01-01
+end: 2026-31-12
+Time: 8.60s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_UpdateContract_01-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="246" customHeight="1">
       <x:c r="A21" s="42" t="str">
         <x:v>PIM_JOB_UpdateContract_02</x:v>
       </x:c>
       <x:c r="B21" s="42" t="s">
-        <x:v>293</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C21" s="42" t="s">
-        <x:v>294</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D21" s="42" t="s">
-        <x:v>295</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="E21" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F21" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G21" s="44"/>
-      <x:c r="H21" s="42" t="s">
-        <x:v>296</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="139.5" customHeight="1">
+      <x:c r="F21" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G21" s="44" t="d">
+        <x:v>2026-10-28T03:16:30.004Z</x:v>
+      </x:c>
+      <x:c r="H21" s="42" t="str">
+        <x:v>TD_PIM_JOB_04
+Negative; Bảng quyết định
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: End Date trước Start Date | End date should be after Start date
+Input:
+start: 2026-01-01
+end: 2025-31-12
+Time: 7.27s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_UpdateContract_02-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="233" customHeight="1">
       <x:c r="A22" s="45" t="str">
         <x:v>PIM_JOB_UpdateContract_03</x:v>
       </x:c>
       <x:c r="B22" s="45" t="s">
-        <x:v>297</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C22" s="45" t="s">
-        <x:v>298</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="D22" s="45" t="s">
-        <x:v>299</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="E22" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F22" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G22" s="44"/>
-      <x:c r="H22" s="42" t="s">
-        <x:v>300</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="139.5" customHeight="1">
+      <x:c r="F22" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G22" s="44" t="d">
+        <x:v>2026-10-28T03:16:37.258Z</x:v>
+      </x:c>
+      <x:c r="H22" s="42" t="str">
+        <x:v>TD_PIM_JOB_04
+Negative; Phân tích giá trị biên
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: End Date bằng Start Date | End date should be after Start date
+Input:
+start: 2026-01-01
+end: 2026-01-01
+Time: 7.25s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_UpdateContract_03-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="246" customHeight="1">
       <x:c r="A23" s="42" t="str">
         <x:v>PIM_JOB_UpdateContract_04</x:v>
       </x:c>
       <x:c r="B23" s="42" t="s">
-        <x:v>301</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C23" s="42" t="s">
-        <x:v>302</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D23" s="42" t="s">
-        <x:v>303</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="E23" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F23" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G23" s="44"/>
-      <x:c r="H23" s="42" t="s">
-        <x:v>304</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="139.5" customHeight="1">
+      <x:c r="F23" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G23" s="44" t="d">
+        <x:v>2026-10-28T03:16:44.973Z</x:v>
+      </x:c>
+      <x:c r="H23" s="42" t="str">
+        <x:v>TD_PIM_JOB_04
+Negative; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: Start Date không tồn tại | Should be a valid date in yyyy-dd-mm format
+Input:
+start: 2026-31-02
+end: 2026-31-12
+Time: 7.71s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_UpdateContract_04-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="246" customHeight="1">
       <x:c r="A24" s="45" t="str">
         <x:v>PIM_JOB_UpdateContract_05</x:v>
       </x:c>
       <x:c r="B24" s="45" t="s">
-        <x:v>305</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="C24" s="45" t="s">
-        <x:v>306</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="D24" s="45" t="s">
-        <x:v>307</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="E24" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F24" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G24" s="44"/>
-      <x:c r="H24" s="42" t="s">
-        <x:v>304</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="139.5" customHeight="1">
+      <x:c r="F24" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G24" s="44" t="d">
+        <x:v>2026-10-28T03:16:52.462Z</x:v>
+      </x:c>
+      <x:c r="H24" s="42" t="str">
+        <x:v>TD_PIM_JOB_04
+Negative; Phân vùng tương đương
+Automation: P1
+Playwright / Edge 156.0.4314.50
+Actual: End Date không tồn tại | Should be a valid date in yyyy-dd-mm format
+Input:
+start: 2026-01-01
+end: 2026-31-04
+Time: 7.49s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_UpdateContract_05-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="210" customHeight="1">
       <x:c r="A25" s="42" t="str">
         <x:v>PIM_JOB_UploadContract_01</x:v>
       </x:c>
       <x:c r="B25" s="42" t="s">
-        <x:v>308</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C25" s="42" t="s">
-        <x:v>309</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D25" s="42" t="s">
-        <x:v>310</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="E25" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F25" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G25" s="44"/>
-      <x:c r="H25" s="42" t="s">
-        <x:v>311</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="141.75" customHeight="1">
+      <x:c r="F25" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G25" s="44" t="d">
+        <x:v>2026-10-28T03:17:15.431Z</x:v>
+      </x:c>
+      <x:c r="H25" s="42" t="str">
+        <x:v>TD_PIM_JOB_05
+Positive; Chuyển trạng thái
+Automation: P2
+Playwright / Edge 156.0.4314.50
+Actual: Tải tệp hợp đồng PDF hợp lệ
+Time: 22.97s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_UploadContract_01-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="272" customHeight="1">
       <x:c r="A26" s="45" t="str">
         <x:v>PIM_JOB_UploadContract_02</x:v>
       </x:c>
       <x:c r="B26" s="45" t="s">
-        <x:v>312</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C26" s="45" t="s">
-        <x:v>313</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D26" s="45" t="s">
-        <x:v>314</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="E26" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F26" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G26" s="44"/>
-      <x:c r="H26" s="42" t="s">
-        <x:v>315</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="141.75" customHeight="1">
+      <x:c r="F26" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G26" s="44" t="d">
+        <x:v>2026-10-28T03:17:32.040Z</x:v>
+      </x:c>
+      <x:c r="H26" s="42" t="str">
+        <x:v>TD_PIM_JOB_05
+Negative; Phân tích giá trị biên
+Automation: P2
+Không mặc định giới hạn contract giống ảnh đại diện.
+Playwright / Edge 156.0.4314.50
+Actual: Từ chối tệp hợp đồng vượt giới hạn | Attachment Size Exceeded
+Input:
+hint: Accepts up to 1MB
+size: 1048577
+limit: 1048576
+Time: 16.61s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_UploadContract_02-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="233" customHeight="1">
       <x:c r="A27" s="42" t="str">
         <x:v>PIM_JOB_UploadContract_03</x:v>
       </x:c>
       <x:c r="B27" s="42" t="s">
-        <x:v>316</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C27" s="42" t="s">
-        <x:v>317</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D27" s="42" t="s">
-        <x:v>318</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="E27" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F27" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G27" s="44"/>
-      <x:c r="H27" s="42" t="s">
-        <x:v>319</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="139.5" customHeight="1">
+      <x:c r="F27" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G27" s="44" t="d">
+        <x:v>2026-10-28T03:17:47.868Z</x:v>
+      </x:c>
+      <x:c r="H27" s="42" t="str">
+        <x:v>TD_PIM_JOB_05
+Negative; Phân vùng tương đương
+Automation: P2
+Playwright / Edge 156.0.4314.50
+Actual: Từ chối loại file hợp đồng không cho phép | File type not allowed
+Input:
+filename: contract_disallowed.bin
+Time: 15.83s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_UploadContract_03-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="210" customHeight="1">
       <x:c r="A28" s="45" t="str">
         <x:v>PIM_JOB_KeepContract_01</x:v>
       </x:c>
       <x:c r="B28" s="45" t="s">
-        <x:v>320</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="C28" s="45" t="s">
-        <x:v>321</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="D28" s="45" t="s">
-        <x:v>322</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="E28" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F28" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G28" s="44"/>
-      <x:c r="H28" s="42" t="s">
-        <x:v>323</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="139.5" customHeight="1">
+      <x:c r="F28" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G28" s="44" t="d">
+        <x:v>2026-10-28T03:18:05.591Z</x:v>
+      </x:c>
+      <x:c r="H28" s="42" t="str">
+        <x:v>TD_PIM_JOB_05
+Integration; Chuyển trạng thái
+Automation: P2
+Playwright / Edge 156.0.4314.50
+Actual: Giữ tệp hợp đồng hiện tại khi đổi ngày
+Time: 17.72s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_KeepContract_01-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="210" customHeight="1">
       <x:c r="A29" s="42" t="str">
         <x:v>PIM_JOB_ReplaceContract_01</x:v>
       </x:c>
       <x:c r="B29" s="42" t="s">
-        <x:v>324</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C29" s="42" t="s">
-        <x:v>325</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="D29" s="42" t="s">
-        <x:v>326</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="E29" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F29" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G29" s="44"/>
-      <x:c r="H29" s="42" t="s">
-        <x:v>311</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="139.5" customHeight="1">
+      <x:c r="F29" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G29" s="44" t="d">
+        <x:v>2026-10-28T03:18:23.659Z</x:v>
+      </x:c>
+      <x:c r="H29" s="42" t="str">
+        <x:v>TD_PIM_JOB_05
+Positive; Chuyển trạng thái
+Automation: P2
+Playwright / Edge 156.0.4314.50
+Actual: Thay thế tệp hợp đồng hiện tại
+Time: 18.07s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_ReplaceContract_01-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="210" customHeight="1">
       <x:c r="A30" s="45" t="str">
         <x:v>PIM_JOB_ReplaceContract_02</x:v>
       </x:c>
       <x:c r="B30" s="45" t="s">
-        <x:v>327</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C30" s="45" t="s">
-        <x:v>328</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="D30" s="45" t="s">
-        <x:v>329</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="E30" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F30" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G30" s="44"/>
-      <x:c r="H30" s="42" t="s">
-        <x:v>330</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="139.5" customHeight="1">
+      <x:c r="F30" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G30" s="44" t="d">
+        <x:v>2026-10-28T03:19:03.952Z</x:v>
+      </x:c>
+      <x:c r="H30" s="42" t="str">
+        <x:v>TD_PIM_JOB_05
+Negative; Bảng quyết định
+Automation: P2
+Playwright / Edge 156.0.4314.50
+Actual: Replace Current nhưng không chọn tệp mới | Required
+Time: 40.29s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_ReplaceContract_02-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="210" customHeight="1">
       <x:c r="A31" s="42" t="str">
         <x:v>PIM_JOB_DeleteContract_01</x:v>
       </x:c>
       <x:c r="B31" s="42" t="s">
-        <x:v>331</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="C31" s="42" t="s">
-        <x:v>332</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="D31" s="42" t="s">
-        <x:v>333</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="E31" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F31" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G31" s="44"/>
-      <x:c r="H31" s="42" t="s">
-        <x:v>334</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="139.5" customHeight="1">
+      <x:c r="F31" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G31" s="44" t="d">
+        <x:v>2026-10-28T03:19:37.819Z</x:v>
+      </x:c>
+      <x:c r="H31" s="42" t="str">
+        <x:v>TD_PIM_JOB_05
+Positive; Chuyển trạng thái
+Automation: P2
+Chỉ xóa tệp fixture của nhóm.
+Playwright / Edge 156.0.4314.50
+Actual: Xóa riêng tệp hợp đồng hiện tại
+Time: 33.87s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_DeleteContract_01-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="210" customHeight="1">
       <x:c r="A32" s="45" t="str">
         <x:v>PIM_JOB_CreateAttachment_01</x:v>
       </x:c>
       <x:c r="B32" s="45" t="s">
-        <x:v>335</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C32" s="45" t="s">
-        <x:v>336</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="D32" s="45" t="s">
-        <x:v>337</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="E32" s="45" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F32" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G32" s="44"/>
-      <x:c r="H32" s="42" t="s">
-        <x:v>311</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="139.5" customHeight="1">
+      <x:c r="F32" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G32" s="44" t="d">
+        <x:v>2026-10-28T03:19:54.952Z</x:v>
+      </x:c>
+      <x:c r="H32" s="42" t="str">
+        <x:v>TD_PIM_JOB_05
+Positive; Chuyển trạng thái
+Automation: P2
+Playwright / Edge 156.0.4314.50
+Actual: Thêm attachment tại tab Job
+Time: 17.13s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_CreateAttachment_01-result.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="210" customHeight="1">
       <x:c r="A33" s="42" t="str">
         <x:v>PIM_JOB_CancelAttachment_01</x:v>
       </x:c>
       <x:c r="B33" s="42" t="s">
-        <x:v>338</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C33" s="42" t="s">
-        <x:v>339</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="D33" s="42" t="s">
-        <x:v>340</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="E33" s="42" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F33" s="43" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G33" s="44"/>
-      <x:c r="H33" s="42" t="s">
-        <x:v>341</x:v>
+      <x:c r="F33" s="43" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G33" s="44" t="d">
+        <x:v>2026-10-28T03:20:01.794Z</x:v>
+      </x:c>
+      <x:c r="H33" s="42" t="str">
+        <x:v>TD_PIM_JOB_05
+Negative; Chuyển trạng thái
+Automation: P2
+Playwright / Edge 156.0.4314.50
+Actual: Hủy thêm attachment tại tab Job
+Time: 6.84s
+Log: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/results.json
+Ảnh: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/screenshots/PIM_JOB_CancelAttachment_01-result.png</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15.75" customHeight="1"/>
@@ -12053,7 +12421,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="3" t="s">
-        <x:v>342</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -12066,59 +12434,59 @@
     </x:row>
     <x:row r="4" ht="31.5" customHeight="1">
       <x:c r="A4" s="38" t="s">
-        <x:v>343</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B4" s="38" t="s">
-        <x:v>344</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="C4" s="38" t="s">
-        <x:v>345</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="D4" s="38" t="s">
-        <x:v>346</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="E4" s="38" t="s">
-        <x:v>347</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="F4" s="38" t="s">
-        <x:v>348</x:v>
+        <x:v>318</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="109.5" customHeight="1">
       <x:c r="A5" s="35" t="s">
-        <x:v>349</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B5" s="35" t="s">
-        <x:v>350</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C5" s="35" t="s">
-        <x:v>351</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="D5" s="35" t="s">
-        <x:v>352</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="E5" s="35" t="s">
-        <x:v>353</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="F5" s="35" t="s">
-        <x:v>354</x:v>
+        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="109.5" customHeight="1">
       <x:c r="A6" s="35" t="s">
-        <x:v>355</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B6" s="35" t="s">
-        <x:v>356</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C6" s="35" t="s">
-        <x:v>357</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="D6" s="35" t="s">
-        <x:v>358</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E6" s="35" t="s">
-        <x:v>359</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="F6" s="35" t="str">
         <x:v>Tài khoản demo công khai; không thay mật khẩu.</x:v>
@@ -12126,230 +12494,230 @@
     </x:row>
     <x:row r="7" ht="109.5" customHeight="1">
       <x:c r="A7" s="35" t="s">
-        <x:v>360</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B7" s="35" t="str">
         <x:v>ID=G1N01D0001; First=G01N01; Last=NhutDuplicate</x:v>
       </x:c>
       <x:c r="C7" s="35" t="s">
-        <x:v>361</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="D7" s="35" t="str">
         <x:v>PIM_EMP_Create_14; PIM_EMP_Search_01; PIM_EMP_Reset_01</x:v>
       </x:c>
       <x:c r="E7" s="35" t="s">
-        <x:v>362</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="F7" s="35" t="s">
-        <x:v>363</x:v>
+        <x:v>333</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="109.5" customHeight="1">
       <x:c r="A8" s="35" t="s">
-        <x:v>364</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B8" s="35" t="s">
-        <x:v>365</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="C8" s="35" t="s">
-        <x:v>366</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="D8" s="35" t="str">
         <x:v>PIM_PERSONAL; PIM_EMP_Search_02</x:v>
       </x:c>
       <x:c r="E8" s="35" t="s">
-        <x:v>367</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="F8" s="35" t="s">
-        <x:v>368</x:v>
+        <x:v>338</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="109.5" customHeight="1">
       <x:c r="A9" s="35" t="s">
-        <x:v>369</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B9" s="35" t="s">
-        <x:v>370</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="C9" s="35" t="s">
-        <x:v>371</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="D9" s="35" t="s">
-        <x:v>372</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="E9" s="35" t="s">
-        <x:v>373</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="F9" s="35" t="s">
-        <x:v>374</x:v>
+        <x:v>344</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="109.5" customHeight="1">
       <x:c r="A10" s="35" t="s">
-        <x:v>375</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B10" s="35" t="s">
-        <x:v>376</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="C10" s="35" t="s">
-        <x:v>377</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D10" s="35" t="str">
         <x:v>PIM_EMP_Filter_01</x:v>
       </x:c>
       <x:c r="E10" s="35" t="s">
-        <x:v>378</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="F10" s="35" t="s">
-        <x:v>379</x:v>
+        <x:v>349</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="109.5" customHeight="1">
       <x:c r="A11" s="35" t="s">
-        <x:v>380</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B11" s="35" t="s">
-        <x:v>381</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="C11" s="35" t="s">
-        <x:v>382</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="D11" s="35" t="s">
-        <x:v>383</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="E11" s="35" t="s">
-        <x:v>384</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="F11" s="35" t="s">
-        <x:v>385</x:v>
+        <x:v>355</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="109.5" customHeight="1">
       <x:c r="A12" s="35" t="s">
-        <x:v>386</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B12" s="35" t="s">
-        <x:v>387</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="C12" s="35" t="s">
-        <x:v>388</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="D12" s="35" t="s">
-        <x:v>389</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="E12" s="35" t="s">
-        <x:v>390</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="F12" s="35" t="s">
-        <x:v>391</x:v>
+        <x:v>361</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="109.5" customHeight="1">
       <x:c r="A13" s="35" t="s">
-        <x:v>392</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B13" s="35" t="s">
-        <x:v>393</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="C13" s="35" t="s">
-        <x:v>394</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D13" s="35" t="s">
-        <x:v>395</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="E13" s="35" t="s">
-        <x:v>396</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="F13" s="35" t="s">
-        <x:v>397</x:v>
+        <x:v>367</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="109.5" customHeight="1">
       <x:c r="A14" s="35" t="s">
-        <x:v>398</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B14" s="35" t="s">
-        <x:v>399</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="C14" s="35" t="s">
-        <x:v>400</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="D14" s="35" t="s">
-        <x:v>401</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="E14" s="35" t="s">
-        <x:v>402</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="F14" s="35" t="s">
-        <x:v>403</x:v>
+        <x:v>373</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="109.5" customHeight="1">
       <x:c r="A15" s="35" t="s">
-        <x:v>404</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B15" s="35" t="s">
-        <x:v>405</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="C15" s="35" t="s">
-        <x:v>406</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="D15" s="35" t="s">
-        <x:v>407</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="E15" s="35" t="s">
-        <x:v>408</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="F15" s="35" t="s">
-        <x:v>409</x:v>
+        <x:v>379</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="109.5" customHeight="1">
       <x:c r="A16" s="35" t="s">
-        <x:v>410</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B16" s="35" t="s">
-        <x:v>411</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="C16" s="35" t="s">
-        <x:v>412</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D16" s="35" t="s">
-        <x:v>413</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="E16" s="35" t="s">
-        <x:v>414</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="F16" s="35" t="s">
-        <x:v>415</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="109.5" customHeight="1">
       <x:c r="A17" s="35" t="s">
-        <x:v>416</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B17" s="35" t="s">
-        <x:v>417</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="C17" s="35" t="s">
-        <x:v>418</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="D17" s="35" t="str">
         <x:v>PIM_EMP_UploadPhoto_01–02</x:v>
       </x:c>
       <x:c r="E17" s="35" t="s">
-        <x:v>419</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="F17" s="35" t="s">
-        <x:v>420</x:v>
+        <x:v>390</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="109.5" customHeight="1">
       <x:c r="A18" s="35" t="s">
-        <x:v>421</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B18" s="35" t="s">
-        <x:v>422</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="C18" s="35" t="str">
         <x:v>PDF thực. PNG hợp lệ 1.048.577 byte (1 MiB + 1 byte), có ancillary chunk; không đổi đuôi tệp.</x:v>
@@ -12358,150 +12726,150 @@
         <x:v>PIM_EMP_UploadPhoto_03–04</x:v>
       </x:c>
       <x:c r="E18" s="35" t="s">
-        <x:v>423</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="F18" s="35" t="s">
-        <x:v>424</x:v>
+        <x:v>394</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="109.5" customHeight="1">
       <x:c r="A19" s="35" t="s">
-        <x:v>425</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="B19" s="35" t="s">
-        <x:v>426</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="C19" s="35" t="s">
-        <x:v>427</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="D19" s="35" t="s">
-        <x:v>428</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="E19" s="35" t="s">
-        <x:v>429</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="F19" s="35" t="s">
-        <x:v>430</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="109.5" customHeight="1">
+        <x:v>400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="110" customHeight="1">
       <x:c r="A20" s="35" t="s">
-        <x:v>431</x:v>
-      </x:c>
-      <x:c r="B20" s="35" t="s">
-        <x:v>432</x:v>
-      </x:c>
-      <x:c r="C20" s="35" t="s">
-        <x:v>433</x:v>
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="B20" s="35" t="str">
+        <x:v>Max Attachment Size: 1048576 byte</x:v>
+      </x:c>
+      <x:c r="C20" s="35" t="str">
+        <x:v>CSV được phép; BIN (application/octet-stream) bị chặn. Tệp quá cỡ: 1.048.577 byte.</x:v>
       </x:c>
       <x:c r="D20" s="35" t="str">
         <x:v>PIM_JOB_UploadContract_02–03; các TC upload</x:v>
       </x:c>
       <x:c r="E20" s="35" t="s">
-        <x:v>434</x:v>
-      </x:c>
-      <x:c r="F20" s="35" t="s">
-        <x:v>435</x:v>
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="F20" s="35" t="str">
+        <x:v>Nguồn: evidence/executions/23130226/PIM_DETAILS_2026-10-28T03-14-37-161Z/upload-config.json</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="109.5" customHeight="1">
       <x:c r="A21" s="35" t="s">
-        <x:v>436</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B21" s="35" t="s">
-        <x:v>437</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="C21" s="35" t="s">
-        <x:v>438</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="D21" s="35" t="s">
-        <x:v>439</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="E21" s="35" t="s">
-        <x:v>440</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="F21" s="35" t="s">
-        <x:v>441</x:v>
+        <x:v>408</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="109.5" customHeight="1">
       <x:c r="A22" s="35" t="s">
-        <x:v>442</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B22" s="35" t="s">
-        <x:v>443</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="C22" s="35" t="s">
-        <x:v>444</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="D22" s="35" t="s">
-        <x:v>445</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="E22" s="35" t="s">
-        <x:v>446</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="F22" s="35" t="s">
-        <x:v>447</x:v>
+        <x:v>414</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="109.5" customHeight="1">
       <x:c r="A23" s="35" t="s">
-        <x:v>448</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B23" s="35" t="s">
-        <x:v>449</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C23" s="35" t="s">
-        <x:v>450</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="D23" s="35" t="s">
-        <x:v>451</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="E23" s="35" t="s">
-        <x:v>452</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="F23" s="35" t="s">
-        <x:v>453</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="109.5" customHeight="1">
       <x:c r="A24" s="35" t="s">
-        <x:v>454</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B24" s="35" t="s">
-        <x:v>455</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="C24" s="35" t="s">
-        <x:v>456</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="D24" s="35" t="s">
-        <x:v>457</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="E24" s="35" t="s">
-        <x:v>458</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="F24" s="35" t="s">
-        <x:v>459</x:v>
+        <x:v>426</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="109.5" customHeight="1">
       <x:c r="A25" s="35" t="s">
-        <x:v>460</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="B25" s="35" t="s">
-        <x:v>461</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="C25" s="35" t="s">
-        <x:v>462</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="D25" s="35" t="s">
-        <x:v>463</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="E25" s="35" t="s">
-        <x:v>464</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="F25" s="35" t="s">
-        <x:v>465</x:v>
+        <x:v>432</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15.75" customHeight="1">
@@ -12514,13 +12882,13 @@
     </x:row>
     <x:row r="27" ht="15.75" customHeight="1">
       <x:c r="A27" s="38" t="s">
-        <x:v>466</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B27" s="38" t="s">
-        <x:v>467</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="C27" s="38" t="s">
-        <x:v>468</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="D27" s="1"/>
       <x:c r="E27" s="1"/>
@@ -12534,7 +12902,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C28" s="35" t="s">
-        <x:v>469</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="D28" s="2"/>
       <x:c r="E28" s="2"/>
@@ -12542,13 +12910,13 @@
     </x:row>
     <x:row r="29" ht="69.75" customHeight="1">
       <x:c r="A29" s="35" t="s">
-        <x:v>470</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B29" s="35" t="s">
-        <x:v>471</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="C29" s="35" t="s">
-        <x:v>472</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="D29" s="2"/>
       <x:c r="E29" s="2"/>
@@ -12556,13 +12924,13 @@
     </x:row>
     <x:row r="30" ht="69.75" customHeight="1">
       <x:c r="A30" s="35" t="s">
-        <x:v>473</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B30" s="35" t="s">
-        <x:v>474</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="C30" s="35" t="s">
-        <x:v>475</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="D30" s="2"/>
       <x:c r="E30" s="2"/>
@@ -12570,13 +12938,13 @@
     </x:row>
     <x:row r="31" ht="69.75" customHeight="1">
       <x:c r="A31" s="35" t="s">
-        <x:v>476</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B31" s="35" t="s">
-        <x:v>477</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="C31" s="35" t="s">
-        <x:v>478</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="D31" s="2"/>
       <x:c r="E31" s="2"/>
@@ -12587,10 +12955,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B32" s="35" t="s">
-        <x:v>479</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="C32" s="35" t="s">
-        <x:v>480</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="D32" s="2"/>
       <x:c r="E32" s="2"/>
@@ -12598,13 +12966,13 @@
     </x:row>
     <x:row r="33" ht="69.75" customHeight="1">
       <x:c r="A33" s="35" t="s">
-        <x:v>481</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B33" s="35" t="s">
-        <x:v>482</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="C33" s="35" t="s">
-        <x:v>483</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D33" s="2"/>
       <x:c r="E33" s="2"/>
@@ -13657,7 +14025,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="3" t="s">
-        <x:v>484</x:v>
+        <x:v>451</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -13673,19 +14041,19 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B4" s="38" t="s">
-        <x:v>485</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="C4" s="38" t="s">
-        <x:v>486</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="D4" s="38" t="s">
-        <x:v>487</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="E4" s="38" t="s">
-        <x:v>488</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="F4" s="38" t="s">
-        <x:v>489</x:v>
+        <x:v>456</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="103.5" customHeight="1">
@@ -13693,19 +14061,19 @@
         <x:v>1.0</x:v>
       </x:c>
       <x:c r="B5" s="35" t="s">
-        <x:v>490</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="C5" s="35" t="s">
-        <x:v>491</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="D5" s="35" t="s">
-        <x:v>492</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="E5" s="35" t="s">
-        <x:v>493</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="F5" s="35" t="str">
-        <x:v>Đã thực hiện PIM_EMP</x:v>
+        <x:v>Đã thực hiện</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="103.5" customHeight="1">
@@ -13713,19 +14081,19 @@
         <x:v>2.0</x:v>
       </x:c>
       <x:c r="B6" s="35" t="s">
-        <x:v>494</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="C6" s="35" t="str">
-        <x:v>Tạo F_DUP, F_PERSON, F_FILTER qua UI; ghi numeric employee key. Chuẩn bị JPG/PNG/PDF và PNG 1 MiB + 1 byte. F_JOB chưa tạo.</x:v>
+        <x:v>Nhân viên Personal/Job riêng, ID theo run token; PDF hợp lệ, quá giới hạn và BIN để kiểm tra upload.</x:v>
       </x:c>
       <x:c r="D6" s="35" t="s">
-        <x:v>495</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="E6" s="35" t="s">
-        <x:v>496</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="F6" s="35" t="str">
-        <x:v>Đã chuẩn bị PIM_EMP</x:v>
+        <x:v>Đã thực hiện</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="103.5" customHeight="1">
@@ -13733,19 +14101,19 @@
         <x:v>3.0</x:v>
       </x:c>
       <x:c r="B7" s="35" t="s">
-        <x:v>497</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="C7" s="35" t="str">
         <x:v>Chạy Playwright PIM_EMP, thêm assertion cho từng expected, lưu log và screenshot thật.</x:v>
       </x:c>
       <x:c r="D7" s="35" t="s">
-        <x:v>498</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="E7" s="35" t="str">
         <x:v>Playwright 1.62.1; Microsoft Edge headless.</x:v>
       </x:c>
       <x:c r="F7" s="35" t="str">
-        <x:v>Đã thực hiện PIM_EMP</x:v>
+        <x:v>Đã thực hiện</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="103.5" customHeight="1">
@@ -13753,19 +14121,19 @@
         <x:v>4.0</x:v>
       </x:c>
       <x:c r="B8" s="35" t="s">
-        <x:v>499</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="C8" s="35" t="str">
-        <x:v>Runner PIM_EMP gồm 25 case theo ID workbook, setup và cleanup riêng. PIM_PERSONAL/PIM_JOB chưa triển khai.</x:v>
+        <x:v>25 case PIM_EMP; 25 PIM_PERSONAL và 25 PIM_JOB theo ID workbook.</x:v>
       </x:c>
       <x:c r="D8" s="35" t="s">
-        <x:v>500</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="E8" s="35" t="s">
-        <x:v>501</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="F8" s="35" t="str">
-        <x:v>Đã thực hiện PIM_EMP</x:v>
+        <x:v>Đã thực hiện</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="103.5" customHeight="1">
@@ -13773,7 +14141,7 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="B9" s="35" t="s">
-        <x:v>502</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="C9" s="35" t="str">
         <x:v>Playwright kiểm tra validation, tìm kiếm, filter và giá trị sau Save/reload.</x:v>
@@ -13785,7 +14153,7 @@
         <x:v>Đợi phản hồi Search và UI cập nhật trước khi assertion.</x:v>
       </x:c>
       <x:c r="F9" s="35" t="str">
-        <x:v>Đã thực hiện PIM_EMP</x:v>
+        <x:v>Đã thực hiện</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="103.5" customHeight="1">
@@ -13793,19 +14161,19 @@
         <x:v>6.0</x:v>
       </x:c>
       <x:c r="B10" s="35" t="s">
-        <x:v>503</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C10" s="35" t="str">
-        <x:v>Kiểm thử upload JPG/PNG/PDF/ảnh quá cỡ và sorting. Attachment/contract chưa chạy.</x:v>
+        <x:v>Kiểm tra attachment, giới hạn tệp; giữ/thay/xóa hợp đồng và đối chiếu nội dung PDF tải xuống.</x:v>
       </x:c>
       <x:c r="D10" s="35" t="s">
-        <x:v>504</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="E10" s="35" t="str">
         <x:v>Playwright setInputFiles; kiểm tra validation và lưu/reload.</x:v>
       </x:c>
       <x:c r="F10" s="35" t="str">
-        <x:v>Đã thực hiện PIM_EMP</x:v>
+        <x:v>Đã thực hiện</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="103.5" customHeight="1">
@@ -13813,19 +14181,19 @@
         <x:v>7.0</x:v>
       </x:c>
       <x:c r="B11" s="35" t="s">
-        <x:v>505</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C11" s="35" t="s">
-        <x:v>506</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D11" s="35" t="s">
-        <x:v>507</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="E11" s="35" t="str">
         <x:v>Đợi giá trị form thực, không chỉ phần tử hiện hữu.</x:v>
       </x:c>
       <x:c r="F11" s="35" t="str">
-        <x:v>Đã thực hiện PIM_EMP</x:v>
+        <x:v>Đã thực hiện</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="103.5" customHeight="1">
@@ -13833,19 +14201,19 @@
         <x:v>8.0</x:v>
       </x:c>
       <x:c r="B12" s="35" t="s">
-        <x:v>508</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="C12" s="35" t="s">
-        <x:v>509</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D12" s="35" t="s">
-        <x:v>510</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="E12" s="35" t="str">
-        <x:v>Run PIM_EMP_20261021_04; thời gian từng case trong Note và JSON.</x:v>
+        <x:v>PIM_EMP_20261021_04; PIM_DETAILS_2026-10-28T03-06-34-596Z; PIM_DETAILS_2026-10-28T03-14-37-161Z</x:v>
       </x:c>
       <x:c r="F12" s="35" t="str">
-        <x:v>Đã thực hiện PIM_EMP</x:v>
+        <x:v>Đã thực hiện</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="103.5" customHeight="1">
@@ -13853,19 +14221,19 @@
         <x:v>9.0</x:v>
       </x:c>
       <x:c r="B13" s="35" t="s">
-        <x:v>511</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C13" s="35" t="s">
-        <x:v>512</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="D13" s="35" t="s">
-        <x:v>513</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="E13" s="35" t="s">
-        <x:v>514</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="F13" s="35" t="str">
-        <x:v>Xem log cleanup</x:v>
+        <x:v>Đã dọn dữ liệu</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="103.5" customHeight="1">
@@ -13873,16 +14241,16 @@
         <x:v>10.0</x:v>
       </x:c>
       <x:c r="B14" s="35" t="s">
-        <x:v>515</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="C14" s="35" t="s">
-        <x:v>516</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="D14" s="35" t="s">
-        <x:v>517</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E14" s="35" t="s">
-        <x:v>518</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="F14" s="35" t="str">
         <x:v>Thiết kế đã rà soát</x:v>
@@ -13906,7 +14274,7 @@
     </x:row>
     <x:row r="17" ht="44" customHeight="1">
       <x:c r="A17" s="2" t="str">
-        <x:v>PIM_EMP đã chạy bằng Playwright. Hai chức năng PIM_PERSONAL/PIM_JOB chưa chạy, giữ Untested. ID dùng Module_Action_XX; số thứ tự bắt đầu từ 01 trong từng nhóm hành động.</x:v>
+        <x:v>Đã chạy 75 case của ba chức năng PIM. Kết quả từng case và các lần chạy nằm trong evidence/executions/23130226/.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -14938,7 +15306,7 @@
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
       <x:c r="B1" s="3" t="s">
-        <x:v>519</x:v>
+        <x:v>486</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -14981,29 +15349,29 @@
       <x:c r="H4" s="39"/>
       <x:c r="I4" s="39"/>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="65" customHeight="1">
       <x:c r="B5" s="35" t="s">
-        <x:v>520</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="C5" s="39"/>
       <x:c r="D5" s="46" t="str">
-        <x:v>PIM_EMP_20261021_04</x:v>
+        <x:v>PIM_EMP_20261021_04; PIM_DETAILS_2026-10-28T03-06-34-596Z; PIM_DETAILS_2026-10-28T03-14-37-161Z</x:v>
       </x:c>
       <x:c r="E5" s="36"/>
       <x:c r="F5" s="36"/>
       <x:c r="G5" s="50" t="d">
-        <x:v>2026-10-21T10:26:20.547Z</x:v>
+        <x:v>2026-10-28T03:20:14.908Z</x:v>
       </x:c>
       <x:c r="H5" s="36"/>
       <x:c r="I5" s="36"/>
     </x:row>
     <x:row r="6">
       <x:c r="B6" s="35" t="s">
-        <x:v>521</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="C6" s="39"/>
       <x:c r="D6" s="46" t="str">
-        <x:v>Playwright / Microsoft Edge 155.0.4283.62 (headless)</x:v>
+        <x:v>Playwright / Edge 155.0.4283.62 (EMP); 156.0.4314.50 (PERSONAL/JOB)</x:v>
       </x:c>
       <x:c r="E6" s="36"/>
       <x:c r="F6" s="36"/>
@@ -15054,7 +15422,7 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="I9" s="38" t="s">
-        <x:v>522</x:v>
+        <x:v>489</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
@@ -15098,7 +15466,7 @@
       </x:c>
       <x:c r="D11" s="35" t="n">
         <x:f>PIM_PERSONAL!A6</x:f>
-        <x:v>0</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E11" s="35" t="n">
         <x:f>PIM_PERSONAL!B6</x:f>
@@ -15106,7 +15474,7 @@
       </x:c>
       <x:c r="F11" s="35" t="n">
         <x:f>PIM_PERSONAL!C6</x:f>
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G11" s="35" t="n">
         <x:f>PIM_PERSONAL!D6</x:f>
@@ -15130,7 +15498,7 @@
       </x:c>
       <x:c r="D12" s="35" t="n">
         <x:f>PIM_JOB!A6</x:f>
-        <x:v>0</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E12" s="35" t="n">
         <x:f>PIM_JOB!B6</x:f>
@@ -15138,7 +15506,7 @@
       </x:c>
       <x:c r="F12" s="35" t="n">
         <x:f>PIM_JOB!C6</x:f>
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G12" s="35" t="n">
         <x:f>PIM_JOB!D6</x:f>
@@ -15165,12 +15533,12 @@
     </x:row>
     <x:row r="14">
       <x:c r="B14" s="47" t="s">
-        <x:v>522</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="C14" s="36"/>
       <x:c r="D14" s="47" t="n">
         <x:f t="shared" ref="D14:I14" si="1">SUM(D10:D12)</x:f>
-        <x:v>23</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E14" s="47" t="n">
         <x:f t="shared" si="1">SUM(E10:E12)</x:f>
@@ -15178,7 +15546,7 @@
       </x:c>
       <x:c r="F14" s="47" t="n">
         <x:f t="shared" si="1">SUM(F10:F12)</x:f>
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G14" s="47" t="n">
         <x:f t="shared" si="1">SUM(G10:G12)</x:f>
@@ -15215,13 +15583,13 @@
     </x:row>
     <x:row r="17">
       <x:c r="B17" s="35" t="s">
-        <x:v>523</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="C17" s="39"/>
       <x:c r="D17" s="39"/>
       <x:c r="E17" s="48" t="n">
         <x:f>IF(I14=0,"",(D14+E14)/I14)</x:f>
-        <x:v>0.30666666666666664</x:v>
+        <x:v>0.9733333333333334</x:v>
       </x:c>
       <x:c r="F17" s="39"/>
       <x:c r="G17" s="2"/>
@@ -15230,7 +15598,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="B18" s="35" t="s">
-        <x:v>524</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="C18" s="39"/>
       <x:c r="D18" s="39"/>
@@ -15255,7 +15623,7 @@
     </x:row>
     <x:row r="20" ht="39.75" customHeight="1">
       <x:c r="B20" s="2" t="s">
-        <x:v>525</x:v>
+        <x:v>492</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1">
@@ -15270,7 +15638,7 @@
     </x:row>
     <x:row r="22" ht="65" customHeight="1">
       <x:c r="B22" s="2" t="str">
-        <x:v>Kết quả PIM_EMP: 23 Passed, 0 Failed, 2 Blocked. PIM_PERSONAL/PIM_JOB: 50 Untested. Log và ảnh: evidence/executions/23130226/PIM_EMP_20261021_04/. Các run trước dùng chẩn đoán script, không cộng dồn vào report.</x:v>
+        <x:v>PIM_EMP: 23 Passed, 2 Blocked. PIM_PERSONAL/PIM_JOB: 50 Passed, 0 Failed, 0 Blocked. Lấy kết quả mới nhất theo Case ID; đường dẫn log/ảnh tại cột Note.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15.75" customHeight="1">
